--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$C$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Runs'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Runs'!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,12 +458,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,7 +480,13 @@
         </is>
       </c>
       <c r="C1" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D1" s="1" t="n">
         <v>3710</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>6010</v>
       </c>
     </row>
     <row r="2">
@@ -493,6 +501,12 @@
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>101.40</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -506,6 +520,12 @@
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>105.20</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -519,6 +539,12 @@
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>336.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -532,6 +558,12 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>630.00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -545,6 +577,12 @@
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14000.00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -558,6 +596,12 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5800.00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -570,11 +614,13 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -587,16 +633,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Jamesbond</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -605,11 +653,17 @@
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>355.00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Jamesbond</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -618,11 +672,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Jamesbond</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -632,14 +688,16 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>355.00</t>
-        </is>
-      </c>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Jamesbond</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -647,12 +705,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -661,11 +725,17 @@
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>787.50</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -674,11 +744,17 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>792.50</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>UpNDown</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -687,11 +763,17 @@
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>UpNDown</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -700,73 +782,11 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Qbert</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>787.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Qbert</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>792.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>UpNDown</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2654.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>UpNDown</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -777,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -883,12 +903,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Krull_seed6010_X</t>
+          <t>Mamba2_AC_Assault_seed6010_X</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>mera5ngk</t>
+          <t>ds19f3ml</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -908,7 +928,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -919,7 +939,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>336.00</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="n">
         <v>50000</v>
@@ -939,18 +963,18 @@
         <v>0.0625</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>46277.48331018518</v>
+        <v>46277.48542824074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Frostbite_seed6010_X</t>
+          <t>Mamba2_AC_Amidar_seed6010_X</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>kwxa3efq</t>
+          <t>d2x1c1en</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -970,7 +994,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -1001,18 +1025,18 @@
         <v>0.0625</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>46277.48446759259</v>
+        <v>46277.4872800926</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Assault_seed6010_X</t>
+          <t>Mamba2_AC_Amidar_seed3710_X</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ds19f3ml</t>
+          <t>s7qnin4f</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1032,19 +1056,27 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6010</v>
+        <v>3710</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>101.40</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1063,18 +1095,18 @@
         <v>0.0625</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>46277.48542824074</v>
+        <v>46277.51052083333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed6010_X</t>
+          <t>Mamba2_AC_Pong_seed2000_X</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>d2x1c1en</t>
+          <t>ldp9bu6i</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1094,11 +1126,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>6010</v>
+        <v>2000</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1125,18 +1157,18 @@
         <v>0.0625</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>46277.4872800926</v>
+        <v>46277.51086805556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed3710_X</t>
+          <t>Mamba2_AC_BattleZone_seed3710_X</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>s7qnin4f</t>
+          <t>9l57kpp0</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1156,7 +1188,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>BattleZone</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -1167,8 +1199,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>14000.00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1187,18 +1227,18 @@
         <v>0.0625</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>46277.51052083333</v>
+        <v>46277.51194444444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed2000_X</t>
+          <t>Mamba2_AC_Amidar_seed3710_O</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ldp9bu6i</t>
+          <t>f2hapfd6</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1218,19 +1258,27 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2000</v>
+        <v>3710</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>105.20</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1249,18 +1297,18 @@
         <v>0.0625</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>46277.51086805556</v>
+        <v>46277.58818287037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_BattleZone_seed3710_X</t>
+          <t>Mamba2_AC_BattleZone_seed3710_O</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>9l57kpp0</t>
+          <t>xjmo67zz</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1288,11 +1336,19 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>5800.00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1311,18 +1367,18 @@
         <v>0.0625</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>46277.51194444444</v>
+        <v>46277.5909375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed3710_O</t>
+          <t>Mamba2_AC_Pong_seed2010_X</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>f2hapfd6</t>
+          <t>r7xx98gc</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1342,18 +1398,22 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3710</v>
+        <v>2010</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
         <v>50000</v>
@@ -1373,18 +1433,18 @@
         <v>0.0625</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>46277.58818287037</v>
+        <v>46277.63061342593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_BattleZone_seed3710_O</t>
+          <t>Mamba2_AC_Assault_seed6010_O</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>xjmo67zz</t>
+          <t>cjat5h3s</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1404,18 +1464,22 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>BattleZone</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3710</v>
+        <v>6010</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>630.00</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
         <v>50000</v>
@@ -1435,18 +1499,18 @@
         <v>0.0625</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>46277.5909375</v>
+        <v>46277.66618055556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed2010_X</t>
+          <t>Mamba2_AC_Amidar_seed6010_O</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>r7xx98gc</t>
+          <t>b7d1fcs6</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1466,15 +1530,15 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2010</v>
+        <v>6010</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
@@ -1497,18 +1561,18 @@
         <v>0.0625</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>46277.63061342593</v>
+        <v>46277.66625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Krull_seed6010_O</t>
+          <t>Mamba2_AC_Pong_seed2000_O</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>jfobo71c</t>
+          <t>54peul18</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1528,11 +1592,11 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6010</v>
+        <v>2000</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1559,18 +1623,18 @@
         <v>0.0625</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>46277.66219907408</v>
+        <v>46277.70894675926</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Frostbite_seed6010_O</t>
+          <t>Mamba2_AC_Qbert_seed3710_X</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>yek1u6ty</t>
+          <t>rdsp4vkd</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1590,19 +1654,27 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6010</v>
+        <v>3710</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>787.50</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1621,18 +1693,18 @@
         <v>0.0625</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>46277.66439814815</v>
+        <v>46277.78224537037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Assault_seed6010_O</t>
+          <t>Mamba2_AC_ChopperCommand_seed3710_X</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>cjat5h3s</t>
+          <t>wprgvkwu</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1652,19 +1724,27 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>ChopperCommand</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>6010</v>
+        <v>3710</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1683,18 +1763,18 @@
         <v>0.0625</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>46277.66618055556</v>
+        <v>46277.79376157407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed6010_O</t>
+          <t>Mamba2_AC_Pong_seed2010_O</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>b7d1fcs6</t>
+          <t>dbr7fc7u</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1714,18 +1794,22 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>6010</v>
+        <v>2010</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
         <v>50000</v>
@@ -1745,18 +1829,18 @@
         <v>0.0625</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>46277.66625</v>
+        <v>46277.83049768519</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed2000_O</t>
+          <t>Mamba2_AC_Qbert_seed3710_O</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>54peul18</t>
+          <t>bwkx0q0r</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1776,19 +1860,27 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2000</v>
+        <v>3710</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>792.50</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="n">
         <v>50000</v>
       </c>
@@ -1807,18 +1899,18 @@
         <v>0.0625</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>46277.70894675926</v>
+        <v>46277.86043981482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Qbert_seed3710_X</t>
+          <t>Mamba2_AC_ChopperCommand_seed3710_O</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>rdsp4vkd</t>
+          <t>nclj0x34</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1838,7 +1930,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>ChopperCommand</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -1846,17 +1938,17 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>787.50</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -1877,18 +1969,18 @@
         <v>0.0625</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>46277.78224537037</v>
+        <v>46277.87179398148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_ChopperCommand_seed3710_X</t>
+          <t>Mamba2_AC_Jamesbond_seed3710_X</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>wprgvkwu</t>
+          <t>6jiief14</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1908,7 +2000,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>ChopperCommand</t>
+          <t>Jamesbond</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -1921,12 +2013,12 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>1250.00</t>
+          <t>355.00</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
@@ -1947,18 +2039,18 @@
         <v>0.0625</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>46277.79376157407</v>
+        <v>46278.05765046296</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed2010_O</t>
+          <t>Mamba2_AC_UpNDown_seed3710_X</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>dbr7fc7u</t>
+          <t>se3zzsqc</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1978,19 +2070,27 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>UpNDown</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2010</v>
+        <v>3710</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2009,291 +2109,11 @@
         <v>0.0625</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>46277.83049768519</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Qbert_seed3710_O</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>bwkx0q0r</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Qbert</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>792.50</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>46277.86043981482</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_ChopperCommand_seed3710_O</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>nclj0x34</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>ChopperCommand</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>1430.00</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>46277.87179398148</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Jamesbond_seed3710_X</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>6jiief14</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Jamesbond</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>355.00</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>46278.05765046296</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_UpNDown_seed3710_X</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>se3zzsqc</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>UpNDown</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2654.00</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P23" s="4" t="n">
         <v>46278.08553240741</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -632,7 +632,11 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>323.40</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
@@ -654,7 +658,11 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>310.80</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>630.00</t>
@@ -1076,7 +1084,11 @@
           <t>268.00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>244.00</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1102,7 +1114,11 @@
           <t>267.00</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>246.00</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1117,8 +1133,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2198.00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1016.00</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1135,8 +1159,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>1160.00</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1082.00</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
@@ -1256,7 +1288,11 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>9836.00</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1274,7 +1310,11 @@
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>8737.00</t>
+        </is>
+      </c>
       <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2512,8 +2552,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>323.40</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2644,8 +2692,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>9836.00</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2706,8 +2762,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>244.00</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2768,8 +2832,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2198.00</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2830,8 +2902,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>310.80</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2892,8 +2972,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>8737.00</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="n">
         <v>50000</v>
       </c>
@@ -2954,8 +3042,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>246.00</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="n">
         <v>50000</v>
       </c>
@@ -3156,8 +3252,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>1016.00</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="n">
         <v>50000</v>
       </c>
@@ -3358,8 +3462,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>1160.00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
       <c r="K28" s="3" t="n">
         <v>50000</v>
       </c>
@@ -3420,8 +3532,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>1082.00</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="n">
         <v>50000</v>
       </c>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -95,13 +95,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -489,6 +489,8 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,13 +514,19 @@
         <v>2010</v>
       </c>
       <c r="F1" s="1" t="n">
+        <v>3290</v>
+      </c>
+      <c r="G1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>6010</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>6020</v>
       </c>
     </row>
     <row r="2">
@@ -532,38 +540,58 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>1376.00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -579,43 +607,47 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -632,40 +664,52 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>630.00</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
     </row>
@@ -681,45 +725,57 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -738,24 +794,28 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -775,39 +835,43 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>13600.00</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -824,42 +888,46 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -876,42 +944,46 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -931,39 +1003,43 @@
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -980,34 +1056,46 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CrazyClimber</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1034,32 +1122,36 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>136.50</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>131.50</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1079,47 +1171,59 @@
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1145,33 +1249,45 @@
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>1082.00</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1190,7 +1306,7 @@
           <t>7552.00</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -1198,28 +1314,36 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1239,39 +1363,43 @@
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>445.00</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1288,34 +1416,38 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1328,7 +1460,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -1336,26 +1468,42 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>KungFuMaster</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>17320.00</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1378,28 +1526,32 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1419,44 +1571,48 @@
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>810.00</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1464,46 +1620,102 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>6669.00</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>2654.00</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>6669.00</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>4831.00</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1516,7 +1728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1620,65 +1832,65 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6010_X</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ds19f3ml</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O2" s="3" t="n">
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P2" s="6" t="n">
@@ -1686,69 +1898,69 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed3710_X</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>s7qnin4f</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" s="3" t="n">
+      <c r="K3" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P3" s="6" t="n">
@@ -1756,69 +1968,69 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed3710_X</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>9l57kpp0</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O4" s="3" t="n">
+      <c r="K4" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P4" s="6" t="n">
@@ -1826,69 +2038,69 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed3710_O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>f2hapfd6</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O5" s="3" t="n">
+      <c r="K5" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P5" s="6" t="n">
@@ -1896,69 +2108,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed3710_O</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>xjmo67zz</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O6" s="3" t="n">
+      <c r="K6" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P6" s="6" t="n">
@@ -1966,65 +2178,65 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Pong_seed2010_X</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>r7xx98gc</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O7" s="3" t="n">
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P7" s="6" t="n">
@@ -2032,65 +2244,65 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6010_O</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>cjat5h3s</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" s="3" t="n">
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P8" s="6" t="n">
@@ -2098,69 +2310,69 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed3710_X</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>rdsp4vkd</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O9" s="3" t="n">
+      <c r="K9" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P9" s="6" t="n">
@@ -2168,69 +2380,69 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed3710_X</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>wprgvkwu</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O10" s="3" t="n">
+      <c r="K10" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P10" s="6" t="n">
@@ -2238,65 +2450,65 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Pong_seed2010_O</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>dbr7fc7u</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O11" s="3" t="n">
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P11" s="6" t="n">
@@ -2304,69 +2516,69 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed3710_O</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>bwkx0q0r</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O12" s="3" t="n">
+      <c r="K12" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P12" s="6" t="n">
@@ -2374,69 +2586,69 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed3710_O</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>nclj0x34</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O13" s="3" t="n">
+      <c r="K13" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O13" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P13" s="6" t="n">
@@ -2444,69 +2656,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed3710_X</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>6jiief14</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3" t="n">
+      <c r="K14" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P14" s="6" t="n">
@@ -2514,69 +2726,69 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6000_X</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>trzt11e3</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" s="3" t="n">
+      <c r="K15" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P15" s="6" t="n">
@@ -2584,69 +2796,69 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed3710_X</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>se3zzsqc</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O16" s="3" t="n">
+      <c r="K16" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P16" s="6" t="n">
@@ -2654,69 +2866,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed6000_X</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>1yec0x84</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>7.71</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O17" s="3" t="n">
+      <c r="K17" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P17" s="6" t="n">
@@ -2724,69 +2936,69 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed6000_X</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>x179mvnn</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" s="3" t="n">
+      <c r="K18" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P18" s="6" t="n">
@@ -2794,69 +3006,69 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2000_X</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>w71i8l57</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>2198.00</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O19" s="3" t="n">
+      <c r="K19" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P19" s="6" t="n">
@@ -2864,69 +3076,69 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6000_O</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>gkig0jzp</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" s="3" t="n">
+      <c r="K20" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O20" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P20" s="6" t="n">
@@ -2934,69 +3146,69 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed6000_O</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>44jwn1l3</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>6.68</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O21" s="3" t="n">
+      <c r="K21" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P21" s="6" t="n">
@@ -3004,69 +3216,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed6000_O</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>ta68s2xt</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O22" s="3" t="n">
+      <c r="K22" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P22" s="6" t="n">
@@ -3074,69 +3286,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed3710_X</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>viyvv2sn</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O23" s="3" t="n">
+      <c r="K23" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O23" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P23" s="6" t="n">
@@ -3144,69 +3356,69 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed710_X</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>1s2r1ww6</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>260.00</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O24" s="3" t="n">
+      <c r="K24" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P24" s="6" t="n">
@@ -3214,69 +3426,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2010_X</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>d79dpuck</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>1016.00</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O25" s="3" t="n">
+      <c r="K25" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P25" s="6" t="n">
@@ -3284,69 +3496,69 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed3710_O</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>3inp5tkf</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O26" s="3" t="n">
+      <c r="K26" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O26" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P26" s="6" t="n">
@@ -3354,69 +3566,69 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed710_O</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>j8k6dit4</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O27" s="3" t="n">
+      <c r="K27" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O27" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P27" s="6" t="n">
@@ -3424,69 +3636,69 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2000_O</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>hayhdbkq</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O28" s="3" t="n">
+      <c r="K28" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P28" s="6" t="n">
@@ -3494,69 +3706,69 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2010_O</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>6jttrkzf</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>1082.00</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O29" s="3" t="n">
+      <c r="K29" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P29" s="6" t="n">
@@ -3564,69 +3776,69 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Alien_seed6000_X</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>v3h7qzfr</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>0.16</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O30" s="3" t="n">
+      <c r="K30" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O30" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P30" s="6" t="n">
@@ -3634,69 +3846,69 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed6000_X</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>yjshhtba</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O31" s="3" t="n">
+      <c r="K31" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O31" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P31" s="6" t="n">
@@ -3704,69 +3916,69 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6000_X</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>opbwjgoy</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O32" s="3" t="n">
+      <c r="K32" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O32" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P32" s="6" t="n">
@@ -3774,69 +3986,69 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6010_X</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>9v6xo84n</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O33" s="3" t="n">
+      <c r="K33" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P33" s="6" t="n">
@@ -3844,69 +4056,69 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Alien_seed6000_O</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>jazjrjus</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O34" s="3" t="n">
+      <c r="K34" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P34" s="6" t="n">
@@ -3914,69 +4126,69 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed6000_O</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>1k1plu0t</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O35" s="3" t="n">
+      <c r="K35" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O35" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P35" s="6" t="n">
@@ -3984,69 +4196,69 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6000_O</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>s7kzk78g</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O36" s="3" t="n">
+      <c r="K36" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P36" s="6" t="n">
@@ -4054,69 +4266,69 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6010_O</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>nxxmc2a8</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O37" s="3" t="n">
+      <c r="K37" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P37" s="6" t="n">
@@ -4124,69 +4336,69 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2000_X</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>gpz37fx4</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>224.50</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O38" s="3" t="n">
+      <c r="K38" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P38" s="6" t="n">
@@ -4194,69 +4406,69 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2010_X</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>uqrdvt6u</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>116.00</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>-0.02</t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O39" s="3" t="n">
+      <c r="K39" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P39" s="6" t="n">
@@ -4264,69 +4476,69 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed710_X</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>66c4h08p</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>480.00</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O40" s="3" t="n">
+      <c r="K40" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O40" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P40" s="6" t="n">
@@ -4334,69 +4546,69 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2000_O</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>pg8ek0ba</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>136.50</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O41" s="3" t="n">
+      <c r="K41" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O41" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P41" s="6" t="n">
@@ -4404,69 +4616,69 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed710_X</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>ti91iyzh</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>9400.00</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O42" s="3" t="n">
+      <c r="K42" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O42" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P42" s="6" t="n">
@@ -4474,69 +4686,69 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed710_O</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>a54n9otf</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>810.00</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O43" s="3" t="n">
+      <c r="K43" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O43" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P43" s="6" t="n">
@@ -4544,61 +4756,61 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BankHeist_seed6000_X</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>z0jszbje</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>crashed</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O44" s="3" t="n">
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O44" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P44" s="6" t="n">
@@ -4606,69 +4818,69 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed710_O</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>d1xbki7b</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>13600.00</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="K45" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O45" s="3" t="n">
+      <c r="K45" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O45" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P45" s="6" t="n">
@@ -4676,69 +4888,69 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2010_O</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>mgo4pji4</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>131.50</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O46" s="3" t="n">
+      <c r="K46" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P46" s="6" t="n">
@@ -4746,61 +4958,61 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_BankHeist_seed6010_X</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>4b4w07hb</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>crashed</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O47" s="3" t="n">
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O47" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P47" s="6" t="n">
@@ -4808,69 +5020,69 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6000_X</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>8am80ulg</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>7.77</t>
         </is>
       </c>
-      <c r="K48" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N48" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O48" s="3" t="n">
+      <c r="K48" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O48" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P48" s="6" t="n">
@@ -4878,69 +5090,69 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6010_X</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>ygndqe22</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>6.17</t>
         </is>
       </c>
-      <c r="K49" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O49" s="3" t="n">
+      <c r="K49" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O49" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P49" s="6" t="n">
@@ -4948,69 +5160,69 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed710_X</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>z767yjw0</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>6669.00</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="K50" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O50" s="3" t="n">
+      <c r="K50" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O50" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P50" s="6" t="n">
@@ -5018,69 +5230,69 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed710_X</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>28777040</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>1450.00</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="K51" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O51" s="3" t="n">
+      <c r="K51" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P51" s="6" t="n">
@@ -5088,69 +5300,69 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed710_O</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>mbjmpmf5</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>4831.00</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="K52" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N52" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O52" s="3" t="n">
+      <c r="K52" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O52" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P52" s="6" t="n">
@@ -5158,69 +5370,69 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6000_O</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>efjroqcm</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G53" s="3" t="n">
+      <c r="G53" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>8.22</t>
         </is>
       </c>
-      <c r="K53" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N53" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O53" s="3" t="n">
+      <c r="K53" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O53" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P53" s="6" t="n">
@@ -5228,69 +5440,69 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed710_O</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>25ay75ia</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>1350.00</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="K54" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N54" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O54" s="3" t="n">
+      <c r="K54" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O54" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P54" s="6" t="n">
@@ -5298,69 +5510,69 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6010_O</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>3b60h9wf</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>4.52</t>
         </is>
       </c>
-      <c r="K55" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N55" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O55" s="3" t="n">
+      <c r="K55" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O55" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P55" s="6" t="n">
@@ -5368,69 +5580,69 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6000_X</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>471e46mi</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O56" s="3" t="n">
+      <c r="K56" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O56" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P56" s="6" t="n">
@@ -5438,69 +5650,69 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed3710_O</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>ycm22u8x</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>3710</v>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="K57" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N57" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O57" s="3" t="n">
+      <c r="K57" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O57" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P57" s="6" t="n">
@@ -5508,69 +5720,69 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6010_X</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>nn7colrf</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="4" t="n">
         <v>6010</v>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="K58" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O58" s="3" t="n">
+      <c r="K58" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O58" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P58" s="6" t="n">
@@ -5578,69 +5790,69 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed710_X</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>udojzqq3</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>485.00</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="K59" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O59" s="3" t="n">
+      <c r="K59" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O59" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P59" s="6" t="n">
@@ -5648,69 +5860,69 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Hero_seed2000_X</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>zhmjfyq2</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>7552.00</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="K60" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N60" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O60" s="3" t="n">
+      <c r="K60" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O60" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P60" s="6" t="n">
@@ -5718,69 +5930,69 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed710_O</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>vx1geb4a</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="G61" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>445.00</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="K61" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O61" s="3" t="n">
+      <c r="K61" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O61" s="4" t="n">
         <v>0.0625</v>
       </c>
       <c r="P61" s="6" t="n">
@@ -6281,6 +6493,1324 @@
       </c>
       <c r="P69" s="8" t="n">
         <v>46279.95943287037</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed710_O</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>60mawi6e</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>710</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>17320.00</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P70" s="6" t="n">
+        <v>46280.03707175926</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>tbv6brxu</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O71" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>46280.04559027778</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed2010_O</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>kzgxj2nm</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N72" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O72" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>46280.05359953704</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6000_Both</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>afcawwxy</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O73" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P73" s="8" t="n">
+        <v>46280.10148148148</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>fgvceo4q</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N74" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O74" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P74" s="8" t="n">
+        <v>46280.10788194444</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2jzlrkza</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N75" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O75" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P75" s="8" t="n">
+        <v>46280.1452199074</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed710_Both</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>tx3sbd42</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O76" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P76" s="8" t="n">
+        <v>46280.16856481481</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>rsx2aezz</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P77" s="8" t="n">
+        <v>46280.19780092593</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed3290_Both</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>3darugr1</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+      <c r="K78" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N78" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>46280.2187962963</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>f9y9q608</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>1376.00</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P79" s="6" t="n">
+        <v>46280.24451388889</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed710_O</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>316d6dg5</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr"/>
+      <c r="J80" s="7" t="inlineStr"/>
+      <c r="K80" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N80" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O80" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P80" s="8" t="n">
+        <v>46280.24539351852</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed6020_Both</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>n1hjnzlz</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O81" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P81" s="8" t="n">
+        <v>46280.26670138889</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed6020_Both</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>n1hjnzlz</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr"/>
+      <c r="K82" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N82" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O82" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P82" s="8" t="n">
+        <v>46280.26670138889</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>p85gt3g5</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N83" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O83" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P83" s="8" t="n">
+        <v>46280.27893518518</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>6rn1636n</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N84" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O84" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P84" s="8" t="n">
+        <v>46280.29326388889</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>6rn1636n</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O85" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P85" s="8" t="n">
+        <v>46280.29326388889</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed3290_O</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>bc75s840</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O86" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P86" s="8" t="n">
+        <v>46280.31445601852</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>xabv161o</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O87" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P87" s="8" t="n">
+        <v>46280.32222222222</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>xabv161o</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O88" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P88" s="8" t="n">
+        <v>46280.32222222222</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>r41a1emc</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O89" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P89" s="8" t="n">
+        <v>46280.32361111111</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>r41a1emc</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O90" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P90" s="8" t="n">
+        <v>46280.32361111111</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -95,13 +95,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,11 +540,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
@@ -562,36 +558,36 @@
       <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1169.00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,32 +618,32 @@
       <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -675,39 +671,39 @@
           <t>336.00</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -725,7 +721,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -746,36 +742,36 @@
       <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -798,24 +794,24 @@
       <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -846,32 +842,32 @@
       <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>13600.00</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -902,32 +898,32 @@
       <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -958,32 +954,32 @@
       <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>17.20</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1014,32 +1010,32 @@
       <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1057,45 +1053,45 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66980.00</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>82640.00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>CrazyClimber</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>77110.00</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>71030.00</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1126,32 +1122,32 @@
       <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>136.50</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>131.50</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1171,11 +1167,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
@@ -1190,40 +1182,40 @@
       <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1249,45 +1241,41 @@
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>1082.00</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1306,9 +1294,9 @@
           <t>7552.00</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7510.00</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -1318,32 +1306,32 @@
       <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>7564.00</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1374,32 +1362,32 @@
       <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>445.00</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>605.00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1426,28 +1414,28 @@
       <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1460,15 +1448,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>20980.00</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -1478,32 +1466,32 @@
       <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>KungFuMaster</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>17320.00</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1530,28 +1518,28 @@
       <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="4" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1582,32 +1570,32 @@
       <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>810.00</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1626,7 +1614,7 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
@@ -1634,32 +1622,32 @@
       <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>RoadRunner</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1690,32 +1678,32 @@
       <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>4831.00</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1728,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1832,65 +1820,65 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6010_X</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ds19f3ml</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O2" s="4" t="n">
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P2" s="6" t="n">
@@ -1898,69 +1886,69 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed3710_X</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>s7qnin4f</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P3" s="6" t="n">
@@ -1968,69 +1956,69 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed3710_X</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>9l57kpp0</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P4" s="6" t="n">
@@ -2038,69 +2026,69 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed3710_O</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>f2hapfd6</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P5" s="6" t="n">
@@ -2108,69 +2096,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed3710_O</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>xjmo67zz</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P6" s="6" t="n">
@@ -2178,65 +2166,65 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Pong_seed2010_X</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>r7xx98gc</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O7" s="4" t="n">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P7" s="6" t="n">
@@ -2244,65 +2232,65 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6010_O</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>cjat5h3s</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" s="4" t="n">
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O8" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P8" s="6" t="n">
@@ -2310,69 +2298,69 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed3710_X</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>rdsp4vkd</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O9" s="4" t="n">
+      <c r="K9" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P9" s="6" t="n">
@@ -2380,69 +2368,69 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed3710_X</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>wprgvkwu</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O10" s="4" t="n">
+      <c r="K10" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O10" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P10" s="6" t="n">
@@ -2450,65 +2438,65 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Pong_seed2010_O</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>dbr7fc7u</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Pong</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O11" s="4" t="n">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P11" s="6" t="n">
@@ -2516,69 +2504,69 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed3710_O</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>bwkx0q0r</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O12" s="4" t="n">
+      <c r="K12" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O12" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P12" s="6" t="n">
@@ -2586,69 +2574,69 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed3710_O</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>nclj0x34</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O13" s="4" t="n">
+      <c r="K13" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O13" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P13" s="6" t="n">
@@ -2656,69 +2644,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed3710_X</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>6jiief14</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="K14" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P14" s="6" t="n">
@@ -2726,69 +2714,69 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6000_X</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>trzt11e3</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="K15" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O15" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P15" s="6" t="n">
@@ -2796,69 +2784,69 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed3710_X</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>se3zzsqc</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O16" s="4" t="n">
+      <c r="K16" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O16" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P16" s="6" t="n">
@@ -2866,69 +2854,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed6000_X</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>1yec0x84</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>7.71</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O17" s="4" t="n">
+      <c r="K17" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P17" s="6" t="n">
@@ -2936,69 +2924,69 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed6000_X</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>x179mvnn</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="K18" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P18" s="6" t="n">
@@ -3006,69 +2994,69 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2000_X</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>w71i8l57</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>2198.00</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="K19" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O19" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P19" s="6" t="n">
@@ -3076,69 +3064,69 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Assault_seed6000_O</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>gkig0jzp</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="K20" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O20" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P20" s="6" t="n">
@@ -3146,69 +3134,69 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed6000_O</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>44jwn1l3</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Krull</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>6.68</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O21" s="4" t="n">
+      <c r="K21" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O21" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P21" s="6" t="n">
@@ -3216,69 +3204,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed6000_O</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>ta68s2xt</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K22" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O22" s="4" t="n">
+      <c r="K22" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O22" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P22" s="6" t="n">
@@ -3286,69 +3274,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed3710_X</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>viyvv2sn</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="K23" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O23" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P23" s="6" t="n">
@@ -3356,69 +3344,69 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed710_X</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>1s2r1ww6</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>260.00</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O24" s="4" t="n">
+      <c r="K24" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P24" s="6" t="n">
@@ -3426,69 +3414,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2010_X</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>d79dpuck</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>1016.00</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O25" s="4" t="n">
+      <c r="K25" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O25" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P25" s="6" t="n">
@@ -3496,69 +3484,69 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed3710_O</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>3inp5tkf</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O26" s="4" t="n">
+      <c r="K26" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O26" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P26" s="6" t="n">
@@ -3566,69 +3554,69 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Frostbite_seed710_O</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>j8k6dit4</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Frostbite</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O27" s="4" t="n">
+      <c r="K27" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O27" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P27" s="6" t="n">
@@ -3636,69 +3624,69 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2000_O</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>hayhdbkq</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O28" s="4" t="n">
+      <c r="K28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P28" s="6" t="n">
@@ -3706,69 +3694,69 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Gopher_seed2010_O</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>6jttrkzf</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Gopher</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>1082.00</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="K29" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O29" s="4" t="n">
+      <c r="K29" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P29" s="6" t="n">
@@ -3776,69 +3764,69 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Alien_seed6000_X</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>v3h7qzfr</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>0.16</t>
         </is>
       </c>
-      <c r="K30" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O30" s="4" t="n">
+      <c r="K30" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O30" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P30" s="6" t="n">
@@ -3846,69 +3834,69 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed6000_X</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>yjshhtba</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="K31" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O31" s="4" t="n">
+      <c r="K31" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P31" s="6" t="n">
@@ -3916,69 +3904,69 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6000_X</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>opbwjgoy</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="K32" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O32" s="4" t="n">
+      <c r="K32" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O32" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P32" s="6" t="n">
@@ -3986,69 +3974,69 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6010_X</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>9v6xo84n</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K33" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O33" s="4" t="n">
+      <c r="K33" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P33" s="6" t="n">
@@ -4056,69 +4044,69 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Alien_seed6000_O</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>jazjrjus</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="K34" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O34" s="4" t="n">
+      <c r="K34" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O34" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P34" s="6" t="n">
@@ -4126,69 +4114,69 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed6000_O</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>1k1plu0t</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="K35" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O35" s="4" t="n">
+      <c r="K35" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O35" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P35" s="6" t="n">
@@ -4196,69 +4184,69 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6000_O</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>s7kzk78g</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K36" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O36" s="4" t="n">
+      <c r="K36" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P36" s="6" t="n">
@@ -4266,69 +4254,69 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed6010_O</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>nxxmc2a8</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K37" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O37" s="4" t="n">
+      <c r="K37" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P37" s="6" t="n">
@@ -4336,69 +4324,69 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2000_X</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>gpz37fx4</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>224.50</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K38" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O38" s="4" t="n">
+      <c r="K38" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P38" s="6" t="n">
@@ -4406,69 +4394,69 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2010_X</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>uqrdvt6u</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>116.00</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>-0.02</t>
         </is>
       </c>
-      <c r="K39" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O39" s="4" t="n">
+      <c r="K39" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P39" s="6" t="n">
@@ -4476,69 +4464,69 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed710_X</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>66c4h08p</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>480.00</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="K40" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O40" s="4" t="n">
+      <c r="K40" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O40" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P40" s="6" t="n">
@@ -4546,69 +4534,69 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2000_O</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>pg8ek0ba</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>136.50</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="K41" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O41" s="4" t="n">
+      <c r="K41" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O41" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P41" s="6" t="n">
@@ -4616,69 +4604,69 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed710_X</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>ti91iyzh</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>9400.00</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="K42" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O42" s="4" t="n">
+      <c r="K42" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O42" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P42" s="6" t="n">
@@ -4686,69 +4674,69 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Qbert_seed710_O</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>a54n9otf</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Qbert</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>810.00</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="K43" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O43" s="4" t="n">
+      <c r="K43" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O43" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P43" s="6" t="n">
@@ -4756,61 +4744,61 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BankHeist_seed6000_X</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>z0jszbje</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>crashed</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O44" s="4" t="n">
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O44" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P44" s="6" t="n">
@@ -4818,69 +4806,69 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BattleZone_seed710_O</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>d1xbki7b</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>BattleZone</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>13600.00</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="K45" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O45" s="4" t="n">
+      <c r="K45" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O45" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P45" s="6" t="n">
@@ -4888,69 +4876,69 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_DemonAttack_seed2010_O</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>mgo4pji4</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>DemonAttack</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>131.50</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="K46" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O46" s="4" t="n">
+      <c r="K46" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O46" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P46" s="6" t="n">
@@ -4958,61 +4946,61 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_BankHeist_seed6010_X</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>4b4w07hb</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>crashed</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>BankHeist</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O47" s="4" t="n">
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O47" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P47" s="6" t="n">
@@ -5020,69 +5008,69 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6000_X</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>8am80ulg</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>7.77</t>
         </is>
       </c>
-      <c r="K48" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O48" s="4" t="n">
+      <c r="K48" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O48" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P48" s="6" t="n">
@@ -5090,69 +5078,69 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6010_X</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>ygndqe22</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>6.17</t>
         </is>
       </c>
-      <c r="K49" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O49" s="4" t="n">
+      <c r="K49" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O49" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P49" s="6" t="n">
@@ -5160,69 +5148,69 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed710_X</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>z767yjw0</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>6669.00</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="K50" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O50" s="4" t="n">
+      <c r="K50" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O50" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P50" s="6" t="n">
@@ -5230,69 +5218,69 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed710_X</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>28777040</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>1450.00</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O51" s="4" t="n">
+      <c r="K51" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O51" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P51" s="6" t="n">
@@ -5300,69 +5288,69 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed710_O</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>mbjmpmf5</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>4831.00</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O52" s="4" t="n">
+      <c r="K52" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O52" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P52" s="6" t="n">
@@ -5370,69 +5358,69 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6000_O</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>efjroqcm</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>8.22</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O53" s="4" t="n">
+      <c r="K53" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O53" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P53" s="6" t="n">
@@ -5440,69 +5428,69 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_ChopperCommand_seed710_O</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>25ay75ia</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>ChopperCommand</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>1350.00</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O54" s="4" t="n">
+      <c r="K54" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O54" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P54" s="6" t="n">
@@ -5510,69 +5498,69 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Boxing_seed6010_O</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>3b60h9wf</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>4.52</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O55" s="4" t="n">
+      <c r="K55" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O55" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P55" s="6" t="n">
@@ -5580,69 +5568,69 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6000_X</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>471e46mi</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="K56" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O56" s="4" t="n">
+      <c r="K56" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O56" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P56" s="6" t="n">
@@ -5650,69 +5638,69 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed3710_O</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>ycm22u8x</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="K57" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O57" s="4" t="n">
+      <c r="K57" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O57" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P57" s="6" t="n">
@@ -5720,69 +5708,69 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6010_X</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>nn7colrf</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="K58" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O58" s="4" t="n">
+      <c r="K58" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O58" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P58" s="6" t="n">
@@ -5790,69 +5778,69 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed710_X</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>udojzqq3</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>485.00</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="K59" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O59" s="4" t="n">
+      <c r="K59" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O59" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P59" s="6" t="n">
@@ -5860,69 +5848,69 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Hero_seed2000_X</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>zhmjfyq2</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>7552.00</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="K60" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O60" s="4" t="n">
+      <c r="K60" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O60" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P60" s="6" t="n">
@@ -5930,69 +5918,69 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed710_O</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>vx1geb4a</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>445.00</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="K61" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O61" s="4" t="n">
+      <c r="K61" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O61" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P61" s="6" t="n">
@@ -6000,565 +5988,629 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6000_O</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>wk800gq1</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
-      <c r="K62" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N62" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O62" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P62" s="8" t="n">
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P62" s="6" t="n">
         <v>46279.76197916667</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed6010_O</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>17rcltnt</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N63" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O63" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P63" s="8" t="n">
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>17.20</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P63" s="6" t="n">
         <v>46279.82975694445</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Hero_seed2010_X</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>b5j43zxs</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O64" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P64" s="8" t="n">
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>7510.00</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P64" s="6" t="n">
         <v>46279.83283564815</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_CrazyClimber_seed6000_X</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>sx1arxkl</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>CrazyClimber</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N65" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O65" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P65" s="8" t="n">
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>66980.00</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P65" s="6" t="n">
         <v>46279.86658564815</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Jamesbond_seed3710_O</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>4k7l8t8l</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Jamesbond</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-      <c r="K66" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M66" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N66" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O66" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P66" s="8" t="n">
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>605.00</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P66" s="6" t="n">
         <v>46279.86854166666</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Hero_seed2000_O</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>sg87sqnn</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N67" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O67" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P67" s="8" t="n">
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>7564.00</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P67" s="6" t="n">
         <v>46279.88961805555</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_CrazyClimber_seed6010_X</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>nuhliwrg</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>CrazyClimber</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr"/>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M68" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N68" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O68" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P68" s="8" t="n">
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>82640.00</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P68" s="6" t="n">
         <v>46279.92807870371</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_KungFuMaster_seed710_X</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>8x4uybyx</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>KungFuMaster</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N69" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O69" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P69" s="8" t="n">
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>20980.00</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P69" s="6" t="n">
         <v>46279.95943287037</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_KungFuMaster_seed710_O</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>60mawi6e</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>finished</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>KungFuMaster</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>17320.00</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="K70" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O70" s="4" t="n">
+      <c r="K70" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O70" s="3" t="n">
         <v>0.0625</v>
       </c>
       <c r="P70" s="6" t="n">
@@ -6566,64 +6618,72 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_CrazyClimber_seed6000_O</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>tbv6brxu</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>CrazyClimber</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr"/>
-      <c r="J71" s="7" t="inlineStr"/>
-      <c r="K71" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N71" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O71" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P71" s="8" t="n">
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>77110.00</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P71" s="6" t="n">
         <v>46280.04559027778</v>
       </c>
     </row>
@@ -6690,138 +6750,154 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Gopher_seed6000_Both</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>afcawwxy</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Gopher</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-      <c r="K73" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N73" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O73" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P73" s="8" t="n">
-        <v>46280.10148148148</v>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>fgvceo4q</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>71030.00</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P73" s="6" t="n">
+        <v>46280.10788194444</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_CrazyClimber_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>fgvceo4q</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>CrazyClimber</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2jzlrkza</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-      <c r="K74" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N74" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O74" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P74" s="8" t="n">
-        <v>46280.10788194444</v>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>1169.00</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P74" s="6" t="n">
+        <v>46280.1452199074</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Alien_seed3710_O</t>
+          <t>Mamba2_AC_RoadRunner_seed6000_O</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>2jzlrkza</t>
+          <t>rsx2aezz</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -6841,11 +6917,11 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Alien</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="G75" s="7" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -6872,80 +6948,88 @@
         <v>0.0625</v>
       </c>
       <c r="P75" s="8" t="n">
-        <v>46280.1452199074</v>
+        <v>46280.19780092593</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Alien_seed710_Both</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>tx3sbd42</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>f9y9q608</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
-        <v>710</v>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
+      <c r="G76" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N76" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O76" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P76" s="8" t="n">
-        <v>46280.16856481481</v>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>1376.00</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P76" s="6" t="n">
+        <v>46280.24451388889</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_RoadRunner_seed6000_O</t>
+          <t>Mamba2_AC_Alien_seed710_O</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>rsx2aezz</t>
+          <t>316d6dg5</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -6965,11 +7049,11 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Alien</t>
         </is>
       </c>
       <c r="G77" s="7" t="n">
-        <v>6000</v>
+        <v>710</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -6996,18 +7080,18 @@
         <v>0.0625</v>
       </c>
       <c r="P77" s="8" t="n">
-        <v>46280.19780092593</v>
+        <v>46280.24539351852</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Frostbite_seed3290_Both</t>
+          <t>Mamba2_AC_Assault_seed6020_Both</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>3darugr1</t>
+          <t>n1hjnzlz</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -7027,11 +7111,11 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G78" s="7" t="n">
-        <v>3290</v>
+        <v>6020</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -7058,88 +7142,80 @@
         <v>0.0625</v>
       </c>
       <c r="P78" s="8" t="n">
-        <v>46280.2187962963</v>
+        <v>46280.26670138889</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Alien_seed3710_X</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>f9y9q608</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Alien</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>1376.00</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P79" s="6" t="n">
-        <v>46280.24451388889</v>
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed6020_Both</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>n1hjnzlz</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O79" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P79" s="8" t="n">
+        <v>46280.26670138889</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Alien_seed710_O</t>
+          <t>Mamba2_AC_Gopher_seed6000_O</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>316d6dg5</t>
+          <t>p85gt3g5</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -7159,11 +7235,11 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Alien</t>
+          <t>Gopher</t>
         </is>
       </c>
       <c r="G80" s="7" t="n">
-        <v>710</v>
+        <v>6000</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -7190,18 +7266,18 @@
         <v>0.0625</v>
       </c>
       <c r="P80" s="8" t="n">
-        <v>46280.24539351852</v>
+        <v>46280.27893518518</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Assault_seed6020_Both</t>
+          <t>Mamba2_AC_Asterix_seed2000_Both</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>n1hjnzlz</t>
+          <t>6rn1636n</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -7221,11 +7297,11 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Asterix</t>
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>6020</v>
+        <v>2000</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -7252,18 +7328,18 @@
         <v>0.0625</v>
       </c>
       <c r="P81" s="8" t="n">
-        <v>46280.26670138889</v>
+        <v>46280.29326388889</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Assault_seed6020_Both</t>
+          <t>Mamba2_AC_Asterix_seed2000_Both</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>n1hjnzlz</t>
+          <t>6rn1636n</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -7283,11 +7359,11 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Asterix</t>
         </is>
       </c>
       <c r="G82" s="7" t="n">
-        <v>6020</v>
+        <v>2000</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -7314,18 +7390,18 @@
         <v>0.0625</v>
       </c>
       <c r="P82" s="8" t="n">
-        <v>46280.26670138889</v>
+        <v>46280.29326388889</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Gopher_seed6000_O</t>
+          <t>Mamba2_AC_Frostbite_seed3290_O</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>p85gt3g5</t>
+          <t>bc75s840</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -7345,11 +7421,11 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="G83" s="7" t="n">
-        <v>6000</v>
+        <v>3290</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -7376,18 +7452,18 @@
         <v>0.0625</v>
       </c>
       <c r="P83" s="8" t="n">
-        <v>46280.27893518518</v>
+        <v>46280.31445601852</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>6rn1636n</t>
+          <t>xabv161o</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -7407,11 +7483,11 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Asterix</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="G84" s="7" t="n">
-        <v>2000</v>
+        <v>3710</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -7438,18 +7514,18 @@
         <v>0.0625</v>
       </c>
       <c r="P84" s="8" t="n">
-        <v>46280.29326388889</v>
+        <v>46280.32222222222</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>6rn1636n</t>
+          <t>xabv161o</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -7469,11 +7545,11 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Asterix</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="G85" s="7" t="n">
-        <v>2000</v>
+        <v>3710</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -7500,18 +7576,18 @@
         <v>0.0625</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>46280.29326388889</v>
+        <v>46280.32222222222</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Frostbite_seed3290_O</t>
+          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>bc75s840</t>
+          <t>r41a1emc</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -7531,15 +7607,15 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="G86" s="7" t="n">
-        <v>3290</v>
+        <v>6010</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr"/>
@@ -7562,18 +7638,18 @@
         <v>0.0625</v>
       </c>
       <c r="P86" s="8" t="n">
-        <v>46280.31445601852</v>
+        <v>46280.32361111111</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
+          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>xabv161o</t>
+          <t>r41a1emc</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -7593,11 +7669,11 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="G87" s="7" t="n">
-        <v>3710</v>
+        <v>6010</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -7624,192 +7700,6 @@
         <v>0.0625</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>46280.32222222222</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>xabv161o</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>KungFuMaster</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-      <c r="K88" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L88" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N88" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O88" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P88" s="8" t="n">
-        <v>46280.32222222222</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>r41a1emc</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>RoadRunner</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
-      <c r="K89" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N89" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O89" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P89" s="8" t="n">
-        <v>46280.32361111111</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>r41a1emc</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>RoadRunner</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr"/>
-      <c r="J90" s="7" t="inlineStr"/>
-      <c r="K90" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M90" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N90" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O90" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P90" s="8" t="n">
         <v>46280.32361111111</v>
       </c>
     </row>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>906.00</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
@@ -568,9 +572,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -671,11 +675,7 @@
           <t>336.00</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -721,12 +721,12 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
@@ -758,7 +758,11 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
@@ -1167,7 +1171,11 @@
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
@@ -1199,9 +1207,9 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2224.00</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1241,7 +1249,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
@@ -1269,9 +1281,9 @@
       </c>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>3132.00</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
@@ -1322,9 +1334,9 @@
           <t>7564.00</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>3155.00</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -1484,9 +1496,9 @@
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>23080.00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -1496,7 +1508,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1506,11 +1518,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
@@ -1520,7 +1528,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1528,13 +1536,13 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
@@ -1544,7 +1552,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1552,19 +1560,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>480.00</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>787.50</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
@@ -1572,7 +1576,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1580,19 +1584,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>810.00</t>
-        </is>
-      </c>
+      <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>792.50</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1608,23 +1608,27 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>480.00</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>787.50</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1632,27 +1636,27 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>810.00</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>792.50</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1660,27 +1664,23 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>6669.00</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2654.00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1688,22 +1688,78 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>4831.00</t>
-        </is>
-      </c>
+      <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>6669.00</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>4831.00</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1716,7 +1772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6688,64 +6744,72 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Hero_seed2010_O</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>kzgxj2nm</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M72" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N72" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O72" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P72" s="8" t="n">
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>3155.00</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P72" s="6" t="n">
         <v>46280.05359953704</v>
       </c>
     </row>
@@ -6890,64 +6954,72 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_RoadRunner_seed6000_O</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>rsx2aezz</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>RoadRunner</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N75" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O75" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P75" s="8" t="n">
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P75" s="6" t="n">
         <v>46280.19780092593</v>
       </c>
     </row>
@@ -7022,262 +7094,294 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Alien_seed710_O</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>316d6dg5</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Alien</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-      <c r="K77" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N77" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O77" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P77" s="8" t="n">
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>1283.00</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P77" s="6" t="n">
         <v>46280.24539351852</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Assault_seed6020_Both</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>n1hjnzlz</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>6020</v>
-      </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>p85gt3g5</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>3132.00</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P78" s="6" t="n">
+        <v>46280.27893518518</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed3290_O</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>bc75s840</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>2224.00</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P79" s="6" t="n">
+        <v>46280.31445601852</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed710_X</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>40bq2gif</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-      <c r="K78" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N78" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O78" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P78" s="8" t="n">
-        <v>46280.26670138889</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Assault_seed6020_Both</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>n1hjnzlz</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>6020</v>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L79" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N79" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O79" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P79" s="8" t="n">
-        <v>46280.26670138889</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Gopher_seed6000_O</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>p85gt3g5</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Gopher</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr"/>
-      <c r="J80" s="7" t="inlineStr"/>
-      <c r="K80" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N80" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O80" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P80" s="8" t="n">
-        <v>46280.27893518518</v>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>906.00</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P80" s="6" t="n">
+        <v>46280.35971064815</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+          <t>Mamba2_AC_Asterix_seed2010_Both</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>6rn1636n</t>
+          <t>19rblpab</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -7301,7 +7405,7 @@
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -7328,18 +7432,18 @@
         <v>0.0625</v>
       </c>
       <c r="P81" s="8" t="n">
-        <v>46280.29326388889</v>
+        <v>46280.39324074074</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2000_Both</t>
+          <t>Mamba2_AC_Asterix_seed2010_Both</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>6rn1636n</t>
+          <t>19rblpab</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -7363,7 +7467,7 @@
         </is>
       </c>
       <c r="G82" s="7" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -7390,80 +7494,88 @@
         <v>0.0625</v>
       </c>
       <c r="P82" s="8" t="n">
-        <v>46280.29326388889</v>
+        <v>46280.39324074074</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Frostbite_seed3290_O</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>bc75s840</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="n">
-        <v>3290</v>
-      </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>hf7phu9g</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="7" t="inlineStr"/>
-      <c r="K83" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M83" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N83" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O83" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P83" s="8" t="n">
-        <v>46280.31445601852</v>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>23080.00</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v>46280.39851851852</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
+          <t>Mamba2_AC_RoadRunner_seed6000_X</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>xabv161o</t>
+          <t>aju4cos2</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -7483,11 +7595,11 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="G84" s="7" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -7514,18 +7626,18 @@
         <v>0.0625</v>
       </c>
       <c r="P84" s="8" t="n">
-        <v>46280.32222222222</v>
+        <v>46280.41853009259</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_Both</t>
+          <t>Mamba2_AC_Assault_seed6020_O</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>xabv161o</t>
+          <t>kleh8r1x</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -7545,11 +7657,11 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G85" s="7" t="n">
-        <v>3710</v>
+        <v>6020</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -7576,18 +7688,18 @@
         <v>0.0625</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>46280.32222222222</v>
+        <v>46280.44364583334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
+          <t>Mamba2_AC_Frostbite_seed3290_X</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>r41a1emc</t>
+          <t>9z12wlax</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -7607,11 +7719,11 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="G86" s="7" t="n">
-        <v>6010</v>
+        <v>3290</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -7638,18 +7750,18 @@
         <v>0.0625</v>
       </c>
       <c r="P86" s="8" t="n">
-        <v>46280.32361111111</v>
+        <v>46280.4897337963</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_Both</t>
+          <t>Mamba2_AC_RoadRunner_seed6010_O</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>r41a1emc</t>
+          <t>hsgssals</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -7700,7 +7812,255 @@
         <v>0.0625</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>46280.32361111111</v>
+        <v>46280.50119212963</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>v0ocexdz</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O88" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P88" s="8" t="n">
+        <v>46280.5120949074</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed710_O</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>fbe03nf8</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O89" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P89" s="8" t="n">
+        <v>46280.51324074074</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1ebddl68</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O90" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P90" s="8" t="n">
+        <v>46280.52025462963</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>tc8yw820</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M91" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O91" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P91" s="8" t="n">
+        <v>46280.54377314815</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>608.00</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1376.00</t>
@@ -579,7 +583,11 @@
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>705.00</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1169.00</t>
@@ -632,10 +640,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>98.00</t>
@@ -675,7 +691,11 @@
           <t>336.00</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>521.80</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -703,9 +723,9 @@
           <t>630.00</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>428.40</t>
         </is>
       </c>
     </row>
@@ -721,7 +741,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1585.00</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
@@ -753,14 +777,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1880.00</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1250.00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -813,8 +837,16 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1171,9 +1203,9 @@
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1952.00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1249,9 +1281,9 @@
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2150.00</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1404,7 +1436,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1413,22 +1445,22 @@
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>9836.00</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1437,22 +1469,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>8737.00</t>
-        </is>
-      </c>
+      <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Krull</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1460,27 +1492,23 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>20980.00</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>9836.00</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Krull</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1488,27 +1516,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>17320.00</t>
-        </is>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>23080.00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>8737.00</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1516,11 +1540,19 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>20980.00</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>19020.00</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
@@ -1528,7 +1560,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1536,15 +1568,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>17320.00</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>23080.00</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
@@ -1552,7 +1588,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1560,15 +1596,19 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>4188.00</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1749.00</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
@@ -1576,7 +1616,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1584,15 +1624,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>4075.00</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1885.00</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
@@ -1600,7 +1644,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1608,19 +1652,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>480.00</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>787.50</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
@@ -1628,7 +1668,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1636,19 +1676,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>810.00</t>
-        </is>
-      </c>
+      <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>792.50</t>
-        </is>
-      </c>
+      <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr"/>
@@ -1656,7 +1692,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1664,23 +1700,27 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1688,27 +1728,27 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>-80.00</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1718,7 +1758,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6669.00</t>
+          <t>480.00</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1726,7 +1766,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2654.00</t>
+          <t>787.50</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -1736,7 +1776,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1746,7 +1786,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>4831.00</t>
+          <t>810.00</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1754,12 +1794,176 @@
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5486.00</t>
+          <t>792.50</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>7030.00</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>7860.00</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>8520.00</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>8500.00</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>474.00</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>6669.00</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>4831.00</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>5486.00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1772,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7374,138 +7578,154 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Asterix_seed2010_Both</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>19rblpab</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Asterix</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>2010</v>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>hf7phu9g</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>23080.00</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P81" s="6" t="n">
+        <v>46280.39851851852</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>aju4cos2</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-      <c r="K81" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L81" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N81" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O81" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P81" s="8" t="n">
-        <v>46280.39324074074</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Asterix_seed2010_Both</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>19rblpab</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>Asterix</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>2010</v>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr"/>
-      <c r="J82" s="7" t="inlineStr"/>
-      <c r="K82" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N82" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O82" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P82" s="8" t="n">
-        <v>46280.39324074074</v>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>7030.00</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v>46280.41853009259</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_O</t>
+          <t>Mamba2_AC_Assault_seed6020_O</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>hf7phu9g</t>
+          <t>kleh8r1x</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -7525,542 +7745,1996 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>428.40</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v>46280.44364583334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed3290_X</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>9z12wlax</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>1952.00</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P84" s="6" t="n">
+        <v>46280.4897337963</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>hsgssals</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>8500.00</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P85" s="6" t="n">
+        <v>46280.50119212963</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>v0ocexdz</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>1880.00</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P86" s="6" t="n">
+        <v>46280.5120949074</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed710_O</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>fbe03nf8</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>4075.00</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P87" s="6" t="n">
+        <v>46280.51324074074</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>1ebddl68</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
           <t>KungFuMaster</t>
         </is>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="G88" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>19020.00</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P88" s="6" t="n">
+        <v>46280.52025462963</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>tc8yw820</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>2150.00</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P89" s="6" t="n">
+        <v>46280.54377314815</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2010_O</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>zvz2cic8</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>23080.00</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N83" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P83" s="6" t="n">
-        <v>46280.39851851852</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_RoadRunner_seed6000_X</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>aju4cos2</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P90" s="6" t="n">
+        <v>46280.59976851852</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed710_X</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>gfazd0dc</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>4188.00</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v>46280.61607638889</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>kyj0dljo</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>1885.00</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P92" s="6" t="n">
+        <v>46280.67431712963</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3290_O</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>yyoxlhkt</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>705.00</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P93" s="6" t="n">
+        <v>46280.68962962963</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed6020_X</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>wetpo7g0</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>521.80</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P94" s="6" t="n">
+        <v>46280.71888888889</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_RoadRunner_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>i24w1ijj</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>RoadRunner</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>7860.00</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P95" s="6" t="n">
+        <v>46280.74344907407</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed710_O</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>iudb0o6o</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>-80.00</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P96" s="6" t="n">
+        <v>46280.77001157407</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>5b54zq6r</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>474.00</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P97" s="6" t="n">
+        <v>46280.77847222222</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>6y2gnwcm</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>1749.00</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P98" s="6" t="n">
+        <v>46280.79672453704</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Alien_seed3290_X</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>hgh8q61o</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>608.00</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P99" s="6" t="n">
+        <v>46280.84616898148</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed710_X</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>lffv2me9</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P100" s="6" t="n">
+        <v>46280.85199074074</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>5gwmyiis</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>1585.00</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P101" s="6" t="n">
+        <v>46280.86395833334</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>up7lur50</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>RoadRunner</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="n">
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N102" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O102" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P102" s="8" t="n">
+        <v>46280.89765046296</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>mw672cve</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O103" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P103" s="8" t="n">
+        <v>46280.90140046296</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>e1fce6nn</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N104" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O104" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P104" s="8" t="n">
+        <v>46280.92248842592</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Asterix_seed2010_X</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>bbga41u3</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Asterix</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="7" t="inlineStr"/>
-      <c r="K84" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N84" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O84" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P84" s="8" t="n">
-        <v>46280.41853009259</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Assault_seed6020_O</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>kleh8r1x</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr"/>
+      <c r="J105" s="7" t="inlineStr"/>
+      <c r="K105" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N105" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O105" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P105" s="8" t="n">
+        <v>46280.94780092593</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>qxxqmm0y</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P106" s="6" t="n">
+        <v>46280.95078703704</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed710_O</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>3jry8ac9</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="n">
-        <v>6020</v>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
-      <c r="K85" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M85" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N85" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O85" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P85" s="8" t="n">
-        <v>46280.44364583334</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Frostbite_seed3290_X</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>9z12wlax</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr"/>
+      <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M107" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N107" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O107" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P107" s="8" t="n">
+        <v>46281.00620370371</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed3290_O</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>mcs6bbdf</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="n">
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n">
         <v>3290</v>
       </c>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="inlineStr"/>
+      <c r="J108" s="7" t="inlineStr"/>
+      <c r="K108" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O108" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P108" s="8" t="n">
+        <v>46281.03773148148</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>qsi9gets</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr"/>
-      <c r="J86" s="7" t="inlineStr"/>
-      <c r="K86" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M86" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N86" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O86" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P86" s="8" t="n">
-        <v>46280.4897337963</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>hsgssals</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="I109" s="7" t="inlineStr"/>
+      <c r="J109" s="7" t="inlineStr"/>
+      <c r="K109" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O109" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P109" s="8" t="n">
+        <v>46281.04005787037</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>37vv5lqr</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>RoadRunner</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="inlineStr"/>
+      <c r="J110" s="7" t="inlineStr"/>
+      <c r="K110" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N110" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O110" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P110" s="8" t="n">
+        <v>46281.05363425926</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>wsddwdqf</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr"/>
+      <c r="J111" s="7" t="inlineStr"/>
+      <c r="K111" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N111" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O111" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P111" s="8" t="n">
+        <v>46281.06334490741</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>wsddwdqf</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-      <c r="K87" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M87" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N87" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O87" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P87" s="8" t="n">
-        <v>46280.50119212963</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Asterix_seed2000_O</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>v0ocexdz</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Asterix</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-      <c r="K88" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L88" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N88" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O88" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P88" s="8" t="n">
-        <v>46280.5120949074</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_MsPacman_seed710_O</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>fbe03nf8</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>MsPacman</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>710</v>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
-      <c r="K89" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N89" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O89" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P89" s="8" t="n">
-        <v>46280.51324074074</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_KungFuMaster_seed3710_X</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>1ebddl68</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>KungFuMaster</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr"/>
-      <c r="J90" s="7" t="inlineStr"/>
-      <c r="K90" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M90" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N90" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O90" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P90" s="8" t="n">
-        <v>46280.52025462963</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Gopher_seed6000_X</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>tc8yw820</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Gopher</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="7" t="inlineStr"/>
-      <c r="K91" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M91" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N91" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O91" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P91" s="8" t="n">
-        <v>46280.54377314815</v>
+      <c r="I112" s="7" t="inlineStr"/>
+      <c r="J112" s="7" t="inlineStr"/>
+      <c r="K112" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M112" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N112" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O112" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P112" s="8" t="n">
+        <v>46281.06334490741</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -612,10 +612,18 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>100.90</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92.60</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
@@ -640,16 +648,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>118.30</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>139.80</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -746,9 +754,9 @@
           <t>1585.00</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -873,7 +881,11 @@
           <t>13500.00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
     </row>
@@ -901,7 +913,11 @@
           <t>6200.00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
     </row>
@@ -916,7 +932,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
@@ -944,11 +964,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>56.40</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>98.60</t>
@@ -1153,7 +1181,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
     </row>
@@ -1181,7 +1213,11 @@
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
     </row>
@@ -1445,11 +1481,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1474,7 +1506,11 @@
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
@@ -1708,9 +1744,9 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -1873,12 +1909,16 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>432.00</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1902,9 +1942,9 @@
           <t>474.00</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>458.00</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -1976,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9110,64 +9150,72 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Seaquest_seed6010_O</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>mw672cve</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>Seaquest</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="G103" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr"/>
-      <c r="K103" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M103" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N103" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O103" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P103" s="8" t="n">
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>458.00</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P103" s="6" t="n">
         <v>46280.90140046296</v>
       </c>
     </row>
@@ -9234,64 +9282,72 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Asterix_seed2010_X</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>bbga41u3</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>Asterix</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G105" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr"/>
-      <c r="J105" s="7" t="inlineStr"/>
-      <c r="K105" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M105" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N105" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O105" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P105" s="8" t="n">
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>1495.00</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P105" s="6" t="n">
         <v>46280.94780092593</v>
       </c>
     </row>
@@ -9366,324 +9422,364 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed710_O</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>3jry8ac9</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="G107" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="7" t="inlineStr"/>
-      <c r="K107" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M107" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N107" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O107" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P107" s="8" t="n">
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>118.30</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P107" s="6" t="n">
         <v>46281.00620370371</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Amidar_seed3290_O</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>mcs6bbdf</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="3" t="n">
         <v>3290</v>
       </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr"/>
-      <c r="J108" s="7" t="inlineStr"/>
-      <c r="K108" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N108" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O108" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P108" s="8" t="n">
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>139.80</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P108" s="6" t="n">
         <v>46281.03773148148</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_PrivateEye_seed3710_X</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>qsi9gets</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>PrivateEye</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr"/>
-      <c r="J109" s="7" t="inlineStr"/>
-      <c r="K109" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N109" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O109" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P109" s="8" t="n">
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P109" s="6" t="n">
         <v>46281.04005787037</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Seaquest_seed6000_X</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>37vv5lqr</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>Seaquest</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I110" s="7" t="inlineStr"/>
-      <c r="J110" s="7" t="inlineStr"/>
-      <c r="K110" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M110" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N110" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O110" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P110" s="8" t="n">
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>432.00</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P110" s="6" t="n">
         <v>46281.05363425926</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Kangaroo_seed2000_Both</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>wsddwdqf</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>Kangaroo</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed710_X</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>q2g9rkmh</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr"/>
-      <c r="J111" s="7" t="inlineStr"/>
-      <c r="K111" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M111" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N111" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O111" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P111" s="8" t="n">
-        <v>46281.06334490741</v>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>100.90</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P111" s="6" t="n">
+        <v>46281.12444444445</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Kangaroo_seed2000_Both</t>
+          <t>Mamba2_AC_Seaquest_seed6010_X</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>wsddwdqf</t>
+          <t>a1jjhzhf</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -9703,15 +9799,15 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>Seaquest</t>
         </is>
       </c>
       <c r="G112" s="7" t="n">
-        <v>2000</v>
+        <v>6010</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr"/>
@@ -9734,7 +9830,643 @@
         <v>0.0625</v>
       </c>
       <c r="P112" s="8" t="n">
-        <v>46281.06334490741</v>
+        <v>46281.17542824074</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_O</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>u5ocyhhy</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>56.40</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P113" s="6" t="n">
+        <v>46281.1941087963</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed3290_X</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>ijhzsqmr</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>92.60</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P114" s="6" t="n">
+        <v>46281.23145833334</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed6000_Both</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>tqpeo48v</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="7" t="inlineStr"/>
+      <c r="K115" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M115" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N115" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O115" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P115" s="8" t="n">
+        <v>46281.23458333333</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed6000_Both</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>tqpeo48v</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I116" s="7" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M116" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N116" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O116" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P116" s="8" t="n">
+        <v>46281.23458333333</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>d7qpd2cf</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="inlineStr"/>
+      <c r="J117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N117" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O117" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P117" s="8" t="n">
+        <v>46281.26112268519</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>09cqwkf7</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="inlineStr"/>
+      <c r="J118" s="7" t="inlineStr"/>
+      <c r="K118" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M118" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N118" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O118" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P118" s="8" t="n">
+        <v>46281.27840277777</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6000_Both</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>sc4m9378</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="inlineStr"/>
+      <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M119" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N119" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O119" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P119" s="8" t="n">
+        <v>46281.30539351852</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6000_Both</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>sc4m9378</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="inlineStr"/>
+      <c r="J120" s="7" t="inlineStr"/>
+      <c r="K120" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M120" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N120" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O120" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P120" s="8" t="n">
+        <v>46281.30539351852</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_X</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>kqakm6xy</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="inlineStr"/>
+      <c r="J121" s="7" t="inlineStr"/>
+      <c r="K121" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N121" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O121" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P121" s="8" t="n">
+        <v>46281.32584490741</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed2010_O</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>a0pp1fht</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="inlineStr"/>
+      <c r="J122" s="7" t="inlineStr"/>
+      <c r="K122" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M122" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N122" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O122" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P122" s="8" t="n">
+        <v>46281.34596064815</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -491,6 +491,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,24 +509,27 @@
         <v>710</v>
       </c>
       <c r="D1" s="1" t="n">
+        <v>1710</v>
+      </c>
+      <c r="E1" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>3290</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>6010</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>6020</v>
       </c>
     </row>
@@ -547,23 +551,24 @@
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>608.00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1376.00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -583,23 +588,24 @@
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>705.00</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1169.00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -614,28 +620,29 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>100.90</t>
+          <t>230.30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>92.60</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -650,28 +657,29 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>118.30</t>
+          <t>178.40</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>139.80</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -689,17 +697,18 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>521.80</t>
         </is>
@@ -718,20 +727,25 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>428.40</t>
         </is>
@@ -749,29 +763,30 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1585.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1495.00</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -785,29 +800,30 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>1880.00</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -828,6 +844,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -845,17 +862,18 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>268.00</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>324.00</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -876,18 +894,19 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -908,18 +927,19 @@
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>4900.00</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -932,26 +952,27 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>27.60</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -966,28 +987,29 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>56.40</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1005,17 +1027,18 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1033,17 +1056,18 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>17.20</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1064,14 +1088,15 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1092,14 +1117,15 @@
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1117,17 +1143,18 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>66980.00</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>82640.00</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1145,17 +1172,18 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>77110.00</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>71030.00</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1169,25 +1197,30 @@
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>224.50</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>116.00</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>153.50</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>155.50</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1201,25 +1234,30 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>136.50</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>131.50</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>211.50</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1237,25 +1275,30 @@
           <t>260.00</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1952.00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1273,25 +1316,30 @@
           <t>250.00</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>2224.00</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1305,25 +1353,30 @@
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2198.00</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1016.00</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2150.00</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2888.00</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1337,25 +1390,30 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>1082.00</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>3132.00</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1369,21 +1427,26 @@
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>7552.00</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>7510.00</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1397,21 +1460,30 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>7564.00</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>3155.00</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1432,14 +1504,15 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1460,14 +1533,15 @@
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>605.00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1482,12 +1556,21 @@
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1600.00</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1501,21 +1584,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1533,13 +1617,14 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1557,13 +1642,14 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1584,14 +1670,15 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>19020.00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1610,16 +1697,21 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>23080.00</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1640,14 +1732,15 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>1749.00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1548.00</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1668,14 +1761,15 @@
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>1885.00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>1847.00</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1690,16 +1784,21 @@
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1714,16 +1813,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1744,14 +1852,15 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1766,20 +1875,21 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>-80.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>-219.40</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1800,14 +1910,15 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1828,14 +1939,15 @@
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1853,17 +1965,18 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>7030.00</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>7860.00</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1881,17 +1994,18 @@
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>8520.00</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>8500.00</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1909,17 +2023,18 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>432.00</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>534.00</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1937,17 +2052,18 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>474.00</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>458.00</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1968,14 +2084,15 @@
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1996,14 +2113,15 @@
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2016,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8390,12 +8508,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_MsPacman_seed3710_O</t>
+          <t>Mamba2_AC_Alien_seed3290_O</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>kyj0dljo</t>
+          <t>yyoxlhkt</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -8415,11 +8533,11 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>Alien</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3710</v>
+        <v>3290</v>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
@@ -8428,12 +8546,12 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>1885.00</t>
+          <t>705.00</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="K92" s="3" t="n">
@@ -8454,18 +8572,18 @@
         <v>0.0625</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>46280.67431712963</v>
+        <v>46280.68962962963</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Alien_seed3290_O</t>
+          <t>Mamba2_AC_Assault_seed6020_X</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>yyoxlhkt</t>
+          <t>wetpo7g0</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -8485,25 +8603,25 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Alien</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>3290</v>
+        <v>6020</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>705.00</t>
+          <t>521.80</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K93" s="3" t="n">
@@ -8524,18 +8642,18 @@
         <v>0.0625</v>
       </c>
       <c r="P93" s="6" t="n">
-        <v>46280.68962962963</v>
+        <v>46280.71888888889</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Assault_seed6020_X</t>
+          <t>Mamba2_AC_RoadRunner_seed6010_X</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>wetpo7g0</t>
+          <t>i24w1ijj</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -8555,11 +8673,11 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
@@ -8568,12 +8686,12 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>521.80</t>
+          <t>7860.00</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="K94" s="3" t="n">
@@ -8594,18 +8712,18 @@
         <v>0.0625</v>
       </c>
       <c r="P94" s="6" t="n">
-        <v>46280.71888888889</v>
+        <v>46280.74344907407</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_RoadRunner_seed6010_X</t>
+          <t>Mamba2_AC_Seaquest_seed6000_O</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>i24w1ijj</t>
+          <t>5b54zq6r</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -8625,25 +8743,25 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Seaquest</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>7860.00</t>
+          <t>474.00</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K95" s="3" t="n">
@@ -8664,18 +8782,18 @@
         <v>0.0625</v>
       </c>
       <c r="P95" s="6" t="n">
-        <v>46280.74344907407</v>
+        <v>46280.77847222222</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed710_O</t>
+          <t>Mamba2_AC_Alien_seed3290_X</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>iudb0o6o</t>
+          <t>hgh8q61o</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -8695,25 +8813,25 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Alien</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>710</v>
+        <v>3290</v>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>-80.00</t>
+          <t>608.00</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
@@ -8734,18 +8852,18 @@
         <v>0.0625</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>46280.77001157407</v>
+        <v>46280.84616898148</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Seaquest_seed6000_O</t>
+          <t>Mamba2_AC_Asterix_seed2000_X</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>5b54zq6r</t>
+          <t>5gwmyiis</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -8765,25 +8883,25 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Seaquest</t>
+          <t>Asterix</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>474.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="K97" s="3" t="n">
@@ -8804,23 +8922,23 @@
         <v>0.0625</v>
       </c>
       <c r="P97" s="6" t="n">
-        <v>46280.77847222222</v>
+        <v>46280.86395833334</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_MsPacman_seed3710_X</t>
+          <t>Mamba2_AC_BankHeist_seed6000_O</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>6y2gnwcm</t>
+          <t>up7lur50</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -8835,25 +8953,25 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>BankHeist</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>1749.00</t>
+          <t>268.00</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K98" s="3" t="n">
@@ -8874,18 +8992,18 @@
         <v>0.0625</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>46280.79672453704</v>
+        <v>46280.89765046296</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Alien_seed3290_X</t>
+          <t>Mamba2_AC_Seaquest_seed6010_O</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>hgh8q61o</t>
+          <t>mw672cve</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -8905,25 +9023,25 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Alien</t>
+          <t>Seaquest</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3290</v>
+        <v>6010</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>608.00</t>
+          <t>458.00</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K99" s="3" t="n">
@@ -8944,23 +9062,23 @@
         <v>0.0625</v>
       </c>
       <c r="P99" s="6" t="n">
-        <v>46280.84616898148</v>
+        <v>46280.90140046296</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed710_X</t>
+          <t>Mamba2_AC_BankHeist_seed6010_O</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>lffv2me9</t>
+          <t>e1fce6nn</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -8975,25 +9093,25 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>BankHeist</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>710</v>
+        <v>6010</v>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>324.00</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="K100" s="3" t="n">
@@ -9014,18 +9132,18 @@
         <v>0.0625</v>
       </c>
       <c r="P100" s="6" t="n">
-        <v>46280.85199074074</v>
+        <v>46280.92248842592</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2000_X</t>
+          <t>Mamba2_AC_Asterix_seed2010_X</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>5gwmyiis</t>
+          <t>bbga41u3</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -9049,7 +9167,7 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -9058,12 +9176,12 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K101" s="3" t="n">
@@ -9084,80 +9202,88 @@
         <v>0.0625</v>
       </c>
       <c r="P101" s="6" t="n">
-        <v>46280.86395833334</v>
+        <v>46280.94780092593</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_BankHeist_seed6000_O</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>up7lur50</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>BankHeist</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed3290_O</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>mcs6bbdf</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
-      <c r="K102" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M102" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N102" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O102" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P102" s="8" t="n">
-        <v>46280.89765046296</v>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>139.80</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P102" s="6" t="n">
+        <v>46281.03773148148</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Seaquest_seed6010_O</t>
+          <t>Mamba2_AC_Seaquest_seed6000_X</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>mw672cve</t>
+          <t>37vv5lqr</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -9181,115 +9307,123 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>432.00</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P103" s="6" t="n">
+        <v>46281.05363425926</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>a1jjhzhf</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>458.00</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>534.00</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="K103" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N103" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O103" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P103" s="6" t="n">
-        <v>46280.90140046296</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_BankHeist_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>e1fce6nn</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>BankHeist</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr"/>
-      <c r="J104" s="7" t="inlineStr"/>
-      <c r="K104" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L104" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M104" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N104" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O104" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P104" s="8" t="n">
-        <v>46280.92248842592</v>
+      <c r="K104" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P104" s="6" t="n">
+        <v>46281.17542824074</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Asterix_seed2010_X</t>
+          <t>Mamba2_AC_Amidar_seed3290_X</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>bbga41u3</t>
+          <t>ijhzsqmr</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -9309,11 +9443,11 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Asterix</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2010</v>
+        <v>3290</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -9322,12 +9456,12 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>92.60</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="K105" s="3" t="n">
@@ -9348,18 +9482,18 @@
         <v>0.0625</v>
       </c>
       <c r="P105" s="6" t="n">
-        <v>46280.94780092593</v>
+        <v>46281.23145833334</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed3710_O</t>
+          <t>Mamba2_AC_Kangaroo_seed2000_O</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>qxxqmm0y</t>
+          <t>d7qpd2cf</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -9379,11 +9513,11 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>3710</v>
+        <v>2000</v>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
@@ -9392,12 +9526,12 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K106" s="3" t="n">
@@ -9418,18 +9552,18 @@
         <v>0.0625</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>46280.95078703704</v>
+        <v>46281.26112268519</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_O</t>
+          <t>Mamba2_AC_Kangaroo_seed2010_O</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>3jry8ac9</t>
+          <t>a0pp1fht</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -9449,11 +9583,11 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>710</v>
+        <v>2010</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -9462,12 +9596,12 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>118.30</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K107" s="3" t="n">
@@ -9488,18 +9622,18 @@
         <v>0.0625</v>
       </c>
       <c r="P107" s="6" t="n">
-        <v>46281.00620370371</v>
+        <v>46281.34596064815</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed3290_O</t>
+          <t>Mamba2_AC_Boxing_seed3710_X</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>mcs6bbdf</t>
+          <t>pdn4m7j2</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -9519,25 +9653,25 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Boxing</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>3290</v>
+        <v>3710</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>139.80</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K108" s="3" t="n">
@@ -9558,18 +9692,18 @@
         <v>0.0625</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>46281.03773148148</v>
+        <v>46281.40581018518</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
+          <t>Mamba2_AC_BattleZone_seed6000_O</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>qsi9gets</t>
+          <t>vh7yva6t</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -9589,25 +9723,25 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>BattleZone</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>4900.00</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="K109" s="3" t="n">
@@ -9628,18 +9762,18 @@
         <v>0.0625</v>
       </c>
       <c r="P109" s="6" t="n">
-        <v>46281.04005787037</v>
+        <v>46281.41318287037</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Seaquest_seed6000_X</t>
+          <t>Mamba2_AC_MsPacman_seed3710_O</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>37vv5lqr</t>
+          <t>76be4ipd</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -9659,25 +9793,25 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Seaquest</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>6000</v>
+        <v>3710</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>432.00</t>
+          <t>1847.00</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="K110" s="3" t="n">
@@ -9698,18 +9832,18 @@
         <v>0.0625</v>
       </c>
       <c r="P110" s="6" t="n">
-        <v>46281.05363425926</v>
+        <v>46281.47984953703</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_X</t>
+          <t>Mamba2_AC_DemonAttack_seed6000_O</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>q2g9rkmh</t>
+          <t>hcay6kcv</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -9729,119 +9863,127 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>DemonAttack</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>211.50</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P111" s="6" t="n">
+        <v>46281.48199074074</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed710_O</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>8nt4ru5n</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>100.90</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L111" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M111" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N111" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O111" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P111" s="6" t="n">
-        <v>46281.12444444445</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Seaquest_seed6010_X</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>a1jjhzhf</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>Seaquest</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H112" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I112" s="7" t="inlineStr"/>
-      <c r="J112" s="7" t="inlineStr"/>
-      <c r="K112" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M112" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N112" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O112" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P112" s="8" t="n">
-        <v>46281.17542824074</v>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P112" s="6" t="n">
+        <v>46281.55998842593</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed710_O</t>
+          <t>Mamba2_AC_Kangaroo_seed2000_X</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>u5ocyhhy</t>
+          <t>1iwdyhhb</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -9861,25 +10003,25 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Boxing</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>710</v>
+        <v>2000</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>56.40</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K113" s="3" t="n">
@@ -9900,18 +10042,18 @@
         <v>0.0625</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>46281.1941087963</v>
+        <v>46281.56878472222</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed3290_X</t>
+          <t>Mamba2_AC_BattleZone_seed6000_X</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ijhzsqmr</t>
+          <t>7i7irhf9</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -9931,542 +10073,1700 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P114" s="6" t="n">
+        <v>46281.60291666666</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>3dx0p15l</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>1548.00</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N115" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P115" s="6" t="n">
+        <v>46281.60375</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>qv6pgjpw</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N116" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P116" s="6" t="n">
+        <v>46281.61435185185</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed710_X</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>3ucr91hm</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N117" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O117" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P117" s="6" t="n">
+        <v>46281.64665509259</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed2010_X</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>5v6k3xw5</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>1600.00</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O118" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P118" s="6" t="n">
+        <v>46281.67173611111</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>4axihsuz</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>153.50</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P119" s="6" t="n">
+        <v>46281.72890046296</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>lncnpxxv</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>-219.40</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P120" s="6" t="n">
+        <v>46281.7578587963</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>vpvjr1ct</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>155.50</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N121" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P121" s="6" t="n">
+        <v>46281.78896990741</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed710_O</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>sqqttxrp</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
           <t>Amidar</t>
         </is>
       </c>
-      <c r="G114" s="3" t="n">
-        <v>3290</v>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="G122" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>178.40</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P122" s="6" t="n">
+        <v>46281.80134259259</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>5gfeyji8</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>92.60</t>
-        </is>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L114" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M114" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N114" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O114" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P114" s="6" t="n">
-        <v>46281.23145833334</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_BattleZone_seed6000_Both</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>tqpeo48v</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>2888.00</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P123" s="6" t="n">
+        <v>46281.80818287037</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>78620ail</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P124" s="6" t="n">
+        <v>46281.85913194445</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>umdwnyu2</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P125" s="6" t="n">
+        <v>46281.86515046296</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Amidar_seed710_X</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>2vvni7nk</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Amidar</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>230.30</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P126" s="6" t="n">
+        <v>46281.93247685185</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>liij2pbh</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>BattleZone</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="n">
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr"/>
+      <c r="J127" s="7" t="inlineStr"/>
+      <c r="K127" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M127" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N127" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O127" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P127" s="8" t="n">
+        <v>46281.96268518519</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>ong25zy1</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="inlineStr"/>
+      <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M128" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N128" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O128" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P128" s="8" t="n">
+        <v>46281.96670138889</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_O</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>d6jhcgoq</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P129" s="6" t="n">
+        <v>46282.01916666667</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed6010_Both</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>2v6kp87t</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="inlineStr"/>
+      <c r="J130" s="7" t="inlineStr"/>
+      <c r="K130" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M130" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N130" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O130" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P130" s="8" t="n">
+        <v>46282.03849537037</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed6010_Both</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>2v6kp87t</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr"/>
+      <c r="K131" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N131" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O131" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P131" s="8" t="n">
+        <v>46282.03849537037</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>yt9gk4c9</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr"/>
+      <c r="J132" s="7" t="inlineStr"/>
+      <c r="K132" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M132" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N132" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O132" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P132" s="8" t="n">
+        <v>46282.07037037037</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>038xqoj7</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr"/>
+      <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M133" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N133" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O133" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P133" s="8" t="n">
+        <v>46282.08375</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>4y1odimc</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr"/>
+      <c r="J134" s="7" t="inlineStr"/>
+      <c r="K134" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M134" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N134" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O134" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P134" s="8" t="n">
+        <v>46282.08803240741</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>irlbfy0d</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr"/>
+      <c r="J135" s="7" t="inlineStr"/>
+      <c r="K135" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N135" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O135" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P135" s="8" t="n">
+        <v>46282.14739583333</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_X</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>021u03yl</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>crashed</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P136" s="6" t="n">
+        <v>46282.15549768518</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed6000_O</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>c6xcsvyh</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr"/>
+      <c r="J137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N137" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O137" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P137" s="8" t="n">
+        <v>46282.16440972222</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed1710_Both</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>83uwf39h</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="7" t="inlineStr"/>
-      <c r="K115" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M115" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N115" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O115" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P115" s="8" t="n">
-        <v>46281.23458333333</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_BattleZone_seed6000_Both</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>tqpeo48v</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="I138" s="7" t="inlineStr"/>
+      <c r="J138" s="7" t="inlineStr"/>
+      <c r="K138" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M138" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N138" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O138" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P138" s="8" t="n">
+        <v>46282.16521990741</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed1710_Both</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>83uwf39h</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>BattleZone</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr"/>
-      <c r="J116" s="7" t="inlineStr"/>
-      <c r="K116" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N116" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O116" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P116" s="8" t="n">
-        <v>46281.23458333333</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Kangaroo_seed2000_O</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>d7qpd2cf</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>Kangaroo</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I117" s="7" t="inlineStr"/>
-      <c r="J117" s="7" t="inlineStr"/>
-      <c r="K117" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M117" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N117" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O117" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P117" s="8" t="n">
-        <v>46281.26112268519</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Boxing_seed3710_O</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>09cqwkf7</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="inlineStr"/>
-      <c r="J118" s="7" t="inlineStr"/>
-      <c r="K118" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M118" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N118" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O118" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P118" s="8" t="n">
-        <v>46281.27840277777</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_DemonAttack_seed6000_Both</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>sc4m9378</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>DemonAttack</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H119" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I119" s="7" t="inlineStr"/>
-      <c r="J119" s="7" t="inlineStr"/>
-      <c r="K119" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M119" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N119" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O119" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P119" s="8" t="n">
-        <v>46281.30539351852</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_DemonAttack_seed6000_Both</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>sc4m9378</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>DemonAttack</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H120" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="inlineStr"/>
-      <c r="J120" s="7" t="inlineStr"/>
-      <c r="K120" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L120" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M120" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N120" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O120" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P120" s="8" t="n">
-        <v>46281.30539351852</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Boxing_seed710_X</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>kqakm6xy</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="n">
-        <v>710</v>
-      </c>
-      <c r="H121" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I121" s="7" t="inlineStr"/>
-      <c r="J121" s="7" t="inlineStr"/>
-      <c r="K121" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M121" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N121" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O121" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P121" s="8" t="n">
-        <v>46281.32584490741</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Kangaroo_seed2010_O</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>a0pp1fht</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Kangaroo</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="n">
-        <v>2010</v>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I122" s="7" t="inlineStr"/>
-      <c r="J122" s="7" t="inlineStr"/>
-      <c r="K122" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L122" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M122" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N122" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O122" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P122" s="8" t="n">
-        <v>46281.34596064815</v>
+      <c r="I139" s="7" t="inlineStr"/>
+      <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M139" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N139" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O139" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P139" s="8" t="n">
+        <v>46282.16521990741</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -957,9 +957,9 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27.60</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -994,9 +994,9 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1275,11 +1275,7 @@
           <t>260.00</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
@@ -1441,11 +1437,7 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1797,7 +1789,11 @@
           <t>11.80</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1826,9 +1822,9 @@
           <t>4.30</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>13.90</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
@@ -2134,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9628,12 +9624,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed3710_X</t>
+          <t>Mamba2_AC_BattleZone_seed6000_O</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>pdn4m7j2</t>
+          <t>vh7yva6t</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -9653,25 +9649,25 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Boxing</t>
+          <t>BattleZone</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>4900.00</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="K108" s="3" t="n">
@@ -9692,18 +9688,18 @@
         <v>0.0625</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>46281.40581018518</v>
+        <v>46281.41318287037</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_BattleZone_seed6000_O</t>
+          <t>Mamba2_AC_MsPacman_seed3710_O</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>vh7yva6t</t>
+          <t>76be4ipd</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -9723,11 +9719,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>BattleZone</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>6000</v>
+        <v>3710</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -9736,12 +9732,12 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>4900.00</t>
+          <t>1847.00</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="K109" s="3" t="n">
@@ -9762,18 +9758,18 @@
         <v>0.0625</v>
       </c>
       <c r="P109" s="6" t="n">
-        <v>46281.41318287037</v>
+        <v>46281.47984953703</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_MsPacman_seed3710_O</t>
+          <t>Mamba2_AC_DemonAttack_seed6000_O</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>76be4ipd</t>
+          <t>hcay6kcv</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -9793,11 +9789,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>DemonAttack</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
@@ -9806,12 +9802,12 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>1847.00</t>
+          <t>211.50</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="K110" s="3" t="n">
@@ -9832,18 +9828,18 @@
         <v>0.0625</v>
       </c>
       <c r="P110" s="6" t="n">
-        <v>46281.47984953703</v>
+        <v>46281.48199074074</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_DemonAttack_seed6000_O</t>
+          <t>Mamba2_AC_PrivateEye_seed710_O</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>hcay6kcv</t>
+          <t>8nt4ru5n</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -9863,11 +9859,11 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>DemonAttack</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>6000</v>
+        <v>710</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -9876,12 +9872,12 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>211.50</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K111" s="3" t="n">
@@ -9902,18 +9898,18 @@
         <v>0.0625</v>
       </c>
       <c r="P111" s="6" t="n">
-        <v>46281.48199074074</v>
+        <v>46281.55998842593</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed710_O</t>
+          <t>Mamba2_AC_Kangaroo_seed2000_X</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>8nt4ru5n</t>
+          <t>1iwdyhhb</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -9933,25 +9929,25 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>710</v>
+        <v>2000</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K112" s="3" t="n">
@@ -9972,18 +9968,18 @@
         <v>0.0625</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>46281.55998842593</v>
+        <v>46281.56878472222</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Kangaroo_seed2000_X</t>
+          <t>Mamba2_AC_BattleZone_seed6000_X</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>1iwdyhhb</t>
+          <t>7i7irhf9</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -10003,11 +9999,11 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>BattleZone</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -10016,12 +10012,12 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="K113" s="3" t="n">
@@ -10042,18 +10038,18 @@
         <v>0.0625</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>46281.56878472222</v>
+        <v>46281.60291666666</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_BattleZone_seed6000_X</t>
+          <t>Mamba2_AC_MsPacman_seed3710_X</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>7i7irhf9</t>
+          <t>3dx0p15l</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -10073,11 +10069,11 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>BattleZone</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>6000</v>
+        <v>3710</v>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
@@ -10086,12 +10082,12 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="K114" s="3" t="n">
@@ -10112,18 +10108,18 @@
         <v>0.0625</v>
       </c>
       <c r="P114" s="6" t="n">
-        <v>46281.60291666666</v>
+        <v>46281.60375</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_MsPacman_seed3710_X</t>
+          <t>Mamba2_AC_Pong_seed6000_O</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>3dx0p15l</t>
+          <t>qv6pgjpw</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -10143,25 +10139,25 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="K115" s="3" t="n">
@@ -10182,18 +10178,18 @@
         <v>0.0625</v>
       </c>
       <c r="P115" s="6" t="n">
-        <v>46281.60375</v>
+        <v>46281.61435185185</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed6000_O</t>
+          <t>Mamba2_AC_PrivateEye_seed710_X</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>qv6pgjpw</t>
+          <t>3ucr91hm</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -10213,25 +10209,25 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>6000</v>
+        <v>710</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K116" s="3" t="n">
@@ -10252,18 +10248,18 @@
         <v>0.0625</v>
       </c>
       <c r="P116" s="6" t="n">
-        <v>46281.61435185185</v>
+        <v>46281.64665509259</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed710_X</t>
+          <t>Mamba2_AC_Kangaroo_seed2010_X</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>3ucr91hm</t>
+          <t>5v6k3xw5</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -10283,11 +10279,11 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>710</v>
+        <v>2010</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -10296,12 +10292,12 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K117" s="3" t="n">
@@ -10322,18 +10318,18 @@
         <v>0.0625</v>
       </c>
       <c r="P117" s="6" t="n">
-        <v>46281.64665509259</v>
+        <v>46281.67173611111</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Kangaroo_seed2010_X</t>
+          <t>Mamba2_AC_DemonAttack_seed6000_X</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>5v6k3xw5</t>
+          <t>4axihsuz</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -10353,11 +10349,11 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>DemonAttack</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>2010</v>
+        <v>6000</v>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
@@ -10366,12 +10362,12 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>153.50</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K118" s="3" t="n">
@@ -10392,18 +10388,18 @@
         <v>0.0625</v>
       </c>
       <c r="P118" s="6" t="n">
-        <v>46281.67173611111</v>
+        <v>46281.72890046296</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_DemonAttack_seed6000_X</t>
+          <t>Mamba2_AC_PrivateEye_seed3710_O</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>4axihsuz</t>
+          <t>lncnpxxv</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -10423,25 +10419,25 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>DemonAttack</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>6000</v>
+        <v>3710</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>153.50</t>
+          <t>-219.40</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="K119" s="3" t="n">
@@ -10462,18 +10458,18 @@
         <v>0.0625</v>
       </c>
       <c r="P119" s="6" t="n">
-        <v>46281.72890046296</v>
+        <v>46281.7578587963</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed3710_O</t>
+          <t>Mamba2_AC_DemonAttack_seed6010_X</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>lncnpxxv</t>
+          <t>vpvjr1ct</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -10493,25 +10489,25 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>DemonAttack</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>3710</v>
+        <v>6010</v>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>-219.40</t>
+          <t>155.50</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K120" s="3" t="n">
@@ -10532,18 +10528,18 @@
         <v>0.0625</v>
       </c>
       <c r="P120" s="6" t="n">
-        <v>46281.7578587963</v>
+        <v>46281.78896990741</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_DemonAttack_seed6010_X</t>
+          <t>Mamba2_AC_Amidar_seed710_O</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>vpvjr1ct</t>
+          <t>sqqttxrp</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -10563,25 +10559,25 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>DemonAttack</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>6010</v>
+        <v>710</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>155.50</t>
+          <t>178.40</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="K121" s="3" t="n">
@@ -10602,18 +10598,18 @@
         <v>0.0625</v>
       </c>
       <c r="P121" s="6" t="n">
-        <v>46281.78896990741</v>
+        <v>46281.80134259259</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_O</t>
+          <t>Mamba2_AC_Gopher_seed6010_X</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>sqqttxrp</t>
+          <t>5gfeyji8</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -10633,25 +10629,25 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Gopher</t>
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>710</v>
+        <v>6010</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>178.40</t>
+          <t>2888.00</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K122" s="3" t="n">
@@ -10672,18 +10668,18 @@
         <v>0.0625</v>
       </c>
       <c r="P122" s="6" t="n">
-        <v>46281.80134259259</v>
+        <v>46281.80818287037</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Gopher_seed6010_X</t>
+          <t>Mamba2_AC_Pong_seed6000_X</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>5gfeyji8</t>
+          <t>78620ail</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -10703,11 +10699,11 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -10716,12 +10712,12 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>2888.00</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K123" s="3" t="n">
@@ -10742,18 +10738,18 @@
         <v>0.0625</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>46281.80818287037</v>
+        <v>46281.85913194445</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed6000_X</t>
+          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>78620ail</t>
+          <t>umdwnyu2</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -10773,11 +10769,11 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>6000</v>
+        <v>3710</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
@@ -10786,12 +10782,12 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K124" s="3" t="n">
@@ -10812,18 +10808,18 @@
         <v>0.0625</v>
       </c>
       <c r="P124" s="6" t="n">
-        <v>46281.85913194445</v>
+        <v>46281.86515046296</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
+          <t>Mamba2_AC_Amidar_seed710_X</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>umdwnyu2</t>
+          <t>2vvni7nk</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -10843,11 +10839,11 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>3710</v>
+        <v>710</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -10856,12 +10852,12 @@
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>230.30</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K125" s="3" t="n">
@@ -10882,18 +10878,18 @@
         <v>0.0625</v>
       </c>
       <c r="P125" s="6" t="n">
-        <v>46281.86515046296</v>
+        <v>46281.93247685185</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_X</t>
+          <t>Mamba2_AC_Pong_seed6010_O</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>2vvni7nk</t>
+          <t>liij2pbh</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -10913,25 +10909,25 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>710</v>
+        <v>6010</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>230.30</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="K126" s="3" t="n">
@@ -10952,18 +10948,18 @@
         <v>0.0625</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>46281.93247685185</v>
+        <v>46281.96268518519</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed6010_O</t>
+          <t>Mamba2_AC_Assault_seed2000_O</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>liij2pbh</t>
+          <t>ong25zy1</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10983,11 +10979,11 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>6010</v>
+        <v>2000</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -11014,150 +11010,150 @@
         <v>0.0625</v>
       </c>
       <c r="P127" s="8" t="n">
-        <v>46281.96268518519</v>
+        <v>46281.96670138889</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Assault_seed2000_O</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>ong25zy1</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_O</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>d6jhcgoq</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P128" s="6" t="n">
+        <v>46282.01916666667</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>yt9gk4c9</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="n">
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H128" s="7" t="inlineStr">
+      <c r="H129" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr"/>
-      <c r="J128" s="7" t="inlineStr"/>
-      <c r="K128" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M128" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N128" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O128" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P128" s="8" t="n">
-        <v>46281.96670138889</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Boxing_seed710_O</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>d6jhcgoq</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>710</v>
-      </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>74.00</t>
-        </is>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M129" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N129" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O129" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P129" s="6" t="n">
-        <v>46282.01916666667</v>
+      <c r="I129" s="7" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M129" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N129" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O129" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P129" s="8" t="n">
+        <v>46282.07037037037</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Hero_seed6010_Both</t>
+          <t>Mamba2_AC_DemonAttack_seed6010_O</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>2v6kp87t</t>
+          <t>038xqoj7</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
@@ -11177,7 +11173,7 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>DemonAttack</t>
         </is>
       </c>
       <c r="G130" s="7" t="n">
@@ -11208,80 +11204,88 @@
         <v>0.0625</v>
       </c>
       <c r="P130" s="8" t="n">
-        <v>46282.03849537037</v>
+        <v>46282.08375</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Hero_seed6010_Both</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>2v6kp87t</t>
-        </is>
-      </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I131" s="7" t="inlineStr"/>
-      <c r="J131" s="7" t="inlineStr"/>
-      <c r="K131" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L131" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M131" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N131" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O131" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P131" s="8" t="n">
-        <v>46282.03849537037</v>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>4y1odimc</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P131" s="6" t="n">
+        <v>46282.08803240741</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_KungFuMaster_seed2000_O</t>
+          <t>Mamba2_AC_Gopher_seed6010_O</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>yt9gk4c9</t>
+          <t>irlbfy0d</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -11301,11 +11305,11 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Gopher</t>
         </is>
       </c>
       <c r="G132" s="7" t="n">
-        <v>2000</v>
+        <v>6010</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -11332,80 +11336,80 @@
         <v>0.0625</v>
       </c>
       <c r="P132" s="8" t="n">
-        <v>46282.07037037037</v>
+        <v>46282.14739583333</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_DemonAttack_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>038xqoj7</t>
-        </is>
-      </c>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>DemonAttack</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I133" s="7" t="inlineStr"/>
-      <c r="J133" s="7" t="inlineStr"/>
-      <c r="K133" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L133" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M133" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N133" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O133" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P133" s="8" t="n">
-        <v>46282.08375</v>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_X</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>021u03yl</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>crashed</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P133" s="6" t="n">
+        <v>46282.15549768518</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed3710_O</t>
+          <t>Mamba2_AC_Hero_seed6000_O</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>4y1odimc</t>
+          <t>c6xcsvyh</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -11425,11 +11429,11 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Boxing</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="G134" s="7" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
@@ -11456,18 +11460,18 @@
         <v>0.0625</v>
       </c>
       <c r="P134" s="8" t="n">
-        <v>46282.08803240741</v>
+        <v>46282.16440972222</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Gopher_seed6010_O</t>
+          <t>Mamba2_AC_Pong_seed6010_X</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>irlbfy0d</t>
+          <t>llrdr1sd</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -11487,7 +11491,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
@@ -11495,7 +11499,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr"/>
@@ -11518,80 +11522,80 @@
         <v>0.0625</v>
       </c>
       <c r="P135" s="8" t="n">
-        <v>46282.14739583333</v>
+        <v>46282.18530092593</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Boxing_seed710_X</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>021u03yl</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>crashed</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>eu475zxg</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G136" s="3" t="n">
-        <v>710</v>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="G136" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr"/>
-      <c r="J136" s="3" t="inlineStr"/>
-      <c r="K136" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M136" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N136" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O136" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P136" s="6" t="n">
-        <v>46282.15549768518</v>
+      <c r="I136" s="7" t="inlineStr"/>
+      <c r="J136" s="7" t="inlineStr"/>
+      <c r="K136" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M136" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N136" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O136" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P136" s="8" t="n">
+        <v>46282.20521990741</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Hero_seed6000_O</t>
+          <t>Mamba2_AC_Hero_seed6010_O</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>c6xcsvyh</t>
+          <t>hpkl5ag0</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -11615,7 +11619,7 @@
         </is>
       </c>
       <c r="G137" s="7" t="n">
-        <v>6000</v>
+        <v>6010</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -11642,18 +11646,18 @@
         <v>0.0625</v>
       </c>
       <c r="P137" s="8" t="n">
-        <v>46282.16440972222</v>
+        <v>46282.21564814815</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Frostbite_seed1710_Both</t>
+          <t>Mamba2_AC_Frostbite_seed1710_O</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>83uwf39h</t>
+          <t>tk7szjdx</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -11681,7 +11685,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I138" s="7" t="inlineStr"/>
@@ -11704,69 +11708,7 @@
         <v>0.0625</v>
       </c>
       <c r="P138" s="8" t="n">
-        <v>46282.16521990741</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Frostbite_seed1710_Both</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>83uwf39h</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I139" s="7" t="inlineStr"/>
-      <c r="J139" s="7" t="inlineStr"/>
-      <c r="K139" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L139" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M139" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N139" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O139" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P139" s="8" t="n">
-        <v>46282.16521990741</v>
+        <v>46282.2421412037</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -952,7 +952,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>34.70</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
@@ -11378,8 +11382,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr"/>
-      <c r="J133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>34.70</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
       <c r="K133" s="3" t="n">
         <v>50000</v>
       </c>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -842,8 +842,16 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>281.00</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>464.00</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -5200,8 +5208,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>281.00</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
       <c r="K44" s="3" t="n">
         <v>50000</v>
       </c>
@@ -5402,8 +5418,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>464.00</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
       <c r="K47" s="3" t="n">
         <v>50000</v>
       </c>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -98,10 +98,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,11 @@
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>352.80</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
@@ -727,9 +731,9 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>430.50</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -969,9 +973,9 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32.20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1008,7 +1012,7 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1229,7 +1233,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>155.50</t>
+          <t>255.00</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -1264,9 +1268,9 @@
           <t>211.50</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>124.50</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
@@ -1287,7 +1291,11 @@
           <t>260.00</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2782.00</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
@@ -1324,9 +1332,9 @@
           <t>250.00</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2540.00</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
@@ -1381,7 +1389,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2888.00</t>
+          <t>1676.00</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -1416,9 +1424,9 @@
           <t>3132.00</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2030.00</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr"/>
@@ -1448,8 +1456,16 @@
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>13517.00</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7107.50</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1477,14 +1493,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>13340.00</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>3556.50</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
@@ -1571,7 +1587,11 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
@@ -1600,7 +1620,11 @@
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr"/>
@@ -1616,12 +1640,20 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>8075.00</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>10649.00</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
@@ -1641,12 +1673,24 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>7926.00</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>10233.00</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
           <t>8737.00</t>
@@ -1672,7 +1716,11 @@
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6240.00</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
@@ -1701,9 +1749,9 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>7590.00</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
@@ -1795,15 +1843,19 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>11.80</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-17.80</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -1828,7 +1880,11 @@
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>20.80</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t>4.30</t>
@@ -2142,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P138"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10492,12 +10548,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_DemonAttack_seed6010_X</t>
+          <t>Mamba2_AC_Amidar_seed710_O</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>vpvjr1ct</t>
+          <t>sqqttxrp</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -10517,25 +10573,25 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>DemonAttack</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>6010</v>
+        <v>710</v>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>155.50</t>
+          <t>178.40</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="K120" s="3" t="n">
@@ -10556,18 +10612,18 @@
         <v>0.0625</v>
       </c>
       <c r="P120" s="6" t="n">
-        <v>46281.78896990741</v>
+        <v>46281.80134259259</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_O</t>
+          <t>Mamba2_AC_Pong_seed6000_X</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>sqqttxrp</t>
+          <t>78620ail</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -10587,25 +10643,25 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>710</v>
+        <v>6000</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>178.40</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K121" s="3" t="n">
@@ -10626,18 +10682,18 @@
         <v>0.0625</v>
       </c>
       <c r="P121" s="6" t="n">
-        <v>46281.80134259259</v>
+        <v>46281.85913194445</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Gopher_seed6010_X</t>
+          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>5gfeyji8</t>
+          <t>umdwnyu2</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -10657,11 +10713,11 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>6010</v>
+        <v>3710</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
@@ -10670,12 +10726,12 @@
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>2888.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K122" s="3" t="n">
@@ -10696,18 +10752,18 @@
         <v>0.0625</v>
       </c>
       <c r="P122" s="6" t="n">
-        <v>46281.80818287037</v>
+        <v>46281.86515046296</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed6000_X</t>
+          <t>Mamba2_AC_Amidar_seed710_X</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>78620ail</t>
+          <t>2vvni7nk</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -10727,11 +10783,11 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Amidar</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>6000</v>
+        <v>710</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -10740,12 +10796,12 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>230.30</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K123" s="3" t="n">
@@ -10766,18 +10822,18 @@
         <v>0.0625</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>46281.85913194445</v>
+        <v>46281.93247685185</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_PrivateEye_seed3710_X</t>
+          <t>Mamba2_AC_Pong_seed6010_O</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>umdwnyu2</t>
+          <t>liij2pbh</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -10797,25 +10853,25 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>3710</v>
+        <v>6010</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="K124" s="3" t="n">
@@ -10836,18 +10892,18 @@
         <v>0.0625</v>
       </c>
       <c r="P124" s="6" t="n">
-        <v>46281.86515046296</v>
+        <v>46281.96268518519</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Amidar_seed710_X</t>
+          <t>Mamba2_AC_Assault_seed2000_O</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>2vvni7nk</t>
+          <t>ong25zy1</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -10867,25 +10923,25 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Amidar</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>710</v>
+        <v>2000</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>230.30</t>
+          <t>430.50</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K125" s="3" t="n">
@@ -10906,18 +10962,18 @@
         <v>0.0625</v>
       </c>
       <c r="P125" s="6" t="n">
-        <v>46281.93247685185</v>
+        <v>46281.96670138889</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Pong_seed6010_O</t>
+          <t>Mamba2_AC_Boxing_seed710_O</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>liij2pbh</t>
+          <t>d6jhcgoq</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -10937,11 +10993,11 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Boxing</t>
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>6010</v>
+        <v>710</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
@@ -10950,12 +11006,12 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="K126" s="3" t="n">
@@ -10976,80 +11032,88 @@
         <v>0.0625</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>46281.96268518519</v>
+        <v>46282.01916666667</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Assault_seed2000_O</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>ong25zy1</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="n">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>yt9gk4c9</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="H127" s="7" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr"/>
-      <c r="J127" s="7" t="inlineStr"/>
-      <c r="K127" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N127" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O127" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P127" s="8" t="n">
-        <v>46281.96670138889</v>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>7590.00</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N127" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O127" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P127" s="6" t="n">
+        <v>46282.07037037037</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed710_O</t>
+          <t>Mamba2_AC_DemonAttack_seed6010_O</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>d6jhcgoq</t>
+          <t>038xqoj7</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -11069,181 +11133,197 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>124.50</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P128" s="6" t="n">
+        <v>46282.08375</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6010_O</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>irlbfy0d</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>2030.00</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P129" s="6" t="n">
+        <v>46282.14739583333</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed710_X</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>021u03yl</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>crashed</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G128" s="3" t="n">
+      <c r="G130" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>74.00</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M128" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N128" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O128" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P128" s="6" t="n">
-        <v>46282.01916666667</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_KungFuMaster_seed2000_O</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>yt9gk4c9</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>KungFuMaster</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I129" s="7" t="inlineStr"/>
-      <c r="J129" s="7" t="inlineStr"/>
-      <c r="K129" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M129" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N129" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O129" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P129" s="8" t="n">
-        <v>46282.07037037037</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_DemonAttack_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>038xqoj7</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>DemonAttack</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H130" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I130" s="7" t="inlineStr"/>
-      <c r="J130" s="7" t="inlineStr"/>
-      <c r="K130" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M130" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N130" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O130" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P130" s="8" t="n">
-        <v>46282.08375</v>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>34.70</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P130" s="6" t="n">
+        <v>46282.15549768518</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed3710_O</t>
+          <t>Mamba2_AC_Hero_seed6000_O</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>4y1odimc</t>
+          <t>c6xcsvyh</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -11263,11 +11343,11 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Boxing</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>3710</v>
+        <v>6000</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -11276,12 +11356,12 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>13340.00</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="K131" s="3" t="n">
@@ -11302,85 +11382,93 @@
         <v>0.0625</v>
       </c>
       <c r="P131" s="6" t="n">
-        <v>46282.08803240741</v>
+        <v>46282.16440972222</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Gopher_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>irlbfy0d</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>Gopher</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="n">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>llrdr1sd</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="inlineStr"/>
-      <c r="J132" s="7" t="inlineStr"/>
-      <c r="K132" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N132" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O132" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P132" s="8" t="n">
-        <v>46282.14739583333</v>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>-17.80</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P132" s="6" t="n">
+        <v>46282.18530092593</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Mamba2_AC_Boxing_seed710_X</t>
+          <t>Mamba2_AC_Hero_seed6010_O</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>021u03yl</t>
+          <t>hpkl5ag0</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>crashed</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -11395,356 +11483,1352 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>3556.50</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P133" s="6" t="n">
+        <v>46282.21564814815</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>tk7szjdx</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>2540.00</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P134" s="6" t="n">
+        <v>46282.2421412037</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Assault_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>8ej0i6uu</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>352.80</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P135" s="6" t="n">
+        <v>46282.32163194445</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_DemonAttack_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>lg1zmght</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>DemonAttack</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>255.00</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P136" s="6" t="n">
+        <v>46282.33078703703</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>1hfdhxam</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
           <t>Boxing</t>
         </is>
       </c>
-      <c r="G133" s="3" t="n">
+      <c r="G137" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P137" s="6" t="n">
+        <v>46282.36037037037</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>j52nrws5</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>2782.00</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P138" s="6" t="n">
+        <v>46282.3647337963</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed6000_X</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>tgbroc0c</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>13517.00</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O139" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P139" s="6" t="n">
+        <v>46282.38931712963</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_KungFuMaster_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>7d9n39sb</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>KungFuMaster</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>6240.00</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P140" s="6" t="n">
+        <v>46282.3912037037</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>osdzshj9</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>1676.00</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O141" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P141" s="6" t="n">
+        <v>46282.4034375</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed6010_X</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>tqde4j3q</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>7107.50</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N142" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O142" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P142" s="6" t="n">
+        <v>46282.43136574074</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>hc60link</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O143" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P143" s="6" t="n">
+        <v>46282.49684027778</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>mj5eo1fe</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>20.80</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N144" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O144" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P144" s="6" t="n">
+        <v>46282.51994212963</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Pong_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>nu9tl3vl</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>Pong</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N145" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O145" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P145" s="6" t="n">
+        <v>46282.62939814815</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>pd5f3tfl</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>10233.00</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>8.09</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O146" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P146" s="6" t="n">
+        <v>46282.6515162037</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed710_O</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>yc9w2s5l</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>7926.00</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O147" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P147" s="6" t="n">
+        <v>46282.78369212963</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>w17ofyd6</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>34.70</t>
-        </is>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M133" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N133" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O133" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P133" s="6" t="n">
-        <v>46282.15549768518</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Hero_seed6000_O</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>c6xcsvyh</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>10649.00</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>8.47</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N148" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O148" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P148" s="6" t="n">
+        <v>46282.78776620371</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed710_X</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>ecvlv2af</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>8075.00</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P149" s="6" t="n">
+        <v>46282.91478009259</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>hzj4baq1</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H134" s="7" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I134" s="7" t="inlineStr"/>
-      <c r="J134" s="7" t="inlineStr"/>
-      <c r="K134" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L134" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M134" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N134" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O134" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P134" s="8" t="n">
-        <v>46282.16440972222</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Pong_seed6010_X</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>llrdr1sd</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="I150" s="7" t="inlineStr"/>
+      <c r="J150" s="7" t="inlineStr"/>
+      <c r="K150" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M150" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N150" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O150" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P150" s="8" t="n">
+        <v>46282.94171296297</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed3710_Both</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>h9dw46ew</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Pong</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I135" s="7" t="inlineStr"/>
-      <c r="J135" s="7" t="inlineStr"/>
-      <c r="K135" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M135" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N135" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O135" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P135" s="8" t="n">
-        <v>46282.18530092593</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Boxing_seed3710_X</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>eu475zxg</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="I151" s="7" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr"/>
+      <c r="K151" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M151" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N151" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O151" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P151" s="8" t="n">
+        <v>46282.99206018518</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed3710_Both</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>h9dw46ew</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="n">
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="n">
         <v>3710</v>
       </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I136" s="7" t="inlineStr"/>
-      <c r="J136" s="7" t="inlineStr"/>
-      <c r="K136" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L136" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M136" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N136" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O136" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P136" s="8" t="n">
-        <v>46282.20521990741</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Hero_seed6010_O</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>hpkl5ag0</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="n">
-        <v>6010</v>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
+      <c r="H152" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I137" s="7" t="inlineStr"/>
-      <c r="J137" s="7" t="inlineStr"/>
-      <c r="K137" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L137" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M137" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N137" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O137" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P137" s="8" t="n">
-        <v>46282.21564814815</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Frostbite_seed1710_O</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>tk7szjdx</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>Frostbite</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H138" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I138" s="7" t="inlineStr"/>
-      <c r="J138" s="7" t="inlineStr"/>
-      <c r="K138" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M138" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N138" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O138" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P138" s="8" t="n">
-        <v>46282.2421412037</v>
+      <c r="I152" s="7" t="inlineStr"/>
+      <c r="J152" s="7" t="inlineStr"/>
+      <c r="K152" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M152" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N152" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O152" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P152" s="8" t="n">
+        <v>46282.99206018518</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -840,12 +840,20 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>220.00</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>870.00</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>281.00</t>
@@ -869,12 +877,20 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>184.00</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>339.00</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>268.00</t>
@@ -903,7 +919,11 @@
           <t>9400.00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16200.00</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
@@ -936,7 +956,11 @@
           <t>13600.00</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>9700.00</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1038,12 +1062,20 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9.70</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
@@ -1067,12 +1099,20 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>17.70</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>10.60</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>20.70</t>
@@ -1130,7 +1170,11 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1574,7 +1618,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>580.00</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1587,9 +1635,9 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1420.00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1607,7 +1655,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1620,9 +1672,9 @@
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>1140.00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
@@ -1645,7 +1697,11 @@
           <t>8075.00</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6783.00</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1678,9 +1734,9 @@
           <t>7926.00</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>8213.00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
@@ -2198,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P152"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12646,189 +12702,1177 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed1710_O</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>hzj4baq1</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>8213.00</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P150" s="6" t="n">
+        <v>46282.94171296297</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>7gg68i66</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>1140.00</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N151" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O151" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P151" s="6" t="n">
+        <v>46283.06856481481</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>c2qsumr8</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>6783.00</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P152" s="6" t="n">
+        <v>46283.0745949074</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>vvbxysmh</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>1420.00</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P153" s="6" t="n">
+        <v>46283.19665509259</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed710_O</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>mditu4ar</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N154" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O154" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P154" s="6" t="n">
+        <v>46283.22854166666</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Kangaroo_seed710_X</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>xma3ku4y</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Kangaroo</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>580.00</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P155" s="6" t="n">
+        <v>46283.33405092593</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>dlwj6ky3</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>339.00</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N156" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O156" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P156" s="6" t="n">
+        <v>46283.35032407408</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed710_O</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>ysny5opr</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>184.00</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O157" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P157" s="6" t="n">
+        <v>46283.48784722222</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>rr10cndm</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>870.00</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O158" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P158" s="6" t="n">
+        <v>46283.508125</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed710_X</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>p6nur6oq</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>220.00</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O159" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P159" s="6" t="n">
+        <v>46283.64868055555</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>jftlhvxb</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>9700.00</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N160" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O160" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P160" s="6" t="n">
+        <v>46283.6619212963</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>iv87tu9s</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>16200.00</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O161" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P161" s="6" t="n">
+        <v>46283.76673611111</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Breakout_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>ynh2axz9</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>10.60</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O162" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P162" s="6" t="n">
+        <v>46283.8025</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Breakout_seed710_O</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>kpkgy63f</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>17.70</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N163" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O163" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P163" s="6" t="n">
+        <v>46283.92071759259</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Breakout_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>eb1idchp</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>9.70</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N164" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O164" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P164" s="6" t="n">
+        <v>46283.94190972222</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Breakout_seed710_X</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>foc79krr</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>Krull</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="n">
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr"/>
+      <c r="K165" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L165" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M165" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N165" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O165" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P165" s="8" t="n">
+        <v>46284.05696759259</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>aimffgh0</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n">
         <v>1710</v>
       </c>
-      <c r="H150" s="7" t="inlineStr">
+      <c r="H166" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I150" s="7" t="inlineStr"/>
-      <c r="J150" s="7" t="inlineStr"/>
-      <c r="K150" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M150" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N150" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O150" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P150" s="8" t="n">
-        <v>46282.94171296297</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Kangaroo_seed3710_Both</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>h9dw46ew</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>Kangaroo</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="inlineStr"/>
-      <c r="J151" s="7" t="inlineStr"/>
-      <c r="K151" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L151" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M151" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N151" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O151" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P151" s="8" t="n">
-        <v>46282.99206018518</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Kangaroo_seed3710_Both</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>h9dw46ew</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>Kangaroo</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="n">
-        <v>3710</v>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="inlineStr"/>
-      <c r="J152" s="7" t="inlineStr"/>
-      <c r="K152" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L152" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N152" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O152" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P152" s="8" t="n">
-        <v>46282.99206018518</v>
+      <c r="I166" s="7" t="inlineStr"/>
+      <c r="J166" s="7" t="inlineStr"/>
+      <c r="K166" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M166" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N166" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O166" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P166" s="8" t="n">
+        <v>46284.09695601852</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -1062,9 +1062,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>16.40</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1141,8 +1141,16 @@
           <t>1450.00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2020.00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
@@ -1170,12 +1178,16 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>750.00</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
@@ -1198,12 +1210,20 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73510.00</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>66980.00</t>
@@ -1227,12 +1247,20 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>76910.00</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>72700.00</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>77110.00</t>
@@ -1594,7 +1622,11 @@
           <t>445.00</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr"/>
@@ -2254,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -13752,127 +13784,671 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="7" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>Mamba2_AC_Breakout_seed710_X</t>
         </is>
       </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>foc79krr</t>
         </is>
       </c>
-      <c r="C165" s="7" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>16.40</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N165" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O165" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P165" s="6" t="n">
+        <v>46284.05696759259</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>aimffgh0</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>750.00</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O166" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P166" s="6" t="n">
+        <v>46284.09695601852</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed3710_O</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>n74znd6w</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>72700.00</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N167" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O167" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P167" s="6" t="n">
+        <v>46284.21068287037</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>3baoprtn</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>2020.00</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N168" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O168" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P168" s="6" t="n">
+        <v>46284.24060185185</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed3710_X</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>h4ycpjkq</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>3710</v>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>73510.00</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N169" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O169" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P169" s="6" t="n">
+        <v>46284.33123842593</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed710_O</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>12kfoeby</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>76910.00</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N170" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O170" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P170" s="6" t="n">
+        <v>46284.3950462963</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>j7eucxrl</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D165" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E165" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="n">
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr"/>
+      <c r="K171" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M171" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N171" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O171" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P171" s="8" t="n">
+        <v>46284.43381944444</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed2000_Both</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>j7eucxrl</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I172" s="7" t="inlineStr"/>
+      <c r="J172" s="7" t="inlineStr"/>
+      <c r="K172" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M172" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N172" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O172" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P172" s="8" t="n">
+        <v>46284.43381944444</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Jamesbond_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>657ex7dm</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>Jamesbond</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr"/>
+      <c r="K173" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L173" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M173" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N173" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O173" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P173" s="8" t="n">
+        <v>46284.48659722223</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_CrazyClimber_seed710_X</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>fkwuvuhi</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>CrazyClimber</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="n">
         <v>710</v>
       </c>
-      <c r="H165" s="7" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I165" s="7" t="inlineStr"/>
-      <c r="J165" s="7" t="inlineStr"/>
-      <c r="K165" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L165" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M165" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N165" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O165" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P165" s="8" t="n">
-        <v>46284.05696759259</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_ChopperCommand_seed1710_O</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>aimffgh0</t>
-        </is>
-      </c>
-      <c r="C166" s="7" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D166" s="7" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>ChopperCommand</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H166" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I166" s="7" t="inlineStr"/>
-      <c r="J166" s="7" t="inlineStr"/>
-      <c r="K166" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L166" s="7" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M166" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N166" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O166" s="7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P166" s="8" t="n">
-        <v>46284.09695601852</v>
+      <c r="I174" s="7" t="inlineStr"/>
+      <c r="J174" s="7" t="inlineStr"/>
+      <c r="K174" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M174" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N174" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O174" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P174" s="8" t="n">
+        <v>46284.51091435185</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,6 +122,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,175 +218,175 @@
     <author>Drama</author>
   </authors>
   <commentList>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>첨부된 논문 표의 DramaXS 게임별 점수입니다. X행에 표시합니다.</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>X: Retrieval 미사용, O: Retrieval 적용 (target: 16).
-양쪽에 유효한 점수가 있는 공통 시드만 사용하며 RUNNING/누락 점수는 제외합니다. Drama/results/update_tex.py와 동일하게 표시된 시드 점수를 집계합니다.</t>
+양쪽에 유효한 점수가 있는 공통 시드만 사용하며 RUNNING/누락 점수는 제외합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드도 제외합니다. Drama/results/update_tex.py와 동일하게 표시된 시드 점수를 집계합니다.</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>X행: Retrieval 미사용의 공통 시드 평균 − DramaXS 논문 점수.
 O행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>X행: (Retrieval 미사용 평균 − DramaXS 논문 점수) / (Human − Random).
 O행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
-모든 평균은 공통 시드 기준입니다. HNS는 Random=0, Human=1 기준이며 차이의 부호를 유지합니다. 백분율이 아닙니다. Random/Human은 STORM 엑셀과 동일한 기준값을 사용합니다.</t>
+모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준입니다. HNS는 Random=0, Human=1 기준이며 차이의 부호를 유지합니다. 백분율이 아닙니다. Random/Human은 STORM 엑셀과 동일한 기준값을 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0">
+    <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>Random: 227.8
 Human: 7127.7</t>
       </text>
     </comment>
-    <comment ref="M4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <t>Random: 5.8
 Human: 1719.5</t>
       </text>
     </comment>
-    <comment ref="M6" authorId="0" shapeId="0">
+    <comment ref="N6" authorId="0" shapeId="0">
       <text>
         <t>Random: 222.4
 Human: 742.0</t>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0">
+    <comment ref="N8" authorId="0" shapeId="0">
       <text>
         <t>Random: 210.0
 Human: 8503.3</t>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0">
+    <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>Random: 14.2
 Human: 753.1</t>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>Random: 2360.0
 Human: 37187.5</t>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.1
 Human: 12.1</t>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>Random: 1.7
 Human: 30.5</t>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0">
+    <comment ref="N18" authorId="0" shapeId="0">
       <text>
         <t>Random: 811.0
 Human: 7387.8</t>
       </text>
     </comment>
-    <comment ref="M20" authorId="0" shapeId="0">
+    <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>Random: 10780.5
 Human: 35829.4</t>
       </text>
     </comment>
-    <comment ref="M22" authorId="0" shapeId="0">
+    <comment ref="N22" authorId="0" shapeId="0">
       <text>
         <t>Random: 152.1
 Human: 1971.0</t>
       </text>
     </comment>
-    <comment ref="M24" authorId="0" shapeId="0">
+    <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>Random: 65.2
 Human: 4334.7</t>
       </text>
     </comment>
-    <comment ref="M26" authorId="0" shapeId="0">
+    <comment ref="N26" authorId="0" shapeId="0">
       <text>
         <t>Random: 257.6
 Human: 2412.5</t>
       </text>
     </comment>
-    <comment ref="M28" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>Random: 1027.0
 Human: 30826.4</t>
       </text>
     </comment>
-    <comment ref="M30" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>Random: 29.0
 Human: 302.8</t>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0">
+    <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>Random: 52.0
 Human: 3035.0</t>
       </text>
     </comment>
-    <comment ref="M34" authorId="0" shapeId="0">
+    <comment ref="N34" authorId="0" shapeId="0">
       <text>
         <t>Random: 1598.0
 Human: 2665.5</t>
       </text>
     </comment>
-    <comment ref="M36" authorId="0" shapeId="0">
+    <comment ref="N36" authorId="0" shapeId="0">
       <text>
         <t>Random: 258.5
 Human: 22736.3</t>
       </text>
     </comment>
-    <comment ref="M38" authorId="0" shapeId="0">
+    <comment ref="N38" authorId="0" shapeId="0">
       <text>
         <t>Random: 307.3
 Human: 6951.6</t>
       </text>
     </comment>
-    <comment ref="M40" authorId="0" shapeId="0">
+    <comment ref="N40" authorId="0" shapeId="0">
       <text>
         <t>Random: -20.7
 Human: 14.6</t>
       </text>
     </comment>
-    <comment ref="M42" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="0" shapeId="0">
       <text>
         <t>Random: 24.9
 Human: 69571.3</t>
       </text>
     </comment>
-    <comment ref="M44" authorId="0" shapeId="0">
+    <comment ref="N44" authorId="0" shapeId="0">
       <text>
         <t>Random: 163.9
 Human: 13455.0</t>
       </text>
     </comment>
-    <comment ref="M46" authorId="0" shapeId="0">
+    <comment ref="N46" authorId="0" shapeId="0">
       <text>
         <t>Random: 11.5
 Human: 7845.0</t>
       </text>
     </comment>
-    <comment ref="M48" authorId="0" shapeId="0">
+    <comment ref="N48" authorId="0" shapeId="0">
       <text>
         <t>Random: 68.4
 Human: 42054.7</t>
       </text>
     </comment>
-    <comment ref="M50" authorId="0" shapeId="0">
+    <comment ref="N50" authorId="0" shapeId="0">
       <text>
         <t>Random: 533.4
 Human: 11693.2</t>
@@ -682,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -696,11 +699,12 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -727,41 +731,44 @@
         <v>2010</v>
       </c>
       <c r="G1" s="1" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H1" s="1" t="n">
         <v>3290</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>6010</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>6020</v>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>DramaXS (논문 점수)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -786,34 +793,35 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>608.00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>1376.00</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="3" t="n">
         <v>820</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>1051.5</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="P2" s="5" t="n">
         <v>231.5</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="6" t="n">
         <v>0.03355121088711431</v>
       </c>
     </row>
@@ -836,32 +844,33 @@
       <c r="D3" s="7" t="inlineStr"/>
       <c r="E3" s="7" t="inlineStr"/>
       <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>705.00</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>1169.00</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="9" t="n">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="9" t="n">
         <v>972.25</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="P3" s="9" t="n">
         <v>79.25</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="Q3" s="10" t="n">
         <v>-0.01148567370541602</v>
       </c>
     </row>
@@ -884,34 +893,35 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>92.60</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>140.325</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>9.324999999999989</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.005441442492851717</v>
       </c>
     </row>
@@ -934,32 +944,33 @@
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>139.80</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="9" t="n">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="9" t="n">
         <v>130.175</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="P5" s="9" t="n">
         <v>10.14999999999998</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="Q5" s="10" t="n">
         <v>-0.005922856976133498</v>
       </c>
     </row>
@@ -984,32 +995,33 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>521.80</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
         <v>539</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>383.5</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>-155.5</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>-0.2992686682063125</v>
       </c>
     </row>
@@ -1034,30 +1046,31 @@
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>428.40</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="9" t="n">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="9" t="n">
         <v>449.925</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="P7" s="9" t="n">
         <v>66.42499999999995</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="Q7" s="10" t="n">
         <v>0.1278387220939183</v>
       </c>
     </row>
@@ -1086,28 +1099,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
         <v>1632</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.005787804613362595</v>
       </c>
     </row>
@@ -1136,26 +1150,27 @@
       </c>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="9" t="n">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="9" t="n">
         <v>1397.5</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="P9" s="9" t="n">
         <v>282.5</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="Q9" s="10" t="n">
         <v>-0.03406364173489444</v>
       </c>
     </row>
@@ -1179,33 +1194,34 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>870.00</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>281.00</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>464.00</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>458.75</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="P10" s="5" t="n">
         <v>321.75</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.4354445797807552</v>
       </c>
     </row>
@@ -1229,31 +1245,32 @@
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>339.00</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>324.00</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="9" t="n">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="9" t="n">
         <v>278.75</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="P11" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="Q11" s="10" t="n">
         <v>-0.243605359317905</v>
       </c>
     </row>
@@ -1281,29 +1298,30 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>4000.00</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
         <v>10860</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>10775</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="P12" s="5" t="n">
         <v>-85</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="6" t="n">
         <v>-0.002440600100495298</v>
       </c>
     </row>
@@ -1331,27 +1349,28 @@
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>4900.00</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="9" t="n">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="9" t="n">
         <v>8600</v>
       </c>
-      <c r="O13" s="9" t="n">
+      <c r="P13" s="9" t="n">
         <v>2175</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="Q13" s="10" t="n">
         <v>-0.06245064963032087</v>
       </c>
     </row>
@@ -1375,33 +1394,34 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>32.20</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>58.55</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="P14" s="5" t="n">
         <v>-19.45</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="6" t="n">
         <v>-1.620833333333334</v>
       </c>
     </row>
@@ -1425,31 +1445,32 @@
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>36.00</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
-      <c r="N15" s="9" t="n">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="9" t="n">
         <v>65.7</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="P15" s="9" t="n">
         <v>7.150000000000006</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="Q15" s="10" t="n">
         <v>0.5958333333333338</v>
       </c>
     </row>
@@ -1473,33 +1494,34 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9.70</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>14.725</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="P16" s="5" t="n">
         <v>7.725</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>0.2682291666666666</v>
       </c>
     </row>
@@ -1523,31 +1545,32 @@
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>10.60</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>17.20</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
-      <c r="N17" s="9" t="n">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="9" t="n">
         <v>16.55</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="P17" s="9" t="n">
         <v>1.825000000000001</v>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>0.06336805555555559</v>
       </c>
     </row>
@@ -1578,27 +1601,32 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1450.00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
         <v>1642</v>
       </c>
-      <c r="N18" s="4" t="n">
-        <v>1525</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>-117</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>-0.01778980659287191</v>
+      <c r="O18" s="4" t="n">
+        <v>1510</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>-132</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>-0.02007055102785549</v>
       </c>
     </row>
     <row r="19">
@@ -1628,25 +1656,30 @@
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2260.00</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
-      <c r="N19" s="9" t="n">
-        <v>1172.5</v>
-      </c>
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="9" t="n">
-        <v>352.5</v>
-      </c>
-      <c r="P19" s="10" t="n">
-        <v>-0.05359749422211409</v>
+        <v>1390</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>-0.01824595547986863</v>
       </c>
     </row>
     <row r="20">
@@ -1669,33 +1702,34 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>73510.00</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>66980.00</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>82640.00</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
         <v>83931</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>76802.5</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="P20" s="5" t="n">
         <v>-7128.5</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="6" t="n">
         <v>-0.2845833549577027</v>
       </c>
     </row>
@@ -1719,31 +1753,32 @@
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>72700.00</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>77110.00</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>71030.00</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-      <c r="N21" s="9" t="n">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="9" t="n">
         <v>74437.5</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="P21" s="9" t="n">
         <v>2365</v>
       </c>
-      <c r="P21" s="10" t="n">
+      <c r="Q21" s="10" t="n">
         <v>-0.09441532362698561</v>
       </c>
     </row>
@@ -1772,28 +1807,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>153.50</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>255.00</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="O22" s="4" t="n">
         <v>187.25</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="P22" s="5" t="n">
         <v>-13.75</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="6" t="n">
         <v>-0.007559513991973171</v>
       </c>
     </row>
@@ -1822,26 +1858,27 @@
       </c>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>211.50</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>124.50</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr"/>
-      <c r="N23" s="9" t="n">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="9" t="n">
         <v>151</v>
       </c>
-      <c r="O23" s="9" t="n">
+      <c r="P23" s="9" t="n">
         <v>36.25</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="Q23" s="10" t="n">
         <v>-0.01992962779702018</v>
       </c>
     </row>
@@ -1868,34 +1905,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>1952.00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>1101.2</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="P24" s="5" t="n">
         <v>316.2</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="6" t="n">
         <v>0.07406019440215483</v>
       </c>
     </row>
@@ -1922,32 +1960,33 @@
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>2224.00</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
-      <c r="N25" s="9" t="n">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="9" t="n">
         <v>1105.4</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="P25" s="9" t="n">
         <v>4.200000000000045</v>
       </c>
-      <c r="P25" s="10" t="n">
+      <c r="Q25" s="10" t="n">
         <v>0.0009837217472772094</v>
       </c>
     </row>
@@ -1976,28 +2015,29 @@
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>2150.00</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1676.00</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
         <v>2757</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>1760</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="P26" s="5" t="n">
         <v>-997</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="6" t="n">
         <v>-0.4626664810432038</v>
       </c>
     </row>
@@ -2026,26 +2066,27 @@
       </c>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>3132.00</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>2030.00</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
-      <c r="N27" s="9" t="n">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="9" t="n">
         <v>1851</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="P27" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="P27" s="10" t="n">
+      <c r="Q27" s="10" t="n">
         <v>0.04222933778829644</v>
       </c>
     </row>
@@ -2074,28 +2115,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>13517.00</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>7107.50</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="3" t="n">
         <v>7946</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>8921.625</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>975.625</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="6" t="n">
         <v>0.03273975314939227</v>
       </c>
     </row>
@@ -2124,26 +2166,27 @@
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>13340.00</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>3556.50</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
       <c r="L29" s="7" t="inlineStr"/>
-      <c r="M29" s="8" t="inlineStr"/>
-      <c r="N29" s="9" t="n">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="9" t="n">
         <v>6903.875</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="P29" s="9" t="n">
         <v>2017.75</v>
       </c>
-      <c r="P29" s="10" t="n">
+      <c r="Q29" s="10" t="n">
         <v>-0.0677110948542588</v>
       </c>
     </row>
@@ -2175,25 +2218,26 @@
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>630</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="P30" s="5" t="n">
         <v>258</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="6" t="n">
         <v>0.9422936449963477</v>
       </c>
     </row>
@@ -2224,24 +2268,29 @@
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>605.00</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
       <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr"/>
-      <c r="N31" s="9" t="n">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="9" t="n">
         <v>531.25</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="P31" s="9" t="n">
         <v>98.75</v>
       </c>
-      <c r="P31" s="10" t="n">
+      <c r="Q31" s="10" t="n">
         <v>-0.3606647187728269</v>
       </c>
     </row>
@@ -2273,25 +2322,26 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>1420.00</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>1350</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="P32" s="5" t="n">
         <v>-34</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="6" t="n">
         <v>-0.01139792155548106</v>
       </c>
     </row>
@@ -2323,23 +2373,24 @@
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>1140.00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
-      <c r="N33" s="9" t="n">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="9" t="n">
         <v>1335</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="P33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="P33" s="10" t="n">
+      <c r="Q33" s="10" t="n">
         <v>-0.005028494803888703</v>
       </c>
     </row>
@@ -2367,29 +2418,30 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>10649.00</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="3" t="n">
         <v>9693</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="O34" s="4" t="n">
         <v>8835.75</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="P34" s="5" t="n">
         <v>-857.25</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="6" t="n">
         <v>-0.8030444964871194</v>
       </c>
     </row>
@@ -2417,27 +2469,28 @@
       <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>10233.00</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="9" t="n">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="9" t="n">
         <v>8777.25</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="P35" s="9" t="n">
         <v>58.5</v>
       </c>
-      <c r="P35" s="10" t="n">
+      <c r="Q35" s="10" t="n">
         <v>-0.05480093676814989</v>
       </c>
     </row>
@@ -2469,25 +2522,26 @@
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>19020.00</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
         <v>23920</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="O36" s="4" t="n">
         <v>16480</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="P36" s="5" t="n">
         <v>-7440</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="6" t="n">
         <v>-0.3309932466700478</v>
       </c>
     </row>
@@ -2519,23 +2573,24 @@
       </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>23080.00</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="9" t="n">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
+      <c r="O37" s="9" t="n">
         <v>16137.5</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="P37" s="9" t="n">
         <v>342.5</v>
       </c>
-      <c r="P37" s="10" t="n">
+      <c r="Q37" s="10" t="n">
         <v>-0.01523725631511981</v>
       </c>
     </row>
@@ -2560,29 +2615,34 @@
           <t>2011.00</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2094.00</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>1548.00</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
         <v>2270</v>
       </c>
-      <c r="N38" s="4" t="n">
-        <v>2582.333333333333</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>312.3333333333335</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v>0.04700771086996876</v>
+      <c r="O38" s="4" t="n">
+        <v>2460.25</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>190.25</v>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>0.02863356561263037</v>
       </c>
     </row>
     <row r="39">
@@ -2606,31 +2666,32 @@
           <t>1857.00</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>2322.00</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>1847.00</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
-      <c r="N39" s="9" t="n">
-        <v>2593</v>
-      </c>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="9" t="n">
-        <v>10.66666666666652</v>
-      </c>
-      <c r="P39" s="10" t="n">
-        <v>0.001605386070265719</v>
+        <v>2525.25</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <v>0.009782821365681862</v>
       </c>
     </row>
     <row r="40">
@@ -2653,33 +2714,34 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>21.00</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>11.80</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>-17.80</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>8.75</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="P40" s="5" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="6" t="n">
         <v>-0.1770538243626062</v>
       </c>
     </row>
@@ -2703,31 +2765,32 @@
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>20.80</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>13.90</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
-      <c r="N41" s="9" t="n">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr"/>
+      <c r="O41" s="9" t="n">
         <v>14.75</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="P41" s="9" t="n">
         <v>5.999999999999998</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="Q41" s="10" t="n">
         <v>0.169971671388102</v>
       </c>
     </row>
@@ -2752,28 +2815,33 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="O42" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="6" t="n">
         <v>0.0001437888948960694</v>
       </c>
     </row>
@@ -2798,26 +2866,31 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>-219.40</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
-      <c r="N43" s="9" t="n">
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="9" t="n">
         <v>-6.466666666666669</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="P43" s="9" t="n">
         <v>106.4666666666667</v>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="Q43" s="10" t="n">
         <v>-0.001530872434326819</v>
       </c>
     </row>
@@ -2845,25 +2918,26 @@
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="3" t="n">
         <v>796</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="O44" s="4" t="n">
         <v>618.3333333333334</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="P44" s="5" t="n">
         <v>-177.6666666666666</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="6" t="n">
         <v>-0.01336734105278469</v>
       </c>
     </row>
@@ -2891,23 +2965,24 @@
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
-      <c r="N45" s="9" t="n">
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
+      <c r="O45" s="9" t="n">
         <v>709.1666666666666</v>
       </c>
-      <c r="O45" s="9" t="n">
+      <c r="P45" s="9" t="n">
         <v>90.83333333333326</v>
       </c>
-      <c r="P45" s="10" t="n">
+      <c r="Q45" s="10" t="n">
         <v>0.006834147161132883</v>
       </c>
     </row>
@@ -2931,33 +3006,34 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>14670.00</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>7030.00</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>7860.00</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="3" t="n">
         <v>14020</v>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="O46" s="4" t="n">
         <v>11812.5</v>
       </c>
-      <c r="O46" s="5" t="n">
+      <c r="P46" s="5" t="n">
         <v>-2207.5</v>
       </c>
-      <c r="P46" s="6" t="n">
+      <c r="Q46" s="6" t="n">
         <v>-0.2818025148401098</v>
       </c>
     </row>
@@ -2981,31 +3057,32 @@
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>15330.00</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>8520.00</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>8500.00</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
-      <c r="M47" s="8" t="inlineStr"/>
-      <c r="N47" s="9" t="n">
+      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="9" t="n">
         <v>12537.5</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="P47" s="9" t="n">
         <v>725</v>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="Q47" s="10" t="n">
         <v>0.09255122231441884</v>
       </c>
     </row>
@@ -3020,39 +3097,44 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>714.00</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>824.00</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>432.00</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>534.00</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="3" t="n">
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="N48" s="4" t="n">
-        <v>596.6666666666666</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>99.66666666666663</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>0.002373790180765313</v>
+      <c r="O48" s="4" t="n">
+        <v>626</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>0.003072430769084201</v>
       </c>
     </row>
     <row r="49">
@@ -3066,41 +3148,42 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>522.00</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>778.00</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>474.00</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>458.00</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
       <c r="L49" s="7" t="inlineStr"/>
-      <c r="M49" s="8" t="inlineStr"/>
-      <c r="N49" s="9" t="n">
-        <v>570</v>
-      </c>
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="9" t="n">
-        <v>26.66666666666663</v>
-      </c>
-      <c r="P49" s="10" t="n">
-        <v>-0.0006351278075626247</v>
+        <v>558</v>
+      </c>
+      <c r="P49" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q49" s="10" t="n">
+        <v>-0.001619575909284695</v>
       </c>
     </row>
     <row r="50">
@@ -3119,30 +3202,35 @@
           <t>6669.00</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>8446.00</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="3" t="n">
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="3" t="n">
         <v>7387</v>
       </c>
-      <c r="N50" s="4" t="n">
-        <v>4661.5</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>-2725.5</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v>-0.2442248068961809</v>
+      <c r="O50" s="4" t="n">
+        <v>5923</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>-1464</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>-0.1311851466872166</v>
       </c>
     </row>
     <row r="51">
@@ -3161,28 +3249,33 @@
           <t>4831.00</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>10098.00</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr"/>
       <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr"/>
-      <c r="M51" s="8" t="inlineStr"/>
-      <c r="N51" s="9" t="n">
-        <v>5158.5</v>
-      </c>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="9" t="n">
-        <v>497</v>
-      </c>
-      <c r="P51" s="10" t="n">
-        <v>0.04453484829477231</v>
+        <v>6805</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>882</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>0.07903367443861001</v>
       </c>
     </row>
   </sheetData>
@@ -3197,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3362,7 +3455,7 @@
       <c r="O2" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P2" s="12" t="n">
+      <c r="P2" s="13" t="n">
         <v>46277.48542824074</v>
       </c>
     </row>
@@ -3432,7 +3525,7 @@
       <c r="O3" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P3" s="12" t="n">
+      <c r="P3" s="13" t="n">
         <v>46277.51052083333</v>
       </c>
     </row>
@@ -3502,7 +3595,7 @@
       <c r="O4" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="13" t="n">
         <v>46277.51194444444</v>
       </c>
     </row>
@@ -3572,7 +3665,7 @@
       <c r="O5" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="13" t="n">
         <v>46277.58818287037</v>
       </c>
     </row>
@@ -3642,7 +3735,7 @@
       <c r="O6" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="13" t="n">
         <v>46277.5909375</v>
       </c>
     </row>
@@ -3708,7 +3801,7 @@
       <c r="O7" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="13" t="n">
         <v>46277.63061342593</v>
       </c>
     </row>
@@ -3774,7 +3867,7 @@
       <c r="O8" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="13" t="n">
         <v>46277.66618055556</v>
       </c>
     </row>
@@ -3844,7 +3937,7 @@
       <c r="O9" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="13" t="n">
         <v>46277.78224537037</v>
       </c>
     </row>
@@ -3914,7 +4007,7 @@
       <c r="O10" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="13" t="n">
         <v>46277.79376157407</v>
       </c>
     </row>
@@ -3980,7 +4073,7 @@
       <c r="O11" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="13" t="n">
         <v>46277.83049768519</v>
       </c>
     </row>
@@ -4050,7 +4143,7 @@
       <c r="O12" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P12" s="12" t="n">
+      <c r="P12" s="13" t="n">
         <v>46277.86043981482</v>
       </c>
     </row>
@@ -4120,7 +4213,7 @@
       <c r="O13" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" s="13" t="n">
         <v>46277.87179398148</v>
       </c>
     </row>
@@ -4190,7 +4283,7 @@
       <c r="O14" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" s="13" t="n">
         <v>46278.05765046296</v>
       </c>
     </row>
@@ -4260,7 +4353,7 @@
       <c r="O15" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="13" t="n">
         <v>46278.06443287037</v>
       </c>
     </row>
@@ -4330,7 +4423,7 @@
       <c r="O16" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P16" s="13" t="n">
         <v>46278.08553240741</v>
       </c>
     </row>
@@ -4400,7 +4493,7 @@
       <c r="O17" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P17" s="13" t="n">
         <v>46278.08700231482</v>
       </c>
     </row>
@@ -4470,7 +4563,7 @@
       <c r="O18" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="13" t="n">
         <v>46278.08775462963</v>
       </c>
     </row>
@@ -4540,7 +4633,7 @@
       <c r="O19" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P19" s="12" t="n">
+      <c r="P19" s="13" t="n">
         <v>46278.21667824074</v>
       </c>
     </row>
@@ -4610,7 +4703,7 @@
       <c r="O20" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P20" s="13" t="n">
         <v>46278.24315972222</v>
       </c>
     </row>
@@ -4680,7 +4773,7 @@
       <c r="O21" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="13" t="n">
         <v>46278.26704861111</v>
       </c>
     </row>
@@ -4750,7 +4843,7 @@
       <c r="O22" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P22" s="12" t="n">
+      <c r="P22" s="13" t="n">
         <v>46278.26740740741</v>
       </c>
     </row>
@@ -4820,7 +4913,7 @@
       <c r="O23" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P23" s="12" t="n">
+      <c r="P23" s="13" t="n">
         <v>46278.27628472223</v>
       </c>
     </row>
@@ -4890,7 +4983,7 @@
       <c r="O24" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P24" s="12" t="n">
+      <c r="P24" s="13" t="n">
         <v>46278.27751157407</v>
       </c>
     </row>
@@ -4960,7 +5053,7 @@
       <c r="O25" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P25" s="12" t="n">
+      <c r="P25" s="13" t="n">
         <v>46278.29635416667</v>
       </c>
     </row>
@@ -5030,7 +5123,7 @@
       <c r="O26" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P26" s="12" t="n">
+      <c r="P26" s="13" t="n">
         <v>46278.35381944444</v>
       </c>
     </row>
@@ -5100,7 +5193,7 @@
       <c r="O27" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P27" s="12" t="n">
+      <c r="P27" s="13" t="n">
         <v>46278.35512731481</v>
       </c>
     </row>
@@ -5170,7 +5263,7 @@
       <c r="O28" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P28" s="12" t="n">
+      <c r="P28" s="13" t="n">
         <v>46278.4143287037</v>
       </c>
     </row>
@@ -5240,7 +5333,7 @@
       <c r="O29" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" s="13" t="n">
         <v>46278.49403935186</v>
       </c>
     </row>
@@ -5310,7 +5403,7 @@
       <c r="O30" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P30" s="12" t="n">
+      <c r="P30" s="13" t="n">
         <v>46278.65908564815</v>
       </c>
     </row>
@@ -5380,7 +5473,7 @@
       <c r="O31" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P31" s="12" t="n">
+      <c r="P31" s="13" t="n">
         <v>46278.67763888889</v>
       </c>
     </row>
@@ -5450,7 +5543,7 @@
       <c r="O32" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P32" s="12" t="n">
+      <c r="P32" s="13" t="n">
         <v>46278.69815972223</v>
       </c>
     </row>
@@ -5520,7 +5613,7 @@
       <c r="O33" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P33" s="12" t="n">
+      <c r="P33" s="13" t="n">
         <v>46278.72652777778</v>
       </c>
     </row>
@@ -5590,7 +5683,7 @@
       <c r="O34" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P34" s="12" t="n">
+      <c r="P34" s="13" t="n">
         <v>46278.84016203704</v>
       </c>
     </row>
@@ -5660,7 +5753,7 @@
       <c r="O35" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P35" s="12" t="n">
+      <c r="P35" s="13" t="n">
         <v>46278.85677083334</v>
       </c>
     </row>
@@ -5730,7 +5823,7 @@
       <c r="O36" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P36" s="12" t="n">
+      <c r="P36" s="13" t="n">
         <v>46278.8781712963</v>
       </c>
     </row>
@@ -5800,7 +5893,7 @@
       <c r="O37" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P37" s="12" t="n">
+      <c r="P37" s="13" t="n">
         <v>46278.90575231481</v>
       </c>
     </row>
@@ -5870,7 +5963,7 @@
       <c r="O38" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P38" s="12" t="n">
+      <c r="P38" s="13" t="n">
         <v>46278.94225694444</v>
       </c>
     </row>
@@ -5940,7 +6033,7 @@
       <c r="O39" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P39" s="12" t="n">
+      <c r="P39" s="13" t="n">
         <v>46279.06255787037</v>
       </c>
     </row>
@@ -6010,7 +6103,7 @@
       <c r="O40" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P40" s="12" t="n">
+      <c r="P40" s="13" t="n">
         <v>46279.09913194444</v>
       </c>
     </row>
@@ -6080,7 +6173,7 @@
       <c r="O41" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P41" s="12" t="n">
+      <c r="P41" s="13" t="n">
         <v>46279.15164351852</v>
       </c>
     </row>
@@ -6150,7 +6243,7 @@
       <c r="O42" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P42" s="12" t="n">
+      <c r="P42" s="13" t="n">
         <v>46279.15413194444</v>
       </c>
     </row>
@@ -6220,7 +6313,7 @@
       <c r="O43" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P43" s="12" t="n">
+      <c r="P43" s="13" t="n">
         <v>46279.17649305556</v>
       </c>
     </row>
@@ -6290,7 +6383,7 @@
       <c r="O44" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P44" s="12" t="n">
+      <c r="P44" s="13" t="n">
         <v>46279.22236111111</v>
       </c>
     </row>
@@ -6360,7 +6453,7 @@
       <c r="O45" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P45" s="12" t="n">
+      <c r="P45" s="13" t="n">
         <v>46279.23153935185</v>
       </c>
     </row>
@@ -6430,7 +6523,7 @@
       <c r="O46" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P46" s="12" t="n">
+      <c r="P46" s="13" t="n">
         <v>46279.2678125</v>
       </c>
     </row>
@@ -6500,7 +6593,7 @@
       <c r="O47" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P47" s="12" t="n">
+      <c r="P47" s="13" t="n">
         <v>46279.291875</v>
       </c>
     </row>
@@ -6570,7 +6663,7 @@
       <c r="O48" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P48" s="12" t="n">
+      <c r="P48" s="13" t="n">
         <v>46279.29552083334</v>
       </c>
     </row>
@@ -6640,7 +6733,7 @@
       <c r="O49" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P49" s="12" t="n">
+      <c r="P49" s="13" t="n">
         <v>46279.32731481481</v>
       </c>
     </row>
@@ -6710,7 +6803,7 @@
       <c r="O50" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P50" s="12" t="n">
+      <c r="P50" s="13" t="n">
         <v>46279.37328703704</v>
       </c>
     </row>
@@ -6780,7 +6873,7 @@
       <c r="O51" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P51" s="12" t="n">
+      <c r="P51" s="13" t="n">
         <v>46279.41740740741</v>
       </c>
     </row>
@@ -6850,7 +6943,7 @@
       <c r="O52" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P52" s="13" t="n">
         <v>46279.45078703704</v>
       </c>
     </row>
@@ -6920,7 +7013,7 @@
       <c r="O53" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P53" s="12" t="n">
+      <c r="P53" s="13" t="n">
         <v>46279.47466435185</v>
       </c>
     </row>
@@ -6990,7 +7083,7 @@
       <c r="O54" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P54" s="13" t="n">
         <v>46279.49469907407</v>
       </c>
     </row>
@@ -7060,7 +7153,7 @@
       <c r="O55" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P55" s="12" t="n">
+      <c r="P55" s="13" t="n">
         <v>46279.50685185185</v>
       </c>
     </row>
@@ -7130,7 +7223,7 @@
       <c r="O56" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P56" s="13" t="n">
         <v>46279.58126157407</v>
       </c>
     </row>
@@ -7200,7 +7293,7 @@
       <c r="O57" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P57" s="12" t="n">
+      <c r="P57" s="13" t="n">
         <v>46279.62493055555</v>
       </c>
     </row>
@@ -7270,7 +7363,7 @@
       <c r="O58" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P58" s="12" t="n">
+      <c r="P58" s="13" t="n">
         <v>46279.64979166666</v>
       </c>
     </row>
@@ -7340,7 +7433,7 @@
       <c r="O59" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P59" s="12" t="n">
+      <c r="P59" s="13" t="n">
         <v>46279.67836805555</v>
       </c>
     </row>
@@ -7410,7 +7503,7 @@
       <c r="O60" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P60" s="12" t="n">
+      <c r="P60" s="13" t="n">
         <v>46279.68984953704</v>
       </c>
     </row>
@@ -7480,7 +7573,7 @@
       <c r="O61" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P61" s="12" t="n">
+      <c r="P61" s="13" t="n">
         <v>46279.75571759259</v>
       </c>
     </row>
@@ -7550,7 +7643,7 @@
       <c r="O62" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P62" s="13" t="n">
         <v>46279.76197916667</v>
       </c>
     </row>
@@ -7620,7 +7713,7 @@
       <c r="O63" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P63" s="12" t="n">
+      <c r="P63" s="13" t="n">
         <v>46279.82975694445</v>
       </c>
     </row>
@@ -7690,7 +7783,7 @@
       <c r="O64" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P64" s="13" t="n">
         <v>46279.83283564815</v>
       </c>
     </row>
@@ -7760,7 +7853,7 @@
       <c r="O65" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P65" s="12" t="n">
+      <c r="P65" s="13" t="n">
         <v>46279.86658564815</v>
       </c>
     </row>
@@ -7830,7 +7923,7 @@
       <c r="O66" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P66" s="12" t="n">
+      <c r="P66" s="13" t="n">
         <v>46279.86854166666</v>
       </c>
     </row>
@@ -7900,7 +7993,7 @@
       <c r="O67" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P67" s="12" t="n">
+      <c r="P67" s="13" t="n">
         <v>46279.88961805555</v>
       </c>
     </row>
@@ -7970,7 +8063,7 @@
       <c r="O68" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P68" s="12" t="n">
+      <c r="P68" s="13" t="n">
         <v>46279.92807870371</v>
       </c>
     </row>
@@ -8040,7 +8133,7 @@
       <c r="O69" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P69" s="12" t="n">
+      <c r="P69" s="13" t="n">
         <v>46279.95943287037</v>
       </c>
     </row>
@@ -8110,7 +8203,7 @@
       <c r="O70" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P70" s="13" t="n">
         <v>46280.03707175926</v>
       </c>
     </row>
@@ -8180,7 +8273,7 @@
       <c r="O71" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P71" s="12" t="n">
+      <c r="P71" s="13" t="n">
         <v>46280.04559027778</v>
       </c>
     </row>
@@ -8250,7 +8343,7 @@
       <c r="O72" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P72" s="13" t="n">
         <v>46280.05359953704</v>
       </c>
     </row>
@@ -8320,7 +8413,7 @@
       <c r="O73" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P73" s="12" t="n">
+      <c r="P73" s="13" t="n">
         <v>46280.10788194444</v>
       </c>
     </row>
@@ -8390,7 +8483,7 @@
       <c r="O74" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P74" s="13" t="n">
         <v>46280.1452199074</v>
       </c>
     </row>
@@ -8460,7 +8553,7 @@
       <c r="O75" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P75" s="12" t="n">
+      <c r="P75" s="13" t="n">
         <v>46280.19780092593</v>
       </c>
     </row>
@@ -8530,7 +8623,7 @@
       <c r="O76" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P76" s="13" t="n">
         <v>46280.24451388889</v>
       </c>
     </row>
@@ -8600,7 +8693,7 @@
       <c r="O77" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P77" s="12" t="n">
+      <c r="P77" s="13" t="n">
         <v>46280.24539351852</v>
       </c>
     </row>
@@ -8670,7 +8763,7 @@
       <c r="O78" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P78" s="13" t="n">
         <v>46280.27893518518</v>
       </c>
     </row>
@@ -8740,7 +8833,7 @@
       <c r="O79" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P79" s="12" t="n">
+      <c r="P79" s="13" t="n">
         <v>46280.31445601852</v>
       </c>
     </row>
@@ -8810,7 +8903,7 @@
       <c r="O80" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P80" s="12" t="n">
+      <c r="P80" s="13" t="n">
         <v>46280.35971064815</v>
       </c>
     </row>
@@ -8880,7 +8973,7 @@
       <c r="O81" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P81" s="12" t="n">
+      <c r="P81" s="13" t="n">
         <v>46280.39851851852</v>
       </c>
     </row>
@@ -8950,7 +9043,7 @@
       <c r="O82" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P82" s="12" t="n">
+      <c r="P82" s="13" t="n">
         <v>46280.41853009259</v>
       </c>
     </row>
@@ -9020,7 +9113,7 @@
       <c r="O83" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P83" s="12" t="n">
+      <c r="P83" s="13" t="n">
         <v>46280.44364583334</v>
       </c>
     </row>
@@ -9090,7 +9183,7 @@
       <c r="O84" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P84" s="12" t="n">
+      <c r="P84" s="13" t="n">
         <v>46280.4897337963</v>
       </c>
     </row>
@@ -9160,7 +9253,7 @@
       <c r="O85" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P85" s="12" t="n">
+      <c r="P85" s="13" t="n">
         <v>46280.50119212963</v>
       </c>
     </row>
@@ -9230,7 +9323,7 @@
       <c r="O86" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P86" s="13" t="n">
         <v>46280.5120949074</v>
       </c>
     </row>
@@ -9300,7 +9393,7 @@
       <c r="O87" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P87" s="12" t="n">
+      <c r="P87" s="13" t="n">
         <v>46280.51324074074</v>
       </c>
     </row>
@@ -9370,7 +9463,7 @@
       <c r="O88" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P88" s="12" t="n">
+      <c r="P88" s="13" t="n">
         <v>46280.52025462963</v>
       </c>
     </row>
@@ -9440,7 +9533,7 @@
       <c r="O89" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P89" s="12" t="n">
+      <c r="P89" s="13" t="n">
         <v>46280.54377314815</v>
       </c>
     </row>
@@ -9510,7 +9603,7 @@
       <c r="O90" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P90" s="12" t="n">
+      <c r="P90" s="13" t="n">
         <v>46280.59976851852</v>
       </c>
     </row>
@@ -9580,7 +9673,7 @@
       <c r="O91" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P91" s="12" t="n">
+      <c r="P91" s="13" t="n">
         <v>46280.61607638889</v>
       </c>
     </row>
@@ -9650,7 +9743,7 @@
       <c r="O92" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P92" s="12" t="n">
+      <c r="P92" s="13" t="n">
         <v>46280.68962962963</v>
       </c>
     </row>
@@ -9720,7 +9813,7 @@
       <c r="O93" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P93" s="12" t="n">
+      <c r="P93" s="13" t="n">
         <v>46280.71888888889</v>
       </c>
     </row>
@@ -9790,7 +9883,7 @@
       <c r="O94" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P94" s="12" t="n">
+      <c r="P94" s="13" t="n">
         <v>46280.74344907407</v>
       </c>
     </row>
@@ -9860,7 +9953,7 @@
       <c r="O95" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P95" s="12" t="n">
+      <c r="P95" s="13" t="n">
         <v>46280.77847222222</v>
       </c>
     </row>
@@ -9930,7 +10023,7 @@
       <c r="O96" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P96" s="12" t="n">
+      <c r="P96" s="13" t="n">
         <v>46280.84616898148</v>
       </c>
     </row>
@@ -10000,7 +10093,7 @@
       <c r="O97" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P97" s="12" t="n">
+      <c r="P97" s="13" t="n">
         <v>46280.86395833334</v>
       </c>
     </row>
@@ -10070,7 +10163,7 @@
       <c r="O98" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P98" s="12" t="n">
+      <c r="P98" s="13" t="n">
         <v>46280.89765046296</v>
       </c>
     </row>
@@ -10140,7 +10233,7 @@
       <c r="O99" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P99" s="12" t="n">
+      <c r="P99" s="13" t="n">
         <v>46280.90140046296</v>
       </c>
     </row>
@@ -10210,7 +10303,7 @@
       <c r="O100" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P100" s="12" t="n">
+      <c r="P100" s="13" t="n">
         <v>46280.92248842592</v>
       </c>
     </row>
@@ -10280,7 +10373,7 @@
       <c r="O101" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P101" s="12" t="n">
+      <c r="P101" s="13" t="n">
         <v>46280.94780092593</v>
       </c>
     </row>
@@ -10350,7 +10443,7 @@
       <c r="O102" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P102" s="12" t="n">
+      <c r="P102" s="13" t="n">
         <v>46281.03773148148</v>
       </c>
     </row>
@@ -10420,7 +10513,7 @@
       <c r="O103" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P103" s="12" t="n">
+      <c r="P103" s="13" t="n">
         <v>46281.05363425926</v>
       </c>
     </row>
@@ -10490,7 +10583,7 @@
       <c r="O104" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P104" s="12" t="n">
+      <c r="P104" s="13" t="n">
         <v>46281.17542824074</v>
       </c>
     </row>
@@ -10560,7 +10653,7 @@
       <c r="O105" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P105" s="12" t="n">
+      <c r="P105" s="13" t="n">
         <v>46281.23145833334</v>
       </c>
     </row>
@@ -10630,7 +10723,7 @@
       <c r="O106" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P106" s="12" t="n">
+      <c r="P106" s="13" t="n">
         <v>46281.26112268519</v>
       </c>
     </row>
@@ -10700,7 +10793,7 @@
       <c r="O107" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P107" s="12" t="n">
+      <c r="P107" s="13" t="n">
         <v>46281.34596064815</v>
       </c>
     </row>
@@ -10770,7 +10863,7 @@
       <c r="O108" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P108" s="12" t="n">
+      <c r="P108" s="13" t="n">
         <v>46281.41318287037</v>
       </c>
     </row>
@@ -10840,7 +10933,7 @@
       <c r="O109" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P109" s="12" t="n">
+      <c r="P109" s="13" t="n">
         <v>46281.47984953703</v>
       </c>
     </row>
@@ -10910,7 +11003,7 @@
       <c r="O110" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P110" s="12" t="n">
+      <c r="P110" s="13" t="n">
         <v>46281.48199074074</v>
       </c>
     </row>
@@ -10980,7 +11073,7 @@
       <c r="O111" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P111" s="12" t="n">
+      <c r="P111" s="13" t="n">
         <v>46281.55998842593</v>
       </c>
     </row>
@@ -11050,7 +11143,7 @@
       <c r="O112" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P112" s="12" t="n">
+      <c r="P112" s="13" t="n">
         <v>46281.56878472222</v>
       </c>
     </row>
@@ -11120,7 +11213,7 @@
       <c r="O113" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P113" s="12" t="n">
+      <c r="P113" s="13" t="n">
         <v>46281.60291666666</v>
       </c>
     </row>
@@ -11190,7 +11283,7 @@
       <c r="O114" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P114" s="12" t="n">
+      <c r="P114" s="13" t="n">
         <v>46281.60375</v>
       </c>
     </row>
@@ -11260,7 +11353,7 @@
       <c r="O115" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P115" s="12" t="n">
+      <c r="P115" s="13" t="n">
         <v>46281.61435185185</v>
       </c>
     </row>
@@ -11330,7 +11423,7 @@
       <c r="O116" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P116" s="12" t="n">
+      <c r="P116" s="13" t="n">
         <v>46281.64665509259</v>
       </c>
     </row>
@@ -11400,7 +11493,7 @@
       <c r="O117" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P117" s="12" t="n">
+      <c r="P117" s="13" t="n">
         <v>46281.67173611111</v>
       </c>
     </row>
@@ -11470,7 +11563,7 @@
       <c r="O118" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P118" s="12" t="n">
+      <c r="P118" s="13" t="n">
         <v>46281.72890046296</v>
       </c>
     </row>
@@ -11540,7 +11633,7 @@
       <c r="O119" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P119" s="12" t="n">
+      <c r="P119" s="13" t="n">
         <v>46281.7578587963</v>
       </c>
     </row>
@@ -11610,7 +11703,7 @@
       <c r="O120" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P120" s="12" t="n">
+      <c r="P120" s="13" t="n">
         <v>46281.80134259259</v>
       </c>
     </row>
@@ -11680,7 +11773,7 @@
       <c r="O121" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P121" s="12" t="n">
+      <c r="P121" s="13" t="n">
         <v>46281.85913194445</v>
       </c>
     </row>
@@ -11750,7 +11843,7 @@
       <c r="O122" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P122" s="12" t="n">
+      <c r="P122" s="13" t="n">
         <v>46281.86515046296</v>
       </c>
     </row>
@@ -11820,7 +11913,7 @@
       <c r="O123" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P123" s="12" t="n">
+      <c r="P123" s="13" t="n">
         <v>46281.93247685185</v>
       </c>
     </row>
@@ -11890,7 +11983,7 @@
       <c r="O124" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P124" s="12" t="n">
+      <c r="P124" s="13" t="n">
         <v>46281.96268518519</v>
       </c>
     </row>
@@ -11960,7 +12053,7 @@
       <c r="O125" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P125" s="12" t="n">
+      <c r="P125" s="13" t="n">
         <v>46281.96670138889</v>
       </c>
     </row>
@@ -12030,7 +12123,7 @@
       <c r="O126" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P126" s="12" t="n">
+      <c r="P126" s="13" t="n">
         <v>46282.01916666667</v>
       </c>
     </row>
@@ -12100,7 +12193,7 @@
       <c r="O127" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P127" s="12" t="n">
+      <c r="P127" s="13" t="n">
         <v>46282.07037037037</v>
       </c>
     </row>
@@ -12170,7 +12263,7 @@
       <c r="O128" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P128" s="12" t="n">
+      <c r="P128" s="13" t="n">
         <v>46282.08375</v>
       </c>
     </row>
@@ -12240,7 +12333,7 @@
       <c r="O129" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P129" s="12" t="n">
+      <c r="P129" s="13" t="n">
         <v>46282.14739583333</v>
       </c>
     </row>
@@ -12310,7 +12403,7 @@
       <c r="O130" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P130" s="12" t="n">
+      <c r="P130" s="13" t="n">
         <v>46282.15549768518</v>
       </c>
     </row>
@@ -12380,7 +12473,7 @@
       <c r="O131" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P131" s="12" t="n">
+      <c r="P131" s="13" t="n">
         <v>46282.16440972222</v>
       </c>
     </row>
@@ -12450,7 +12543,7 @@
       <c r="O132" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P132" s="12" t="n">
+      <c r="P132" s="13" t="n">
         <v>46282.18530092593</v>
       </c>
     </row>
@@ -12520,7 +12613,7 @@
       <c r="O133" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P133" s="12" t="n">
+      <c r="P133" s="13" t="n">
         <v>46282.21564814815</v>
       </c>
     </row>
@@ -12590,7 +12683,7 @@
       <c r="O134" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P134" s="12" t="n">
+      <c r="P134" s="13" t="n">
         <v>46282.2421412037</v>
       </c>
     </row>
@@ -12660,7 +12753,7 @@
       <c r="O135" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P135" s="12" t="n">
+      <c r="P135" s="13" t="n">
         <v>46282.32163194445</v>
       </c>
     </row>
@@ -12730,7 +12823,7 @@
       <c r="O136" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P136" s="12" t="n">
+      <c r="P136" s="13" t="n">
         <v>46282.33078703703</v>
       </c>
     </row>
@@ -12800,7 +12893,7 @@
       <c r="O137" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P137" s="12" t="n">
+      <c r="P137" s="13" t="n">
         <v>46282.36037037037</v>
       </c>
     </row>
@@ -12870,7 +12963,7 @@
       <c r="O138" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P138" s="12" t="n">
+      <c r="P138" s="13" t="n">
         <v>46282.3647337963</v>
       </c>
     </row>
@@ -12940,7 +13033,7 @@
       <c r="O139" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P139" s="12" t="n">
+      <c r="P139" s="13" t="n">
         <v>46282.38931712963</v>
       </c>
     </row>
@@ -13010,7 +13103,7 @@
       <c r="O140" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P140" s="12" t="n">
+      <c r="P140" s="13" t="n">
         <v>46282.3912037037</v>
       </c>
     </row>
@@ -13080,7 +13173,7 @@
       <c r="O141" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P141" s="12" t="n">
+      <c r="P141" s="13" t="n">
         <v>46282.4034375</v>
       </c>
     </row>
@@ -13150,7 +13243,7 @@
       <c r="O142" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P142" s="12" t="n">
+      <c r="P142" s="13" t="n">
         <v>46282.43136574074</v>
       </c>
     </row>
@@ -13220,7 +13313,7 @@
       <c r="O143" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P143" s="12" t="n">
+      <c r="P143" s="13" t="n">
         <v>46282.49684027778</v>
       </c>
     </row>
@@ -13290,7 +13383,7 @@
       <c r="O144" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P144" s="12" t="n">
+      <c r="P144" s="13" t="n">
         <v>46282.51994212963</v>
       </c>
     </row>
@@ -13360,7 +13453,7 @@
       <c r="O145" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P145" s="12" t="n">
+      <c r="P145" s="13" t="n">
         <v>46282.62939814815</v>
       </c>
     </row>
@@ -13430,7 +13523,7 @@
       <c r="O146" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P146" s="12" t="n">
+      <c r="P146" s="13" t="n">
         <v>46282.6515162037</v>
       </c>
     </row>
@@ -13500,7 +13593,7 @@
       <c r="O147" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P147" s="12" t="n">
+      <c r="P147" s="13" t="n">
         <v>46282.78369212963</v>
       </c>
     </row>
@@ -13570,7 +13663,7 @@
       <c r="O148" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P148" s="12" t="n">
+      <c r="P148" s="13" t="n">
         <v>46282.78776620371</v>
       </c>
     </row>
@@ -13640,7 +13733,7 @@
       <c r="O149" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P149" s="12" t="n">
+      <c r="P149" s="13" t="n">
         <v>46282.91478009259</v>
       </c>
     </row>
@@ -13710,7 +13803,7 @@
       <c r="O150" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P150" s="12" t="n">
+      <c r="P150" s="13" t="n">
         <v>46282.94171296297</v>
       </c>
     </row>
@@ -13780,7 +13873,7 @@
       <c r="O151" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P151" s="12" t="n">
+      <c r="P151" s="13" t="n">
         <v>46283.06856481481</v>
       </c>
     </row>
@@ -13850,7 +13943,7 @@
       <c r="O152" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P152" s="12" t="n">
+      <c r="P152" s="13" t="n">
         <v>46283.0745949074</v>
       </c>
     </row>
@@ -13920,7 +14013,7 @@
       <c r="O153" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P153" s="12" t="n">
+      <c r="P153" s="13" t="n">
         <v>46283.19665509259</v>
       </c>
     </row>
@@ -13990,7 +14083,7 @@
       <c r="O154" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P154" s="12" t="n">
+      <c r="P154" s="13" t="n">
         <v>46283.22854166666</v>
       </c>
     </row>
@@ -14060,7 +14153,7 @@
       <c r="O155" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P155" s="12" t="n">
+      <c r="P155" s="13" t="n">
         <v>46283.33405092593</v>
       </c>
     </row>
@@ -14130,7 +14223,7 @@
       <c r="O156" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P156" s="12" t="n">
+      <c r="P156" s="13" t="n">
         <v>46283.35032407408</v>
       </c>
     </row>
@@ -14200,7 +14293,7 @@
       <c r="O157" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P157" s="12" t="n">
+      <c r="P157" s="13" t="n">
         <v>46283.48784722222</v>
       </c>
     </row>
@@ -14270,7 +14363,7 @@
       <c r="O158" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P158" s="12" t="n">
+      <c r="P158" s="13" t="n">
         <v>46283.508125</v>
       </c>
     </row>
@@ -14340,7 +14433,7 @@
       <c r="O159" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P159" s="12" t="n">
+      <c r="P159" s="13" t="n">
         <v>46283.64868055555</v>
       </c>
     </row>
@@ -14410,7 +14503,7 @@
       <c r="O160" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P160" s="12" t="n">
+      <c r="P160" s="13" t="n">
         <v>46283.6619212963</v>
       </c>
     </row>
@@ -14480,7 +14573,7 @@
       <c r="O161" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P161" s="12" t="n">
+      <c r="P161" s="13" t="n">
         <v>46283.76673611111</v>
       </c>
     </row>
@@ -14550,7 +14643,7 @@
       <c r="O162" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P162" s="12" t="n">
+      <c r="P162" s="13" t="n">
         <v>46283.8025</v>
       </c>
     </row>
@@ -14620,7 +14713,7 @@
       <c r="O163" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P163" s="12" t="n">
+      <c r="P163" s="13" t="n">
         <v>46283.92071759259</v>
       </c>
     </row>
@@ -14690,7 +14783,7 @@
       <c r="O164" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P164" s="12" t="n">
+      <c r="P164" s="13" t="n">
         <v>46283.94190972222</v>
       </c>
     </row>
@@ -14760,7 +14853,7 @@
       <c r="O165" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P165" s="12" t="n">
+      <c r="P165" s="13" t="n">
         <v>46284.05696759259</v>
       </c>
     </row>
@@ -14830,7 +14923,7 @@
       <c r="O166" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P166" s="12" t="n">
+      <c r="P166" s="13" t="n">
         <v>46284.09695601852</v>
       </c>
     </row>
@@ -14900,7 +14993,7 @@
       <c r="O167" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P167" s="12" t="n">
+      <c r="P167" s="13" t="n">
         <v>46284.21068287037</v>
       </c>
     </row>
@@ -14970,7 +15063,7 @@
       <c r="O168" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P168" s="12" t="n">
+      <c r="P168" s="13" t="n">
         <v>46284.24060185185</v>
       </c>
     </row>
@@ -15040,7 +15133,7 @@
       <c r="O169" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P169" s="12" t="n">
+      <c r="P169" s="13" t="n">
         <v>46284.33123842593</v>
       </c>
     </row>
@@ -15110,7 +15203,7 @@
       <c r="O170" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P170" s="12" t="n">
+      <c r="P170" s="13" t="n">
         <v>46284.3950462963</v>
       </c>
     </row>
@@ -15180,7 +15273,7 @@
       <c r="O171" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P171" s="12" t="n">
+      <c r="P171" s="13" t="n">
         <v>46284.48659722223</v>
       </c>
     </row>
@@ -15250,7 +15343,7 @@
       <c r="O172" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P172" s="12" t="n">
+      <c r="P172" s="13" t="n">
         <v>46284.51091435185</v>
       </c>
     </row>
@@ -15320,7 +15413,7 @@
       <c r="O173" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P173" s="12" t="n">
+      <c r="P173" s="13" t="n">
         <v>46284.61217592593</v>
       </c>
     </row>
@@ -15390,7 +15483,7 @@
       <c r="O174" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P174" s="12" t="n">
+      <c r="P174" s="13" t="n">
         <v>46284.63247685185</v>
       </c>
     </row>
@@ -15460,7 +15553,7 @@
       <c r="O175" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P175" s="12" t="n">
+      <c r="P175" s="13" t="n">
         <v>46284.66641203704</v>
       </c>
     </row>
@@ -15530,7 +15623,7 @@
       <c r="O176" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P176" s="12" t="n">
+      <c r="P176" s="13" t="n">
         <v>46284.76607638889</v>
       </c>
     </row>
@@ -15600,7 +15693,7 @@
       <c r="O177" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P177" s="12" t="n">
+      <c r="P177" s="13" t="n">
         <v>46284.78469907407</v>
       </c>
     </row>
@@ -15670,7 +15763,7 @@
       <c r="O178" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P178" s="12" t="n">
+      <c r="P178" s="13" t="n">
         <v>46284.895</v>
       </c>
     </row>
@@ -15740,7 +15833,7 @@
       <c r="O179" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P179" s="12" t="n">
+      <c r="P179" s="13" t="n">
         <v>46284.93909722222</v>
       </c>
     </row>
@@ -15810,7 +15903,7 @@
       <c r="O180" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P180" s="12" t="n">
+      <c r="P180" s="13" t="n">
         <v>46284.99038194444</v>
       </c>
     </row>
@@ -15880,7 +15973,7 @@
       <c r="O181" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P181" s="12" t="n">
+      <c r="P181" s="13" t="n">
         <v>46285.02277777778</v>
       </c>
     </row>
@@ -15950,7 +16043,7 @@
       <c r="O182" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P182" s="12" t="n">
+      <c r="P182" s="13" t="n">
         <v>46285.04913194444</v>
       </c>
     </row>
@@ -16020,7 +16113,7 @@
       <c r="O183" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P183" s="12" t="n">
+      <c r="P183" s="13" t="n">
         <v>46285.16568287037</v>
       </c>
     </row>
@@ -16090,7 +16183,7 @@
       <c r="O184" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P184" s="12" t="n">
+      <c r="P184" s="13" t="n">
         <v>46285.31915509259</v>
       </c>
     </row>
@@ -16160,7 +16253,7 @@
       <c r="O185" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P185" s="12" t="n">
+      <c r="P185" s="13" t="n">
         <v>46285.38929398148</v>
       </c>
     </row>
@@ -16230,7 +16323,7 @@
       <c r="O186" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P186" s="12" t="n">
+      <c r="P186" s="13" t="n">
         <v>46285.45016203704</v>
       </c>
     </row>
@@ -16300,7 +16393,7 @@
       <c r="O187" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P187" s="12" t="n">
+      <c r="P187" s="13" t="n">
         <v>46285.60445601852</v>
       </c>
     </row>
@@ -16370,7 +16463,7 @@
       <c r="O188" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P188" s="12" t="n">
+      <c r="P188" s="13" t="n">
         <v>46285.70131944444</v>
       </c>
     </row>
@@ -16440,7 +16533,7 @@
       <c r="O189" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P189" s="12" t="n">
+      <c r="P189" s="13" t="n">
         <v>46285.73811342593</v>
       </c>
     </row>
@@ -16510,7 +16603,7 @@
       <c r="O190" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P190" s="12" t="n">
+      <c r="P190" s="13" t="n">
         <v>46285.89204861111</v>
       </c>
     </row>
@@ -16580,132 +16673,762 @@
       <c r="O191" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P191" s="12" t="n">
+      <c r="P191" s="13" t="n">
         <v>46286.04180555556</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="13" t="inlineStr">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>Mamba2_AC_MsPacman_seed2000_O</t>
         </is>
       </c>
-      <c r="B192" s="13" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>hywaxnxu</t>
         </is>
       </c>
-      <c r="C192" s="13" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="inlineStr">
+        <is>
+          <t>2322.00</t>
+        </is>
+      </c>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="K192" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L192" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M192" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N192" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O192" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P192" s="13" t="n">
+        <v>46286.10230324074</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed710_O</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>j0q6krva</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I193" s="7" t="inlineStr">
+        <is>
+          <t>522.00</t>
+        </is>
+      </c>
+      <c r="J193" s="7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K193" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M193" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N193" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O193" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P193" s="13" t="n">
+        <v>46286.19703703704</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Seaquest_seed710_X</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>3llt8c9p</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Seaquest</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="n">
+        <v>710</v>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>714.00</t>
+        </is>
+      </c>
+      <c r="J194" s="7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="K194" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M194" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N194" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O194" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P194" s="13" t="n">
+        <v>46286.34505787037</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_MsPacman_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>66zrs3gp</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>MsPacman</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>2094.00</t>
+        </is>
+      </c>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="K195" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M195" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N195" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O195" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P195" s="13" t="n">
+        <v>46286.38792824074</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_UpNDown_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>4g4blfag</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>10098.00</t>
+        </is>
+      </c>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="K196" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M196" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N196" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O196" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P196" s="13" t="n">
+        <v>46286.49905092592</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_UpNDown_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>czoxatz9</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>8446.00</t>
+        </is>
+      </c>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="K197" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M197" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N197" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O197" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P197" s="13" t="n">
+        <v>46286.64550925926</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>l7rgmwuu</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="K198" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M198" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N198" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O198" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P198" s="13" t="n">
+        <v>46286.79150462963</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>gx78qi0n</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I199" s="7" t="inlineStr">
+        <is>
+          <t>2260.00</t>
+        </is>
+      </c>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K199" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N199" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O199" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P199" s="13" t="n">
+        <v>46286.79928240741</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_ChopperCommand_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>z0y36x76</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>ChopperCommand</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="inlineStr">
+        <is>
+          <t>1450.00</t>
+        </is>
+      </c>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="K200" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N200" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O200" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P200" s="13" t="n">
+        <v>46286.94260416667</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="14" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_PrivateEye_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B201" s="14" t="inlineStr">
+        <is>
+          <t>ehm7pwb2</t>
+        </is>
+      </c>
+      <c r="C201" s="14" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D192" s="13" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E192" s="13" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F192" s="13" t="inlineStr">
-        <is>
-          <t>MsPacman</t>
-        </is>
-      </c>
-      <c r="G192" s="13" t="n">
+      <c r="D201" s="14" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E201" s="14" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F201" s="14" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G201" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="H192" s="13" t="inlineStr">
+      <c r="H201" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I201" s="14" t="inlineStr"/>
+      <c r="J201" s="14" t="inlineStr"/>
+      <c r="K201" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L201" s="14" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M201" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N201" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="O201" s="14" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P201" s="15" t="n">
+        <v>46286.99332175926</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Jamesbond_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>xv97695u</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E202" s="14" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F202" s="14" t="inlineStr">
+        <is>
+          <t>Jamesbond</t>
+        </is>
+      </c>
+      <c r="G202" s="14" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H202" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I192" s="13" t="inlineStr"/>
-      <c r="J192" s="13" t="inlineStr"/>
-      <c r="K192" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L192" s="13" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M192" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N192" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="O192" s="13" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P192" s="14" t="n">
-        <v>46286.10230324074</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="13" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Seaquest_seed710_O</t>
-        </is>
-      </c>
-      <c r="B193" s="13" t="inlineStr">
-        <is>
-          <t>j0q6krva</t>
-        </is>
-      </c>
-      <c r="C193" s="13" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D193" s="13" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E193" s="13" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F193" s="13" t="inlineStr">
-        <is>
-          <t>Seaquest</t>
-        </is>
-      </c>
-      <c r="G193" s="13" t="n">
-        <v>710</v>
-      </c>
-      <c r="H193" s="13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I193" s="13" t="inlineStr"/>
-      <c r="J193" s="13" t="inlineStr"/>
-      <c r="K193" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L193" s="13" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M193" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N193" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="O193" s="13" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P193" s="14" t="n">
-        <v>46286.19703703704</v>
+      <c r="I202" s="14" t="inlineStr"/>
+      <c r="J202" s="14" t="inlineStr"/>
+      <c r="K202" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L202" s="14" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M202" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N202" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="O202" s="14" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P202" s="15" t="n">
+        <v>46287.09914351852</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="167" formatCode="+0.0000;-0.0000;0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +49,14 @@
       <color rgb="009C6500"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +66,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -121,10 +132,13 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,10 +286,31 @@
 Human: 753.1</t>
       </text>
     </comment>
+    <comment ref="G12" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>Random: 2360.0
 Human: 37187.5</t>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: BattleZone, seed 2710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 2710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="N14" authorId="0" shapeId="0">
@@ -284,16 +319,37 @@
 Human: 12.1</t>
       </text>
     </comment>
+    <comment ref="G15" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 2710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>Random: 1.7
 Human: 30.5</t>
       </text>
     </comment>
+    <comment ref="D18" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: ChopperCommand, seed 1710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
         <t>Random: 811.0
 Human: 7387.8</t>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: ChopperCommand, seed 1710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="N20" authorId="0" shapeId="0">
@@ -308,10 +364,24 @@
 Human: 1971.0</t>
       </text>
     </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>Random: 65.2
 Human: 4334.7</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Frostbite, seed 710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="N26" authorId="0" shapeId="0">
@@ -320,16 +390,44 @@
 Human: 2412.5</t>
       </text>
     </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Hero, seed 2010
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>Random: 1027.0
 Human: 30826.4</t>
       </text>
     </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Hero, seed 2010
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="E30" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Jamesbond, seed 2000
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>Random: 29.0
 Human: 302.8</t>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Jamesbond, seed 2000
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="N32" authorId="0" shapeId="0">
@@ -1297,7 +1395,11 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>8100.00</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1450,11 @@
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>4300.00</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -1393,7 +1499,11 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>25.80</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1444,7 +1554,11 @@
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -1590,7 +1704,7 @@
           <t>1450.00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>2020.00</t>
         </is>
@@ -1620,13 +1734,13 @@
         <v>1642</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1510</v>
+        <v>1382.5</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-132</v>
+        <v>-259.5</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>-0.02007055102785549</v>
+        <v>-0.03945687872521591</v>
       </c>
     </row>
     <row r="19">
@@ -1645,7 +1759,7 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>750.00</t>
         </is>
@@ -1673,13 +1787,13 @@
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="9" t="n">
-        <v>1390</v>
+        <v>1550</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>120</v>
+        <v>167.5</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>-0.01824595547986863</v>
+        <v>0.02546831285731663</v>
       </c>
     </row>
     <row r="20">
@@ -1893,7 +2007,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>260.00</t>
         </is>
@@ -1928,13 +2042,13 @@
         <v>785</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1101.2</v>
+        <v>1311.5</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>316.2</v>
+        <v>526.5</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.07406019440215483</v>
+        <v>0.123316547605106</v>
       </c>
     </row>
     <row r="25">
@@ -1948,7 +2062,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
@@ -1981,13 +2095,13 @@
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="9" t="n">
-        <v>1105.4</v>
+        <v>1319.25</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>4.200000000000045</v>
+        <v>7.75</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>0.0009837217472772094</v>
+        <v>0.001815200843190069</v>
       </c>
     </row>
     <row r="26">
@@ -2108,12 +2222,16 @@
           <t>7552.00</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>7510.00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3622.50</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
@@ -2132,13 +2250,13 @@
         <v>7946</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8921.625</v>
+        <v>7949.75</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>975.625</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.03273975314939227</v>
+        <v>0.0001258414598951657</v>
       </c>
     </row>
     <row r="29">
@@ -2159,12 +2277,16 @@
           <t>7564.00</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>3155.00</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>7488.00</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
@@ -2181,13 +2303,13 @@
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="9" t="n">
-        <v>6903.875</v>
+        <v>7987.125</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>2017.75</v>
+        <v>37.375</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>-0.0677110948542588</v>
+        <v>0.001254219883621818</v>
       </c>
     </row>
     <row r="30">
@@ -2211,13 +2333,17 @@
           <t>355.00</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>1325.00</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>520.00</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -2232,13 +2358,13 @@
         <v>372</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>630</v>
+        <v>428.75</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>258</v>
+        <v>56.75</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.9422936449963477</v>
+        <v>0.2072680788897005</v>
       </c>
     </row>
     <row r="31">
@@ -2262,15 +2388,15 @@
           <t>475.00</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>600.00</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>615.00</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
@@ -2285,13 +2411,13 @@
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="9" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>98.75</v>
+        <v>106.25</v>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>-0.3606647187728269</v>
+        <v>0.3880569758948137</v>
       </c>
     </row>
     <row r="32">
@@ -2815,9 +2941,9 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2885,13 +3011,13 @@
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="9" t="n">
-        <v>-6.466666666666669</v>
+        <v>-4.850000000000001</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>106.4666666666667</v>
+        <v>104.85</v>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>-0.001530872434326819</v>
+        <v>-0.001507626562985287</v>
       </c>
     </row>
     <row r="44">
@@ -2915,7 +3041,11 @@
           <t>587.50</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>3930.00</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2932,13 +3062,13 @@
         <v>796</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>618.3333333333334</v>
+        <v>1446.25</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>-177.6666666666666</v>
+        <v>650.25</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>-0.01336734105278469</v>
+        <v>0.04892371587001828</v>
       </c>
     </row>
     <row r="45">
@@ -2962,7 +3092,11 @@
           <t>525.00</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>3857.50</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
@@ -2977,13 +3111,13 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="9" t="n">
-        <v>709.1666666666666</v>
+        <v>1496.25</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>90.83333333333326</v>
+        <v>50</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>0.006834147161132883</v>
+        <v>0.003761915868513517</v>
       </c>
     </row>
     <row r="46">
@@ -3254,7 +3388,11 @@
           <t>10098.00</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3290,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P202"/>
+  <dimension ref="A1:P212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3455,7 +3593,7 @@
       <c r="O2" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="14" t="n">
         <v>46277.48542824074</v>
       </c>
     </row>
@@ -3525,7 +3663,7 @@
       <c r="O3" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="14" t="n">
         <v>46277.51052083333</v>
       </c>
     </row>
@@ -3595,7 +3733,7 @@
       <c r="O4" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="14" t="n">
         <v>46277.51194444444</v>
       </c>
     </row>
@@ -3665,7 +3803,7 @@
       <c r="O5" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="14" t="n">
         <v>46277.58818287037</v>
       </c>
     </row>
@@ -3735,7 +3873,7 @@
       <c r="O6" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="14" t="n">
         <v>46277.5909375</v>
       </c>
     </row>
@@ -3801,7 +3939,7 @@
       <c r="O7" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="14" t="n">
         <v>46277.63061342593</v>
       </c>
     </row>
@@ -3867,7 +4005,7 @@
       <c r="O8" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="14" t="n">
         <v>46277.66618055556</v>
       </c>
     </row>
@@ -3937,7 +4075,7 @@
       <c r="O9" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P9" s="13" t="n">
+      <c r="P9" s="14" t="n">
         <v>46277.78224537037</v>
       </c>
     </row>
@@ -4007,7 +4145,7 @@
       <c r="O10" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="14" t="n">
         <v>46277.79376157407</v>
       </c>
     </row>
@@ -4073,7 +4211,7 @@
       <c r="O11" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="P11" s="14" t="n">
         <v>46277.83049768519</v>
       </c>
     </row>
@@ -4143,7 +4281,7 @@
       <c r="O12" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="14" t="n">
         <v>46277.86043981482</v>
       </c>
     </row>
@@ -4213,7 +4351,7 @@
       <c r="O13" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="14" t="n">
         <v>46277.87179398148</v>
       </c>
     </row>
@@ -4283,7 +4421,7 @@
       <c r="O14" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="14" t="n">
         <v>46278.05765046296</v>
       </c>
     </row>
@@ -4353,7 +4491,7 @@
       <c r="O15" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="14" t="n">
         <v>46278.06443287037</v>
       </c>
     </row>
@@ -4423,7 +4561,7 @@
       <c r="O16" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="14" t="n">
         <v>46278.08553240741</v>
       </c>
     </row>
@@ -4493,7 +4631,7 @@
       <c r="O17" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="14" t="n">
         <v>46278.08700231482</v>
       </c>
     </row>
@@ -4563,7 +4701,7 @@
       <c r="O18" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P18" s="13" t="n">
+      <c r="P18" s="14" t="n">
         <v>46278.08775462963</v>
       </c>
     </row>
@@ -4633,7 +4771,7 @@
       <c r="O19" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="P19" s="14" t="n">
         <v>46278.21667824074</v>
       </c>
     </row>
@@ -4703,7 +4841,7 @@
       <c r="O20" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P20" s="13" t="n">
+      <c r="P20" s="14" t="n">
         <v>46278.24315972222</v>
       </c>
     </row>
@@ -4773,7 +4911,7 @@
       <c r="O21" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P21" s="13" t="n">
+      <c r="P21" s="14" t="n">
         <v>46278.26704861111</v>
       </c>
     </row>
@@ -4843,7 +4981,7 @@
       <c r="O22" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P22" s="13" t="n">
+      <c r="P22" s="14" t="n">
         <v>46278.26740740741</v>
       </c>
     </row>
@@ -4913,7 +5051,7 @@
       <c r="O23" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P23" s="13" t="n">
+      <c r="P23" s="14" t="n">
         <v>46278.27628472223</v>
       </c>
     </row>
@@ -4983,7 +5121,7 @@
       <c r="O24" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P24" s="13" t="n">
+      <c r="P24" s="14" t="n">
         <v>46278.27751157407</v>
       </c>
     </row>
@@ -5053,7 +5191,7 @@
       <c r="O25" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P25" s="13" t="n">
+      <c r="P25" s="14" t="n">
         <v>46278.29635416667</v>
       </c>
     </row>
@@ -5123,7 +5261,7 @@
       <c r="O26" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P26" s="13" t="n">
+      <c r="P26" s="14" t="n">
         <v>46278.35381944444</v>
       </c>
     </row>
@@ -5193,7 +5331,7 @@
       <c r="O27" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P27" s="13" t="n">
+      <c r="P27" s="14" t="n">
         <v>46278.35512731481</v>
       </c>
     </row>
@@ -5263,7 +5401,7 @@
       <c r="O28" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P28" s="13" t="n">
+      <c r="P28" s="14" t="n">
         <v>46278.4143287037</v>
       </c>
     </row>
@@ -5333,7 +5471,7 @@
       <c r="O29" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P29" s="13" t="n">
+      <c r="P29" s="14" t="n">
         <v>46278.49403935186</v>
       </c>
     </row>
@@ -5403,7 +5541,7 @@
       <c r="O30" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P30" s="13" t="n">
+      <c r="P30" s="14" t="n">
         <v>46278.65908564815</v>
       </c>
     </row>
@@ -5473,7 +5611,7 @@
       <c r="O31" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="14" t="n">
         <v>46278.67763888889</v>
       </c>
     </row>
@@ -5543,7 +5681,7 @@
       <c r="O32" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P32" s="13" t="n">
+      <c r="P32" s="14" t="n">
         <v>46278.69815972223</v>
       </c>
     </row>
@@ -5613,7 +5751,7 @@
       <c r="O33" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P33" s="13" t="n">
+      <c r="P33" s="14" t="n">
         <v>46278.72652777778</v>
       </c>
     </row>
@@ -5683,7 +5821,7 @@
       <c r="O34" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P34" s="13" t="n">
+      <c r="P34" s="14" t="n">
         <v>46278.84016203704</v>
       </c>
     </row>
@@ -5753,7 +5891,7 @@
       <c r="O35" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P35" s="13" t="n">
+      <c r="P35" s="14" t="n">
         <v>46278.85677083334</v>
       </c>
     </row>
@@ -5823,7 +5961,7 @@
       <c r="O36" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P36" s="13" t="n">
+      <c r="P36" s="14" t="n">
         <v>46278.8781712963</v>
       </c>
     </row>
@@ -5893,7 +6031,7 @@
       <c r="O37" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P37" s="13" t="n">
+      <c r="P37" s="14" t="n">
         <v>46278.90575231481</v>
       </c>
     </row>
@@ -5963,7 +6101,7 @@
       <c r="O38" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P38" s="13" t="n">
+      <c r="P38" s="14" t="n">
         <v>46278.94225694444</v>
       </c>
     </row>
@@ -6033,7 +6171,7 @@
       <c r="O39" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P39" s="13" t="n">
+      <c r="P39" s="14" t="n">
         <v>46279.06255787037</v>
       </c>
     </row>
@@ -6103,7 +6241,7 @@
       <c r="O40" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P40" s="13" t="n">
+      <c r="P40" s="14" t="n">
         <v>46279.09913194444</v>
       </c>
     </row>
@@ -6173,7 +6311,7 @@
       <c r="O41" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P41" s="13" t="n">
+      <c r="P41" s="14" t="n">
         <v>46279.15164351852</v>
       </c>
     </row>
@@ -6243,7 +6381,7 @@
       <c r="O42" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P42" s="13" t="n">
+      <c r="P42" s="14" t="n">
         <v>46279.15413194444</v>
       </c>
     </row>
@@ -6313,7 +6451,7 @@
       <c r="O43" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P43" s="13" t="n">
+      <c r="P43" s="14" t="n">
         <v>46279.17649305556</v>
       </c>
     </row>
@@ -6383,7 +6521,7 @@
       <c r="O44" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P44" s="13" t="n">
+      <c r="P44" s="14" t="n">
         <v>46279.22236111111</v>
       </c>
     </row>
@@ -6453,7 +6591,7 @@
       <c r="O45" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P45" s="13" t="n">
+      <c r="P45" s="14" t="n">
         <v>46279.23153935185</v>
       </c>
     </row>
@@ -6523,7 +6661,7 @@
       <c r="O46" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P46" s="13" t="n">
+      <c r="P46" s="14" t="n">
         <v>46279.2678125</v>
       </c>
     </row>
@@ -6593,7 +6731,7 @@
       <c r="O47" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P47" s="13" t="n">
+      <c r="P47" s="14" t="n">
         <v>46279.291875</v>
       </c>
     </row>
@@ -6663,7 +6801,7 @@
       <c r="O48" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P48" s="13" t="n">
+      <c r="P48" s="14" t="n">
         <v>46279.29552083334</v>
       </c>
     </row>
@@ -6733,7 +6871,7 @@
       <c r="O49" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P49" s="13" t="n">
+      <c r="P49" s="14" t="n">
         <v>46279.32731481481</v>
       </c>
     </row>
@@ -6803,7 +6941,7 @@
       <c r="O50" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P50" s="13" t="n">
+      <c r="P50" s="14" t="n">
         <v>46279.37328703704</v>
       </c>
     </row>
@@ -6873,7 +7011,7 @@
       <c r="O51" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P51" s="13" t="n">
+      <c r="P51" s="14" t="n">
         <v>46279.41740740741</v>
       </c>
     </row>
@@ -6943,7 +7081,7 @@
       <c r="O52" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P52" s="13" t="n">
+      <c r="P52" s="14" t="n">
         <v>46279.45078703704</v>
       </c>
     </row>
@@ -7013,7 +7151,7 @@
       <c r="O53" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P53" s="13" t="n">
+      <c r="P53" s="14" t="n">
         <v>46279.47466435185</v>
       </c>
     </row>
@@ -7083,7 +7221,7 @@
       <c r="O54" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P54" s="13" t="n">
+      <c r="P54" s="14" t="n">
         <v>46279.49469907407</v>
       </c>
     </row>
@@ -7153,7 +7291,7 @@
       <c r="O55" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P55" s="13" t="n">
+      <c r="P55" s="14" t="n">
         <v>46279.50685185185</v>
       </c>
     </row>
@@ -7223,7 +7361,7 @@
       <c r="O56" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P56" s="13" t="n">
+      <c r="P56" s="14" t="n">
         <v>46279.58126157407</v>
       </c>
     </row>
@@ -7293,7 +7431,7 @@
       <c r="O57" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P57" s="13" t="n">
+      <c r="P57" s="14" t="n">
         <v>46279.62493055555</v>
       </c>
     </row>
@@ -7363,7 +7501,7 @@
       <c r="O58" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P58" s="13" t="n">
+      <c r="P58" s="14" t="n">
         <v>46279.64979166666</v>
       </c>
     </row>
@@ -7433,7 +7571,7 @@
       <c r="O59" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P59" s="13" t="n">
+      <c r="P59" s="14" t="n">
         <v>46279.67836805555</v>
       </c>
     </row>
@@ -7503,7 +7641,7 @@
       <c r="O60" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P60" s="13" t="n">
+      <c r="P60" s="14" t="n">
         <v>46279.68984953704</v>
       </c>
     </row>
@@ -7573,7 +7711,7 @@
       <c r="O61" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P61" s="13" t="n">
+      <c r="P61" s="14" t="n">
         <v>46279.75571759259</v>
       </c>
     </row>
@@ -7643,7 +7781,7 @@
       <c r="O62" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P62" s="13" t="n">
+      <c r="P62" s="14" t="n">
         <v>46279.76197916667</v>
       </c>
     </row>
@@ -7713,7 +7851,7 @@
       <c r="O63" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P63" s="13" t="n">
+      <c r="P63" s="14" t="n">
         <v>46279.82975694445</v>
       </c>
     </row>
@@ -7783,7 +7921,7 @@
       <c r="O64" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P64" s="13" t="n">
+      <c r="P64" s="14" t="n">
         <v>46279.83283564815</v>
       </c>
     </row>
@@ -7853,7 +7991,7 @@
       <c r="O65" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P65" s="13" t="n">
+      <c r="P65" s="14" t="n">
         <v>46279.86658564815</v>
       </c>
     </row>
@@ -7923,7 +8061,7 @@
       <c r="O66" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P66" s="13" t="n">
+      <c r="P66" s="14" t="n">
         <v>46279.86854166666</v>
       </c>
     </row>
@@ -7993,7 +8131,7 @@
       <c r="O67" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P67" s="13" t="n">
+      <c r="P67" s="14" t="n">
         <v>46279.88961805555</v>
       </c>
     </row>
@@ -8063,7 +8201,7 @@
       <c r="O68" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P68" s="13" t="n">
+      <c r="P68" s="14" t="n">
         <v>46279.92807870371</v>
       </c>
     </row>
@@ -8133,7 +8271,7 @@
       <c r="O69" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P69" s="13" t="n">
+      <c r="P69" s="14" t="n">
         <v>46279.95943287037</v>
       </c>
     </row>
@@ -8203,7 +8341,7 @@
       <c r="O70" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P70" s="13" t="n">
+      <c r="P70" s="14" t="n">
         <v>46280.03707175926</v>
       </c>
     </row>
@@ -8273,7 +8411,7 @@
       <c r="O71" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P71" s="13" t="n">
+      <c r="P71" s="14" t="n">
         <v>46280.04559027778</v>
       </c>
     </row>
@@ -8343,7 +8481,7 @@
       <c r="O72" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P72" s="13" t="n">
+      <c r="P72" s="14" t="n">
         <v>46280.05359953704</v>
       </c>
     </row>
@@ -8413,7 +8551,7 @@
       <c r="O73" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P73" s="13" t="n">
+      <c r="P73" s="14" t="n">
         <v>46280.10788194444</v>
       </c>
     </row>
@@ -8483,7 +8621,7 @@
       <c r="O74" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P74" s="13" t="n">
+      <c r="P74" s="14" t="n">
         <v>46280.1452199074</v>
       </c>
     </row>
@@ -8553,7 +8691,7 @@
       <c r="O75" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P75" s="13" t="n">
+      <c r="P75" s="14" t="n">
         <v>46280.19780092593</v>
       </c>
     </row>
@@ -8623,7 +8761,7 @@
       <c r="O76" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P76" s="13" t="n">
+      <c r="P76" s="14" t="n">
         <v>46280.24451388889</v>
       </c>
     </row>
@@ -8693,7 +8831,7 @@
       <c r="O77" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P77" s="13" t="n">
+      <c r="P77" s="14" t="n">
         <v>46280.24539351852</v>
       </c>
     </row>
@@ -8763,7 +8901,7 @@
       <c r="O78" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P78" s="13" t="n">
+      <c r="P78" s="14" t="n">
         <v>46280.27893518518</v>
       </c>
     </row>
@@ -8833,7 +8971,7 @@
       <c r="O79" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P79" s="13" t="n">
+      <c r="P79" s="14" t="n">
         <v>46280.31445601852</v>
       </c>
     </row>
@@ -8903,7 +9041,7 @@
       <c r="O80" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P80" s="13" t="n">
+      <c r="P80" s="14" t="n">
         <v>46280.35971064815</v>
       </c>
     </row>
@@ -8973,7 +9111,7 @@
       <c r="O81" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P81" s="13" t="n">
+      <c r="P81" s="14" t="n">
         <v>46280.39851851852</v>
       </c>
     </row>
@@ -9043,7 +9181,7 @@
       <c r="O82" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P82" s="13" t="n">
+      <c r="P82" s="14" t="n">
         <v>46280.41853009259</v>
       </c>
     </row>
@@ -9113,7 +9251,7 @@
       <c r="O83" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P83" s="13" t="n">
+      <c r="P83" s="14" t="n">
         <v>46280.44364583334</v>
       </c>
     </row>
@@ -9183,7 +9321,7 @@
       <c r="O84" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P84" s="13" t="n">
+      <c r="P84" s="14" t="n">
         <v>46280.4897337963</v>
       </c>
     </row>
@@ -9253,7 +9391,7 @@
       <c r="O85" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P85" s="13" t="n">
+      <c r="P85" s="14" t="n">
         <v>46280.50119212963</v>
       </c>
     </row>
@@ -9323,7 +9461,7 @@
       <c r="O86" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P86" s="13" t="n">
+      <c r="P86" s="14" t="n">
         <v>46280.5120949074</v>
       </c>
     </row>
@@ -9393,7 +9531,7 @@
       <c r="O87" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P87" s="13" t="n">
+      <c r="P87" s="14" t="n">
         <v>46280.51324074074</v>
       </c>
     </row>
@@ -9463,7 +9601,7 @@
       <c r="O88" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P88" s="13" t="n">
+      <c r="P88" s="14" t="n">
         <v>46280.52025462963</v>
       </c>
     </row>
@@ -9533,7 +9671,7 @@
       <c r="O89" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P89" s="13" t="n">
+      <c r="P89" s="14" t="n">
         <v>46280.54377314815</v>
       </c>
     </row>
@@ -9603,7 +9741,7 @@
       <c r="O90" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P90" s="13" t="n">
+      <c r="P90" s="14" t="n">
         <v>46280.59976851852</v>
       </c>
     </row>
@@ -9673,7 +9811,7 @@
       <c r="O91" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P91" s="13" t="n">
+      <c r="P91" s="14" t="n">
         <v>46280.61607638889</v>
       </c>
     </row>
@@ -9743,7 +9881,7 @@
       <c r="O92" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P92" s="13" t="n">
+      <c r="P92" s="14" t="n">
         <v>46280.68962962963</v>
       </c>
     </row>
@@ -9813,7 +9951,7 @@
       <c r="O93" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P93" s="13" t="n">
+      <c r="P93" s="14" t="n">
         <v>46280.71888888889</v>
       </c>
     </row>
@@ -9883,7 +10021,7 @@
       <c r="O94" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P94" s="13" t="n">
+      <c r="P94" s="14" t="n">
         <v>46280.74344907407</v>
       </c>
     </row>
@@ -9953,7 +10091,7 @@
       <c r="O95" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P95" s="13" t="n">
+      <c r="P95" s="14" t="n">
         <v>46280.77847222222</v>
       </c>
     </row>
@@ -10023,7 +10161,7 @@
       <c r="O96" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P96" s="13" t="n">
+      <c r="P96" s="14" t="n">
         <v>46280.84616898148</v>
       </c>
     </row>
@@ -10093,7 +10231,7 @@
       <c r="O97" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P97" s="13" t="n">
+      <c r="P97" s="14" t="n">
         <v>46280.86395833334</v>
       </c>
     </row>
@@ -10163,7 +10301,7 @@
       <c r="O98" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P98" s="13" t="n">
+      <c r="P98" s="14" t="n">
         <v>46280.89765046296</v>
       </c>
     </row>
@@ -10233,7 +10371,7 @@
       <c r="O99" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P99" s="13" t="n">
+      <c r="P99" s="14" t="n">
         <v>46280.90140046296</v>
       </c>
     </row>
@@ -10303,7 +10441,7 @@
       <c r="O100" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P100" s="13" t="n">
+      <c r="P100" s="14" t="n">
         <v>46280.92248842592</v>
       </c>
     </row>
@@ -10373,7 +10511,7 @@
       <c r="O101" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P101" s="13" t="n">
+      <c r="P101" s="14" t="n">
         <v>46280.94780092593</v>
       </c>
     </row>
@@ -10443,7 +10581,7 @@
       <c r="O102" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P102" s="13" t="n">
+      <c r="P102" s="14" t="n">
         <v>46281.03773148148</v>
       </c>
     </row>
@@ -10513,7 +10651,7 @@
       <c r="O103" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P103" s="13" t="n">
+      <c r="P103" s="14" t="n">
         <v>46281.05363425926</v>
       </c>
     </row>
@@ -10583,7 +10721,7 @@
       <c r="O104" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P104" s="13" t="n">
+      <c r="P104" s="14" t="n">
         <v>46281.17542824074</v>
       </c>
     </row>
@@ -10653,7 +10791,7 @@
       <c r="O105" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P105" s="13" t="n">
+      <c r="P105" s="14" t="n">
         <v>46281.23145833334</v>
       </c>
     </row>
@@ -10723,7 +10861,7 @@
       <c r="O106" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P106" s="13" t="n">
+      <c r="P106" s="14" t="n">
         <v>46281.26112268519</v>
       </c>
     </row>
@@ -10793,7 +10931,7 @@
       <c r="O107" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P107" s="13" t="n">
+      <c r="P107" s="14" t="n">
         <v>46281.34596064815</v>
       </c>
     </row>
@@ -10863,7 +11001,7 @@
       <c r="O108" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P108" s="13" t="n">
+      <c r="P108" s="14" t="n">
         <v>46281.41318287037</v>
       </c>
     </row>
@@ -10933,7 +11071,7 @@
       <c r="O109" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P109" s="13" t="n">
+      <c r="P109" s="14" t="n">
         <v>46281.47984953703</v>
       </c>
     </row>
@@ -11003,7 +11141,7 @@
       <c r="O110" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P110" s="13" t="n">
+      <c r="P110" s="14" t="n">
         <v>46281.48199074074</v>
       </c>
     </row>
@@ -11073,7 +11211,7 @@
       <c r="O111" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P111" s="13" t="n">
+      <c r="P111" s="14" t="n">
         <v>46281.55998842593</v>
       </c>
     </row>
@@ -11143,7 +11281,7 @@
       <c r="O112" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P112" s="13" t="n">
+      <c r="P112" s="14" t="n">
         <v>46281.56878472222</v>
       </c>
     </row>
@@ -11213,7 +11351,7 @@
       <c r="O113" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P113" s="13" t="n">
+      <c r="P113" s="14" t="n">
         <v>46281.60291666666</v>
       </c>
     </row>
@@ -11283,7 +11421,7 @@
       <c r="O114" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P114" s="13" t="n">
+      <c r="P114" s="14" t="n">
         <v>46281.60375</v>
       </c>
     </row>
@@ -11353,7 +11491,7 @@
       <c r="O115" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P115" s="13" t="n">
+      <c r="P115" s="14" t="n">
         <v>46281.61435185185</v>
       </c>
     </row>
@@ -11423,7 +11561,7 @@
       <c r="O116" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P116" s="13" t="n">
+      <c r="P116" s="14" t="n">
         <v>46281.64665509259</v>
       </c>
     </row>
@@ -11493,7 +11631,7 @@
       <c r="O117" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P117" s="13" t="n">
+      <c r="P117" s="14" t="n">
         <v>46281.67173611111</v>
       </c>
     </row>
@@ -11563,7 +11701,7 @@
       <c r="O118" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P118" s="13" t="n">
+      <c r="P118" s="14" t="n">
         <v>46281.72890046296</v>
       </c>
     </row>
@@ -11633,7 +11771,7 @@
       <c r="O119" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P119" s="13" t="n">
+      <c r="P119" s="14" t="n">
         <v>46281.7578587963</v>
       </c>
     </row>
@@ -11703,7 +11841,7 @@
       <c r="O120" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P120" s="13" t="n">
+      <c r="P120" s="14" t="n">
         <v>46281.80134259259</v>
       </c>
     </row>
@@ -11773,7 +11911,7 @@
       <c r="O121" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P121" s="13" t="n">
+      <c r="P121" s="14" t="n">
         <v>46281.85913194445</v>
       </c>
     </row>
@@ -11843,7 +11981,7 @@
       <c r="O122" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P122" s="13" t="n">
+      <c r="P122" s="14" t="n">
         <v>46281.86515046296</v>
       </c>
     </row>
@@ -11913,7 +12051,7 @@
       <c r="O123" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P123" s="13" t="n">
+      <c r="P123" s="14" t="n">
         <v>46281.93247685185</v>
       </c>
     </row>
@@ -11983,7 +12121,7 @@
       <c r="O124" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P124" s="13" t="n">
+      <c r="P124" s="14" t="n">
         <v>46281.96268518519</v>
       </c>
     </row>
@@ -12053,7 +12191,7 @@
       <c r="O125" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P125" s="13" t="n">
+      <c r="P125" s="14" t="n">
         <v>46281.96670138889</v>
       </c>
     </row>
@@ -12123,7 +12261,7 @@
       <c r="O126" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P126" s="13" t="n">
+      <c r="P126" s="14" t="n">
         <v>46282.01916666667</v>
       </c>
     </row>
@@ -12193,7 +12331,7 @@
       <c r="O127" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P127" s="13" t="n">
+      <c r="P127" s="14" t="n">
         <v>46282.07037037037</v>
       </c>
     </row>
@@ -12263,7 +12401,7 @@
       <c r="O128" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P128" s="13" t="n">
+      <c r="P128" s="14" t="n">
         <v>46282.08375</v>
       </c>
     </row>
@@ -12333,7 +12471,7 @@
       <c r="O129" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P129" s="13" t="n">
+      <c r="P129" s="14" t="n">
         <v>46282.14739583333</v>
       </c>
     </row>
@@ -12403,7 +12541,7 @@
       <c r="O130" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P130" s="13" t="n">
+      <c r="P130" s="14" t="n">
         <v>46282.15549768518</v>
       </c>
     </row>
@@ -12473,7 +12611,7 @@
       <c r="O131" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P131" s="13" t="n">
+      <c r="P131" s="14" t="n">
         <v>46282.16440972222</v>
       </c>
     </row>
@@ -12543,7 +12681,7 @@
       <c r="O132" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P132" s="13" t="n">
+      <c r="P132" s="14" t="n">
         <v>46282.18530092593</v>
       </c>
     </row>
@@ -12613,7 +12751,7 @@
       <c r="O133" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P133" s="13" t="n">
+      <c r="P133" s="14" t="n">
         <v>46282.21564814815</v>
       </c>
     </row>
@@ -12683,7 +12821,7 @@
       <c r="O134" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P134" s="13" t="n">
+      <c r="P134" s="14" t="n">
         <v>46282.2421412037</v>
       </c>
     </row>
@@ -12753,7 +12891,7 @@
       <c r="O135" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P135" s="13" t="n">
+      <c r="P135" s="14" t="n">
         <v>46282.32163194445</v>
       </c>
     </row>
@@ -12823,7 +12961,7 @@
       <c r="O136" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P136" s="13" t="n">
+      <c r="P136" s="14" t="n">
         <v>46282.33078703703</v>
       </c>
     </row>
@@ -12893,7 +13031,7 @@
       <c r="O137" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P137" s="13" t="n">
+      <c r="P137" s="14" t="n">
         <v>46282.36037037037</v>
       </c>
     </row>
@@ -12963,7 +13101,7 @@
       <c r="O138" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P138" s="13" t="n">
+      <c r="P138" s="14" t="n">
         <v>46282.3647337963</v>
       </c>
     </row>
@@ -13033,7 +13171,7 @@
       <c r="O139" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P139" s="13" t="n">
+      <c r="P139" s="14" t="n">
         <v>46282.38931712963</v>
       </c>
     </row>
@@ -13103,7 +13241,7 @@
       <c r="O140" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P140" s="13" t="n">
+      <c r="P140" s="14" t="n">
         <v>46282.3912037037</v>
       </c>
     </row>
@@ -13173,7 +13311,7 @@
       <c r="O141" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P141" s="13" t="n">
+      <c r="P141" s="14" t="n">
         <v>46282.4034375</v>
       </c>
     </row>
@@ -13243,7 +13381,7 @@
       <c r="O142" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P142" s="13" t="n">
+      <c r="P142" s="14" t="n">
         <v>46282.43136574074</v>
       </c>
     </row>
@@ -13313,7 +13451,7 @@
       <c r="O143" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P143" s="13" t="n">
+      <c r="P143" s="14" t="n">
         <v>46282.49684027778</v>
       </c>
     </row>
@@ -13383,7 +13521,7 @@
       <c r="O144" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P144" s="13" t="n">
+      <c r="P144" s="14" t="n">
         <v>46282.51994212963</v>
       </c>
     </row>
@@ -13453,7 +13591,7 @@
       <c r="O145" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P145" s="13" t="n">
+      <c r="P145" s="14" t="n">
         <v>46282.62939814815</v>
       </c>
     </row>
@@ -13523,7 +13661,7 @@
       <c r="O146" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P146" s="13" t="n">
+      <c r="P146" s="14" t="n">
         <v>46282.6515162037</v>
       </c>
     </row>
@@ -13593,7 +13731,7 @@
       <c r="O147" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P147" s="13" t="n">
+      <c r="P147" s="14" t="n">
         <v>46282.78369212963</v>
       </c>
     </row>
@@ -13663,7 +13801,7 @@
       <c r="O148" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P148" s="13" t="n">
+      <c r="P148" s="14" t="n">
         <v>46282.78776620371</v>
       </c>
     </row>
@@ -13733,7 +13871,7 @@
       <c r="O149" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P149" s="13" t="n">
+      <c r="P149" s="14" t="n">
         <v>46282.91478009259</v>
       </c>
     </row>
@@ -13803,7 +13941,7 @@
       <c r="O150" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P150" s="13" t="n">
+      <c r="P150" s="14" t="n">
         <v>46282.94171296297</v>
       </c>
     </row>
@@ -13873,7 +14011,7 @@
       <c r="O151" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P151" s="13" t="n">
+      <c r="P151" s="14" t="n">
         <v>46283.06856481481</v>
       </c>
     </row>
@@ -13943,7 +14081,7 @@
       <c r="O152" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P152" s="13" t="n">
+      <c r="P152" s="14" t="n">
         <v>46283.0745949074</v>
       </c>
     </row>
@@ -14013,7 +14151,7 @@
       <c r="O153" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P153" s="13" t="n">
+      <c r="P153" s="14" t="n">
         <v>46283.19665509259</v>
       </c>
     </row>
@@ -14083,7 +14221,7 @@
       <c r="O154" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P154" s="13" t="n">
+      <c r="P154" s="14" t="n">
         <v>46283.22854166666</v>
       </c>
     </row>
@@ -14153,7 +14291,7 @@
       <c r="O155" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P155" s="13" t="n">
+      <c r="P155" s="14" t="n">
         <v>46283.33405092593</v>
       </c>
     </row>
@@ -14223,7 +14361,7 @@
       <c r="O156" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P156" s="13" t="n">
+      <c r="P156" s="14" t="n">
         <v>46283.35032407408</v>
       </c>
     </row>
@@ -14293,7 +14431,7 @@
       <c r="O157" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P157" s="13" t="n">
+      <c r="P157" s="14" t="n">
         <v>46283.48784722222</v>
       </c>
     </row>
@@ -14363,7 +14501,7 @@
       <c r="O158" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P158" s="13" t="n">
+      <c r="P158" s="14" t="n">
         <v>46283.508125</v>
       </c>
     </row>
@@ -14433,7 +14571,7 @@
       <c r="O159" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P159" s="13" t="n">
+      <c r="P159" s="14" t="n">
         <v>46283.64868055555</v>
       </c>
     </row>
@@ -14503,7 +14641,7 @@
       <c r="O160" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P160" s="13" t="n">
+      <c r="P160" s="14" t="n">
         <v>46283.6619212963</v>
       </c>
     </row>
@@ -14573,7 +14711,7 @@
       <c r="O161" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P161" s="13" t="n">
+      <c r="P161" s="14" t="n">
         <v>46283.76673611111</v>
       </c>
     </row>
@@ -14643,7 +14781,7 @@
       <c r="O162" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P162" s="13" t="n">
+      <c r="P162" s="14" t="n">
         <v>46283.8025</v>
       </c>
     </row>
@@ -14713,7 +14851,7 @@
       <c r="O163" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P163" s="13" t="n">
+      <c r="P163" s="14" t="n">
         <v>46283.92071759259</v>
       </c>
     </row>
@@ -14783,7 +14921,7 @@
       <c r="O164" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P164" s="13" t="n">
+      <c r="P164" s="14" t="n">
         <v>46283.94190972222</v>
       </c>
     </row>
@@ -14853,7 +14991,7 @@
       <c r="O165" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P165" s="13" t="n">
+      <c r="P165" s="14" t="n">
         <v>46284.05696759259</v>
       </c>
     </row>
@@ -14923,7 +15061,7 @@
       <c r="O166" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P166" s="13" t="n">
+      <c r="P166" s="14" t="n">
         <v>46284.09695601852</v>
       </c>
     </row>
@@ -14993,7 +15131,7 @@
       <c r="O167" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P167" s="13" t="n">
+      <c r="P167" s="14" t="n">
         <v>46284.21068287037</v>
       </c>
     </row>
@@ -15063,7 +15201,7 @@
       <c r="O168" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P168" s="13" t="n">
+      <c r="P168" s="14" t="n">
         <v>46284.24060185185</v>
       </c>
     </row>
@@ -15133,7 +15271,7 @@
       <c r="O169" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P169" s="13" t="n">
+      <c r="P169" s="14" t="n">
         <v>46284.33123842593</v>
       </c>
     </row>
@@ -15203,7 +15341,7 @@
       <c r="O170" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P170" s="13" t="n">
+      <c r="P170" s="14" t="n">
         <v>46284.3950462963</v>
       </c>
     </row>
@@ -15273,7 +15411,7 @@
       <c r="O171" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P171" s="13" t="n">
+      <c r="P171" s="14" t="n">
         <v>46284.48659722223</v>
       </c>
     </row>
@@ -15343,7 +15481,7 @@
       <c r="O172" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P172" s="13" t="n">
+      <c r="P172" s="14" t="n">
         <v>46284.51091435185</v>
       </c>
     </row>
@@ -15413,7 +15551,7 @@
       <c r="O173" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P173" s="13" t="n">
+      <c r="P173" s="14" t="n">
         <v>46284.61217592593</v>
       </c>
     </row>
@@ -15483,7 +15621,7 @@
       <c r="O174" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P174" s="13" t="n">
+      <c r="P174" s="14" t="n">
         <v>46284.63247685185</v>
       </c>
     </row>
@@ -15553,7 +15691,7 @@
       <c r="O175" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P175" s="13" t="n">
+      <c r="P175" s="14" t="n">
         <v>46284.66641203704</v>
       </c>
     </row>
@@ -15623,7 +15761,7 @@
       <c r="O176" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P176" s="13" t="n">
+      <c r="P176" s="14" t="n">
         <v>46284.76607638889</v>
       </c>
     </row>
@@ -15693,7 +15831,7 @@
       <c r="O177" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P177" s="13" t="n">
+      <c r="P177" s="14" t="n">
         <v>46284.78469907407</v>
       </c>
     </row>
@@ -15763,7 +15901,7 @@
       <c r="O178" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P178" s="13" t="n">
+      <c r="P178" s="14" t="n">
         <v>46284.895</v>
       </c>
     </row>
@@ -15833,7 +15971,7 @@
       <c r="O179" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P179" s="13" t="n">
+      <c r="P179" s="14" t="n">
         <v>46284.93909722222</v>
       </c>
     </row>
@@ -15903,7 +16041,7 @@
       <c r="O180" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P180" s="13" t="n">
+      <c r="P180" s="14" t="n">
         <v>46284.99038194444</v>
       </c>
     </row>
@@ -15973,7 +16111,7 @@
       <c r="O181" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P181" s="13" t="n">
+      <c r="P181" s="14" t="n">
         <v>46285.02277777778</v>
       </c>
     </row>
@@ -16043,7 +16181,7 @@
       <c r="O182" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P182" s="13" t="n">
+      <c r="P182" s="14" t="n">
         <v>46285.04913194444</v>
       </c>
     </row>
@@ -16113,7 +16251,7 @@
       <c r="O183" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P183" s="13" t="n">
+      <c r="P183" s="14" t="n">
         <v>46285.16568287037</v>
       </c>
     </row>
@@ -16183,7 +16321,7 @@
       <c r="O184" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P184" s="13" t="n">
+      <c r="P184" s="14" t="n">
         <v>46285.31915509259</v>
       </c>
     </row>
@@ -16253,7 +16391,7 @@
       <c r="O185" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P185" s="13" t="n">
+      <c r="P185" s="14" t="n">
         <v>46285.38929398148</v>
       </c>
     </row>
@@ -16323,7 +16461,7 @@
       <c r="O186" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P186" s="13" t="n">
+      <c r="P186" s="14" t="n">
         <v>46285.45016203704</v>
       </c>
     </row>
@@ -16393,7 +16531,7 @@
       <c r="O187" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P187" s="13" t="n">
+      <c r="P187" s="14" t="n">
         <v>46285.60445601852</v>
       </c>
     </row>
@@ -16463,7 +16601,7 @@
       <c r="O188" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P188" s="13" t="n">
+      <c r="P188" s="14" t="n">
         <v>46285.70131944444</v>
       </c>
     </row>
@@ -16533,7 +16671,7 @@
       <c r="O189" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P189" s="13" t="n">
+      <c r="P189" s="14" t="n">
         <v>46285.73811342593</v>
       </c>
     </row>
@@ -16603,7 +16741,7 @@
       <c r="O190" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P190" s="13" t="n">
+      <c r="P190" s="14" t="n">
         <v>46285.89204861111</v>
       </c>
     </row>
@@ -16673,7 +16811,7 @@
       <c r="O191" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P191" s="13" t="n">
+      <c r="P191" s="14" t="n">
         <v>46286.04180555556</v>
       </c>
     </row>
@@ -16743,7 +16881,7 @@
       <c r="O192" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P192" s="13" t="n">
+      <c r="P192" s="14" t="n">
         <v>46286.10230324074</v>
       </c>
     </row>
@@ -16813,7 +16951,7 @@
       <c r="O193" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P193" s="13" t="n">
+      <c r="P193" s="14" t="n">
         <v>46286.19703703704</v>
       </c>
     </row>
@@ -16883,7 +17021,7 @@
       <c r="O194" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P194" s="13" t="n">
+      <c r="P194" s="14" t="n">
         <v>46286.34505787037</v>
       </c>
     </row>
@@ -16953,7 +17091,7 @@
       <c r="O195" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P195" s="13" t="n">
+      <c r="P195" s="14" t="n">
         <v>46286.38792824074</v>
       </c>
     </row>
@@ -17023,7 +17161,7 @@
       <c r="O196" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P196" s="13" t="n">
+      <c r="P196" s="14" t="n">
         <v>46286.49905092592</v>
       </c>
     </row>
@@ -17093,7 +17231,7 @@
       <c r="O197" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P197" s="13" t="n">
+      <c r="P197" s="14" t="n">
         <v>46286.64550925926</v>
       </c>
     </row>
@@ -17163,7 +17301,7 @@
       <c r="O198" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P198" s="13" t="n">
+      <c r="P198" s="14" t="n">
         <v>46286.79150462963</v>
       </c>
     </row>
@@ -17233,7 +17371,7 @@
       <c r="O199" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P199" s="13" t="n">
+      <c r="P199" s="14" t="n">
         <v>46286.79928240741</v>
       </c>
     </row>
@@ -17303,132 +17441,840 @@
       <c r="O200" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P200" s="13" t="n">
+      <c r="P200" s="14" t="n">
         <v>46286.94260416667</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="14" t="inlineStr">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>Mamba2_AC_PrivateEye_seed2000_X</t>
         </is>
       </c>
-      <c r="B201" s="14" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t>ehm7pwb2</t>
         </is>
       </c>
-      <c r="C201" s="14" t="inlineStr">
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>PrivateEye</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I201" s="7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K201" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N201" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O201" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P201" s="14" t="n">
+        <v>46286.99332175926</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Jamesbond_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>xv97695u</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Jamesbond</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I202" s="7" t="inlineStr">
+        <is>
+          <t>615.00</t>
+        </is>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="K202" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M202" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N202" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O202" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P202" s="14" t="n">
+        <v>46287.09914351852</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Jamesbond_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>00v05vqb</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Jamesbond</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I203" s="7" t="inlineStr">
+        <is>
+          <t>520.00</t>
+        </is>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="K203" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N203" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O203" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P203" s="14" t="n">
+        <v>46287.22350694444</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>dowz1e7e</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I204" s="7" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="K204" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M204" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N204" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O204" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P204" s="14" t="n">
+        <v>46287.37719907407</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Qbert_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>odiij089</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Qbert</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I205" s="7" t="inlineStr">
+        <is>
+          <t>3857.50</t>
+        </is>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="K205" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N205" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O205" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P205" s="14" t="n">
+        <v>46287.39092592592</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>0s6oaqrv</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H206" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I206" s="7" t="inlineStr">
+        <is>
+          <t>25.80</t>
+        </is>
+      </c>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="K206" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M206" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N206" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O206" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P206" s="14" t="n">
+        <v>46287.51923611111</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Qbert_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>yp4258u6</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Qbert</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H207" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I207" s="7" t="inlineStr">
+        <is>
+          <t>3930.00</t>
+        </is>
+      </c>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="K207" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N207" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O207" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P207" s="14" t="n">
+        <v>46287.62731481482</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>67ri9q27</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I208" s="7" t="inlineStr">
+        <is>
+          <t>7488.00</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K208" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L208" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M208" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N208" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O208" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P208" s="14" t="n">
+        <v>46287.67415509259</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Hero_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>j1qqfmf6</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I209" s="7" t="inlineStr">
+        <is>
+          <t>3622.50</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="K209" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M209" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N209" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O209" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P209" s="14" t="n">
+        <v>46287.793125</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>hva0dn9v</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I210" s="7" t="inlineStr">
+        <is>
+          <t>4300.00</t>
+        </is>
+      </c>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K210" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L210" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M210" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N210" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O210" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P210" s="14" t="n">
+        <v>46287.94795138889</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_UpNDown_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B211" s="15" t="inlineStr">
+        <is>
+          <t>v31w762m</t>
+        </is>
+      </c>
+      <c r="C211" s="15" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D201" s="14" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E201" s="14" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F201" s="14" t="inlineStr">
-        <is>
-          <t>PrivateEye</t>
-        </is>
-      </c>
-      <c r="G201" s="14" t="n">
+      <c r="D211" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E211" s="15" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F211" s="15" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="G211" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="H201" s="14" t="inlineStr">
+      <c r="H211" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I211" s="15" t="inlineStr"/>
+      <c r="J211" s="15" t="inlineStr"/>
+      <c r="K211" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L211" s="15" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M211" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N211" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O211" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P211" s="16" t="n">
+        <v>46288.02731481481</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BattleZone_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>wp5x6x5i</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>BattleZone</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I201" s="14" t="inlineStr"/>
-      <c r="J201" s="14" t="inlineStr"/>
-      <c r="K201" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L201" s="14" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M201" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="N201" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="O201" s="14" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P201" s="15" t="n">
-        <v>46286.99332175926</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Jamesbond_seed2710_O</t>
-        </is>
-      </c>
-      <c r="B202" s="14" t="inlineStr">
-        <is>
-          <t>xv97695u</t>
-        </is>
-      </c>
-      <c r="C202" s="14" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D202" s="14" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E202" s="14" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F202" s="14" t="inlineStr">
-        <is>
-          <t>Jamesbond</t>
-        </is>
-      </c>
-      <c r="G202" s="14" t="n">
-        <v>2710</v>
-      </c>
-      <c r="H202" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I202" s="14" t="inlineStr"/>
-      <c r="J202" s="14" t="inlineStr"/>
-      <c r="K202" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L202" s="14" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M202" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="N202" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="O202" s="14" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P202" s="15" t="n">
-        <v>46287.09914351852</v>
+      <c r="I212" s="7" t="inlineStr">
+        <is>
+          <t>8100.00</t>
+        </is>
+      </c>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="K212" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M212" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N212" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O212" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P212" s="14" t="n">
+        <v>46288.04887731482</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -313,6 +313,13 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="K14" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6010
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N14" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.1
@@ -322,6 +329,13 @@
     <comment ref="G15" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 2710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Boxing, seed 6010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
@@ -384,10 +398,24 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
+    <comment ref="E26" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 2000
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
     <comment ref="N26" authorId="0" shapeId="0">
       <text>
         <t>Random: 257.6
 Human: 2412.5</t>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Gopher, seed 2000
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
     <comment ref="F28" authorId="0" shapeId="0">
@@ -1496,7 +1524,11 @@
           <t>34.70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92.60</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="11" t="inlineStr">
@@ -1515,7 +1547,7 @@
           <t>93.30</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
@@ -1526,13 +1558,13 @@
         <v>78</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>58.55</v>
+        <v>63.2</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-19.45</v>
+        <v>-14.8</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>-1.620833333333334</v>
+        <v>-1.233333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -1551,7 +1583,11 @@
           <t>74.00</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>92.80</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="12" t="inlineStr">
@@ -1570,7 +1606,7 @@
           <t>98.60</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
@@ -1579,13 +1615,13 @@
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="9" t="n">
-        <v>65.7</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>7.150000000000006</v>
+        <v>12.14999999999999</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>0.5958333333333338</v>
+        <v>1.012499999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2117,7 +2153,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>2198.00</t>
         </is>
@@ -2127,7 +2163,11 @@
           <t>1016.00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2896.00</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -2146,13 +2186,13 @@
         <v>2757</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1760</v>
+        <v>1934.5</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>-997</v>
+        <v>-822.5</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>-0.4626664810432038</v>
+        <v>-0.3816882453942178</v>
       </c>
     </row>
     <row r="27">
@@ -2168,7 +2208,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
@@ -2178,7 +2218,11 @@
           <t>1082.00</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2506.00</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr">
@@ -2195,13 +2239,13 @@
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
       <c r="O27" s="9" t="n">
-        <v>1851</v>
+        <v>2187.5</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>91</v>
+        <v>253</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>0.04222933778829644</v>
+        <v>0.1174068402246044</v>
       </c>
     </row>
     <row r="28">
@@ -2592,7 +2636,11 @@
           <t>8213.00</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
@@ -3341,7 +3389,11 @@
           <t>8446.00</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>3309.00</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3358,13 +3410,13 @@
         <v>7387</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>5923</v>
+        <v>5269.5</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>-1464</v>
+        <v>-2117.5</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>-0.1311851466872166</v>
+        <v>-0.1897435437911074</v>
       </c>
     </row>
     <row r="51">
@@ -3388,9 +3440,9 @@
           <t>10098.00</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>3740.00</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
@@ -3407,13 +3459,13 @@
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="9" t="n">
-        <v>6805</v>
+        <v>6038.75</v>
       </c>
       <c r="P51" s="9" t="n">
-        <v>882</v>
+        <v>769.25</v>
       </c>
       <c r="Q51" s="10" t="n">
-        <v>0.07903367443861001</v>
+        <v>0.06893044678220039</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P212"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -18146,64 +18198,72 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="15" t="inlineStr">
+      <c r="A211" s="7" t="inlineStr">
         <is>
           <t>Mamba2_AC_UpNDown_seed2000_O</t>
         </is>
       </c>
-      <c r="B211" s="15" t="inlineStr">
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t>v31w762m</t>
         </is>
       </c>
-      <c r="C211" s="15" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D211" s="15" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E211" s="15" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F211" s="15" t="inlineStr">
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
         <is>
           <t>UpNDown</t>
         </is>
       </c>
-      <c r="G211" s="15" t="n">
+      <c r="G211" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H211" s="15" t="inlineStr">
+      <c r="H211" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I211" s="15" t="inlineStr"/>
-      <c r="J211" s="15" t="inlineStr"/>
-      <c r="K211" s="15" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L211" s="15" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M211" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="N211" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O211" s="15" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P211" s="16" t="n">
+      <c r="I211" s="7" t="inlineStr">
+        <is>
+          <t>3740.00</t>
+        </is>
+      </c>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="K211" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L211" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M211" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N211" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O211" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P211" s="14" t="n">
         <v>46288.02731481481</v>
       </c>
     </row>
@@ -18275,6 +18335,418 @@
       </c>
       <c r="P212" s="14" t="n">
         <v>46288.04887731482</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed1710_O</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>kr7wfbpc</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I213" s="7" t="inlineStr">
+        <is>
+          <t>92.80</t>
+        </is>
+      </c>
+      <c r="J213" s="7" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="K213" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M213" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N213" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O213" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P213" s="14" t="n">
+        <v>46288.21672453704</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Boxing_seed1710_X</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>3oav4ksg</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>Boxing</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I214" s="7" t="inlineStr">
+        <is>
+          <t>92.60</t>
+        </is>
+      </c>
+      <c r="J214" s="7" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="K214" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L214" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M214" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N214" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O214" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P214" s="14" t="n">
+        <v>46288.343125</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>kuybz5dl</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I215" s="7" t="inlineStr">
+        <is>
+          <t>2506.00</t>
+        </is>
+      </c>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="K215" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M215" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N215" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O215" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P215" s="14" t="n">
+        <v>46288.49837962963</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_UpNDown_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>20qc2zu0</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I216" s="7" t="inlineStr">
+        <is>
+          <t>3309.00</t>
+        </is>
+      </c>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="K216" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L216" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M216" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N216" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O216" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P216" s="14" t="n">
+        <v>46288.50125</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Gopher_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>3crb4hx0</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>Gopher</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H217" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I217" s="7" t="inlineStr">
+        <is>
+          <t>2896.00</t>
+        </is>
+      </c>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="K217" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M217" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N217" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O217" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P217" s="14" t="n">
+        <v>46288.64248842592</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B218" s="15" t="inlineStr">
+        <is>
+          <t>mjjum96z</t>
+        </is>
+      </c>
+      <c r="C218" s="15" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E218" s="15" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F218" s="15" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G218" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H218" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I218" s="15" t="inlineStr"/>
+      <c r="J218" s="15" t="inlineStr"/>
+      <c r="K218" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L218" s="15" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M218" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N218" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O218" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P218" s="16" t="n">
+        <v>46288.91950231481</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -378,80 +378,73 @@
 Human: 1971.0</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
+    <comment ref="N24" authorId="0" shapeId="0">
+      <text>
+        <t>Random: 0.0
+Human: 29.6</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N24" authorId="0" shapeId="0">
+    <comment ref="N26" authorId="0" shapeId="0">
       <text>
         <t>Random: 65.2
 Human: 4334.7</t>
       </text>
     </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
+    <comment ref="C27" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Frostbite, seed 710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
+    <comment ref="E28" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 2000
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>Random: 257.6
 Human: 2412.5</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Gopher, seed 2000
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Hero, seed 2010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>Random: 1027.0
 Human: 30826.4</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F31" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Hero, seed 2010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="E30" authorId="0" shapeId="0">
-      <text>
-        <t>EXCLUDED_SEEDS: Jamesbond, seed 2000
-Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
-취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
-      </text>
-    </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
-      <text>
-        <t>Random: 29.0
-Human: 302.8</t>
-      </text>
-    </comment>
-    <comment ref="E31" authorId="0" shapeId="0">
+    <comment ref="E32" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Jamesbond, seed 2000
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
@@ -460,59 +453,72 @@
     </comment>
     <comment ref="N32" authorId="0" shapeId="0">
       <text>
+        <t>Random: 29.0
+Human: 302.8</t>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Jamesbond, seed 2000
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="N34" authorId="0" shapeId="0">
+      <text>
         <t>Random: 52.0
 Human: 3035.0</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="N36" authorId="0" shapeId="0">
       <text>
         <t>Random: 1598.0
 Human: 2665.5</t>
       </text>
     </comment>
-    <comment ref="N36" authorId="0" shapeId="0">
+    <comment ref="N38" authorId="0" shapeId="0">
       <text>
         <t>Random: 258.5
 Human: 22736.3</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
+    <comment ref="N40" authorId="0" shapeId="0">
       <text>
         <t>Random: 307.3
 Human: 6951.6</t>
       </text>
     </comment>
-    <comment ref="N40" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="0" shapeId="0">
       <text>
         <t>Random: -20.7
 Human: 14.6</t>
       </text>
     </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
+    <comment ref="N44" authorId="0" shapeId="0">
       <text>
         <t>Random: 24.9
 Human: 69571.3</t>
       </text>
     </comment>
-    <comment ref="N44" authorId="0" shapeId="0">
+    <comment ref="N46" authorId="0" shapeId="0">
       <text>
         <t>Random: 163.9
 Human: 13455.0</t>
       </text>
     </comment>
-    <comment ref="N46" authorId="0" shapeId="0">
+    <comment ref="N48" authorId="0" shapeId="0">
       <text>
         <t>Random: 11.5
 Human: 7845.0</t>
       </text>
     </comment>
-    <comment ref="N48" authorId="0" shapeId="0">
+    <comment ref="N50" authorId="0" shapeId="0">
       <text>
         <t>Random: 68.4
 Human: 42054.7</t>
       </text>
     </comment>
-    <comment ref="N50" authorId="0" shapeId="0">
+    <comment ref="N52" authorId="0" shapeId="0">
       <text>
         <t>Random: 533.4
 Human: 11693.2</t>
@@ -811,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2035,7 +2041,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Freeway</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2043,54 +2049,28 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>260.00</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2782.00</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1952.00</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>268.00</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>244.00</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="3" t="n">
-        <v>785</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>1311.5</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>526.5</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0.123316547605106</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Frostbite</t>
+          <t>Freeway</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2098,52 +2078,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>2540.00</t>
-        </is>
-      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>2224.00</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>267.00</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>246.00</t>
-        </is>
-      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="9" t="n">
-        <v>1319.25</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>0.001815200843190069</v>
-      </c>
+      <c r="O25" s="9" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
+      <c r="Q25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2151,54 +2109,54 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>2198.00</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1016.00</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2896.00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>260.00</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2782.00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1952.00</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>268.00</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2150.00</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1676.00</t>
-        </is>
-      </c>
+          <t>244.00</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="3" t="n">
-        <v>2757</v>
+        <v>785</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1934.5</v>
+        <v>1311.5</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>-822.5</v>
+        <v>526.5</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>-0.3816882453942178</v>
+        <v>0.123316547605106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Gopher</t>
+          <t>Frostbite</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2206,52 +2164,52 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>1160.00</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>1082.00</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>2506.00</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2540.00</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>2224.00</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>267.00</t>
+        </is>
+      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>3132.00</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>2030.00</t>
-        </is>
-      </c>
+          <t>246.00</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
       <c r="O27" s="9" t="n">
-        <v>2187.5</v>
+        <v>1319.25</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>253</v>
+        <v>7.75</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>0.1174068402246044</v>
+        <v>0.001815200843190069</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Gopher</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2261,52 +2219,52 @@
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7552.00</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>7510.00</t>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>2198.00</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1016.00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3622.50</t>
+          <t>2896.00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>13517.00</t>
+          <t>2150.00</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7107.50</t>
+          <t>1676.00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="3" t="n">
-        <v>7946</v>
+        <v>2757</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7949.75</v>
+        <v>1934.5</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>3.75</v>
+        <v>-822.5</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.0001258414598951657</v>
+        <v>-0.3816882453942178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Gopher</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2316,50 +2274,50 @@
       </c>
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>7564.00</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>3155.00</t>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>1160.00</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>1082.00</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>7488.00</t>
+          <t>2506.00</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>13340.00</t>
+          <t>3132.00</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>3556.50</t>
+          <t>2030.00</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="9" t="n">
-        <v>7987.125</v>
+        <v>2187.5</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>37.375</v>
+        <v>253</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>0.001254219883621818</v>
+        <v>0.1174068402246044</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Jamesbond</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2367,54 +2325,54 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>485.00</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>355.00</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>1325.00</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7552.00</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>7510.00</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>520.00</t>
+          <t>3622.50</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>355.00</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>13517.00</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7107.50</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="3" t="n">
-        <v>372</v>
+        <v>7946</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>428.75</v>
+        <v>7949.75</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>56.75</v>
+        <v>3.75</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.2072680788897005</v>
+        <v>0.0001258414598951657</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Jamesbond</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2422,52 +2380,52 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>445.00</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>475.00</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr"/>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>7564.00</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>3155.00</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>615.00</t>
+          <t>7488.00</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>605.00</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>13340.00</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>3556.50</t>
+        </is>
+      </c>
       <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="9" t="n">
-        <v>535</v>
+        <v>7987.125</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>106.25</v>
+        <v>37.375</v>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>0.3880569758948137</v>
+        <v>0.001254219883621818</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>Jamesbond</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2477,25 +2435,29 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>580.00</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1600.00</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>485.00</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>355.00</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>1325.00</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>520.00</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1420.00</t>
+          <t>355.00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2503,22 +2465,22 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="3" t="n">
-        <v>1384</v>
+        <v>372</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1350</v>
+        <v>428.75</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>-34</v>
+        <v>56.75</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>-0.01139792155548106</v>
+        <v>0.2072680788897005</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>Jamesbond</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2528,25 +2490,29 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
+          <t>445.00</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
           <t>600.00</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>615.00</t>
+        </is>
+      </c>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>1140.00</t>
+          <t>605.00</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr"/>
@@ -2555,19 +2521,19 @@
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
       <c r="O33" s="9" t="n">
-        <v>1335</v>
+        <v>535</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>15</v>
+        <v>106.25</v>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>-0.005028494803888703</v>
+        <v>0.3880569758948137</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2577,48 +2543,48 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>8075.00</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>6783.00</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>580.00</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1600.00</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10649.00</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>9836.00</t>
-        </is>
-      </c>
+          <t>1420.00</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>9693</v>
+        <v>1384</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8835.75</v>
+        <v>1350</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>-857.25</v>
+        <v>-34</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>-0.8030444964871194</v>
+        <v>-0.01139792155548106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Krull</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2628,50 +2594,46 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>7926.00</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>8213.00</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr"/>
+          <t>600.00</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>10233.00</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>8737.00</t>
-        </is>
-      </c>
+          <t>1140.00</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
       <c r="O35" s="9" t="n">
-        <v>8777.25</v>
+        <v>1335</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>58.5</v>
+        <v>15</v>
       </c>
       <c r="Q35" s="10" t="n">
-        <v>-0.05480093676814989</v>
+        <v>-0.005028494803888703</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Krull</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2681,17 +2643,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>20980.00</t>
+          <t>8075.00</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19680.00</t>
+          <t>6783.00</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6240.00</t>
+          <t>9036.00</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2699,30 +2661,34 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19020.00</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t>10649.00</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>9836.00</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="3" t="n">
-        <v>23920</v>
+        <v>9693</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>16480</v>
+        <v>8875.799999999999</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>-7440</v>
+        <v>-817.2000000000007</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>-0.3309932466700478</v>
+        <v>-0.7655269320843098</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>KungFuMaster</t>
+          <t>Krull</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2732,17 +2698,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>17320.00</t>
+          <t>7926.00</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>16560.00</t>
+          <t>8213.00</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>7590.00</t>
+          <t>11093.00</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -2750,28 +2716,32 @@
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>23080.00</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr"/>
+          <t>10233.00</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>8737.00</t>
+        </is>
+      </c>
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="9" t="n">
-        <v>16137.5</v>
+        <v>9240.4</v>
       </c>
       <c r="P37" s="9" t="n">
-        <v>342.5</v>
+        <v>364.6000000000004</v>
       </c>
       <c r="Q37" s="10" t="n">
-        <v>-0.01523725631511981</v>
+        <v>0.3415456674473071</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2781,17 +2751,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4188.00</t>
+          <t>20980.00</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2011.00</t>
+          <t>19680.00</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2094.00</t>
+          <t>6240.00</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2799,7 +2769,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>19020.00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2807,22 +2777,22 @@
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="3" t="n">
-        <v>2270</v>
+        <v>23920</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>2460.25</v>
+        <v>16480</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>190.25</v>
+        <v>-7440</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>0.02863356561263037</v>
+        <v>-0.3309932466700478</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>MsPacman</t>
+          <t>KungFuMaster</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2832,17 +2802,17 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>4075.00</t>
+          <t>17320.00</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1857.00</t>
+          <t>16560.00</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>2322.00</t>
+          <t>7590.00</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -2850,7 +2820,7 @@
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>1847.00</t>
+          <t>23080.00</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr"/>
@@ -2859,19 +2829,19 @@
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="9" t="n">
-        <v>2525.25</v>
+        <v>16137.5</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>65</v>
+        <v>342.5</v>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>0.009782821365681862</v>
+        <v>-0.01523725631511981</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2879,50 +2849,50 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>4188.00</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2011.00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2094.00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>-17.80</t>
-        </is>
-      </c>
+          <t>1548.00</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="3" t="n">
-        <v>15</v>
+        <v>2270</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>8.75</v>
+        <v>2460.25</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>-6.25</v>
+        <v>190.25</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>-0.1770538243626062</v>
+        <v>0.02863356561263037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>MsPacman</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2930,48 +2900,48 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>4075.00</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1857.00</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>2322.00</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>20.80</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>13.90</t>
-        </is>
-      </c>
+          <t>1847.00</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
       <c r="O41" s="9" t="n">
-        <v>14.75</v>
+        <v>2525.25</v>
       </c>
       <c r="P41" s="9" t="n">
-        <v>5.999999999999998</v>
+        <v>65</v>
       </c>
       <c r="Q41" s="10" t="n">
-        <v>0.169971671388102</v>
+        <v>0.009782821365681862</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2979,50 +2949,50 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>-17.80</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>100</v>
+        <v>8.75</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>10</v>
+        <v>-6.25</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>0.0001437888948960694</v>
+        <v>-0.1770538243626062</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>PrivateEye</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3030,48 +3000,48 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>-219.40</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
+          <t>20.80</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>13.90</t>
+        </is>
+      </c>
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="9" t="n">
-        <v>-4.850000000000001</v>
+        <v>14.75</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>104.85</v>
+        <v>5.999999999999998</v>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>-0.001507626562985287</v>
+        <v>0.169971671388102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3081,17 +3051,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>480.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>587.50</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3930.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3099,7 +3069,7 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>787.50</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -3107,22 +3077,22 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="3" t="n">
-        <v>796</v>
+        <v>90</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>1446.25</v>
+        <v>100</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>650.25</v>
+        <v>10</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>0.04892371587001828</v>
+        <v>0.0001437888948960694</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Qbert</t>
+          <t>PrivateEye</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3132,17 +3102,17 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>810.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>525.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>3857.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
@@ -3150,7 +3120,7 @@
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>792.50</t>
+          <t>-219.40</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr"/>
@@ -3159,19 +3129,19 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="9" t="n">
-        <v>1496.25</v>
+        <v>-4.850000000000001</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>50</v>
+        <v>104.85</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>0.003761915868513517</v>
+        <v>-0.001507626562985287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3181,48 +3151,48 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>17690.00</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>480.00</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>587.50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>3930.00</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14670.00</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>7030.00</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>7860.00</t>
-        </is>
-      </c>
+          <t>787.50</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="3" t="n">
-        <v>14020</v>
+        <v>796</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>11812.5</v>
+        <v>1446.25</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>-2207.5</v>
+        <v>650.25</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>-0.2818025148401098</v>
+        <v>0.04892371587001828</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>RoadRunner</t>
+          <t>Qbert</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -3232,46 +3202,46 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>17800.00</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr"/>
+          <t>810.00</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>525.00</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>3857.50</t>
+        </is>
+      </c>
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>15330.00</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>8520.00</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>8500.00</t>
-        </is>
-      </c>
+          <t>792.50</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="9" t="n">
-        <v>12537.5</v>
+        <v>1496.25</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>725</v>
+        <v>50</v>
       </c>
       <c r="Q47" s="10" t="n">
-        <v>0.09255122231441884</v>
+        <v>0.003761915868513517</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Seaquest</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3281,7 +3251,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>714.00</t>
+          <t>17690.00</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -3291,38 +3261,38 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>824.00</t>
+          <t>14670.00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>432.00</t>
+          <t>7030.00</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>534.00</t>
+          <t>7860.00</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="3" t="n">
-        <v>497</v>
+        <v>14020</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>626</v>
+        <v>11812.5</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>129</v>
+        <v>-2207.5</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>0.003072430769084201</v>
+        <v>-0.2818025148401098</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Seaquest</t>
+          <t>RoadRunner</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -3332,7 +3302,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>522.00</t>
+          <t>17800.00</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
@@ -3342,36 +3312,36 @@
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>778.00</t>
+          <t>15330.00</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>474.00</t>
+          <t>8520.00</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>458.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="9" t="n">
-        <v>558</v>
+        <v>12537.5</v>
       </c>
       <c r="P49" s="9" t="n">
-        <v>68</v>
+        <v>725</v>
       </c>
       <c r="Q49" s="10" t="n">
-        <v>-0.001619575909284695</v>
+        <v>0.09255122231441884</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>Seaquest</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3381,48 +3351,48 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6669.00</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>8446.00</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>3309.00</t>
-        </is>
-      </c>
+          <t>714.00</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2654.00</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
+          <t>824.00</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>432.00</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>534.00</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="3" t="n">
-        <v>7387</v>
+        <v>497</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>5269.5</v>
+        <v>626</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>-2117.5</v>
+        <v>129</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>-0.1897435437911074</v>
+        <v>0.003072430769084201</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>UpNDown</t>
+          <t>Seaquest</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -3432,39 +3402,139 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>4831.00</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>10098.00</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>3740.00</t>
-        </is>
-      </c>
+          <t>522.00</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>5486.00</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" s="7" t="inlineStr"/>
+          <t>778.00</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>474.00</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>458.00</t>
+        </is>
+      </c>
       <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="9" t="n">
+        <v>558</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>-0.001619575909284695</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>6669.00</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>8446.00</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>3309.00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2654.00</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="3" t="n">
+        <v>7387</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>5269.5</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>-2117.5</v>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v>-0.1897435437911074</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>UpNDown</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>4831.00</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>10098.00</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>3740.00</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>5486.00</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr"/>
+      <c r="O53" s="9" t="n">
         <v>6038.75</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P53" s="9" t="n">
         <v>769.25</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="Q53" s="10" t="n">
         <v>0.06893044678220039</v>
       </c>
     </row>
@@ -3480,7 +3550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P218"/>
+  <dimension ref="A1:P220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -18688,65 +18758,205 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="15" t="inlineStr">
+      <c r="A218" s="7" t="inlineStr">
         <is>
           <t>Mamba2_AC_Krull_seed2000_O</t>
         </is>
       </c>
-      <c r="B218" s="15" t="inlineStr">
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t>mjjum96z</t>
         </is>
       </c>
-      <c r="C218" s="15" t="inlineStr">
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I218" s="7" t="inlineStr">
+        <is>
+          <t>11093.00</t>
+        </is>
+      </c>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>8.89</t>
+        </is>
+      </c>
+      <c r="K218" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L218" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M218" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N218" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O218" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P218" s="14" t="n">
+        <v>46288.91950231481</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Krull_seed2000_X</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>21ijqipq</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>Krull</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H219" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>9036.00</t>
+        </is>
+      </c>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="K219" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L219" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M219" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N219" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O219" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P219" s="14" t="n">
+        <v>46289.20876157407</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2710_O</t>
+        </is>
+      </c>
+      <c r="B220" s="15" t="inlineStr">
+        <is>
+          <t>m3lhpghb</t>
+        </is>
+      </c>
+      <c r="C220" s="15" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E218" s="15" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F218" s="15" t="inlineStr">
-        <is>
-          <t>Krull</t>
-        </is>
-      </c>
-      <c r="G218" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H218" s="15" t="inlineStr">
+      <c r="D220" s="15" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E220" s="15" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F220" s="15" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G220" s="15" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H220" s="15" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I218" s="15" t="inlineStr"/>
-      <c r="J218" s="15" t="inlineStr"/>
-      <c r="K218" s="15" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L218" s="15" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M218" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="N218" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O218" s="15" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P218" s="16" t="n">
-        <v>46288.91950231481</v>
+      <c r="I220" s="15" t="inlineStr"/>
+      <c r="J220" s="15" t="inlineStr"/>
+      <c r="K220" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L220" s="15" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M220" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N220" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O220" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P220" s="16" t="n">
+        <v>46289.43347222222</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -136,6 +136,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,115 +235,115 @@
     <author>Drama</author>
   </authors>
   <commentList>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>첨부된 논문 표의 DramaXS 게임별 점수입니다. X행에 표시합니다.</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>X: Retrieval 미사용, O: Retrieval 적용 (target: 16).
 양쪽에 유효한 점수가 있는 공통 시드만 사용하며 RUNNING/누락 점수는 제외합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드도 제외합니다. Drama/results/update_tex.py와 동일하게 표시된 시드 점수를 집계합니다.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>X행: Retrieval 미사용의 공통 시드 평균 − DramaXS 논문 점수.
 O행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>X행: (Retrieval 미사용 평균 − DramaXS 논문 점수) / (Human − Random).
 O행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
 모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준입니다. HNS는 Random=0, Human=1 기준이며 차이의 부호를 유지합니다. 백분율이 아닙니다. Random/Human은 STORM 엑셀과 동일한 기준값을 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
+    <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <t>Random: 227.8
 Human: 7127.7</t>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>Random: 5.8
 Human: 1719.5</t>
       </text>
     </comment>
-    <comment ref="N6" authorId="0" shapeId="0">
+    <comment ref="O6" authorId="0" shapeId="0">
       <text>
         <t>Random: 222.4
 Human: 742.0</t>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0">
+    <comment ref="O8" authorId="0" shapeId="0">
       <text>
         <t>Random: 210.0
 Human: 8503.3</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
+    <comment ref="O10" authorId="0" shapeId="0">
       <text>
         <t>Random: 14.2
 Human: 753.1</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0">
+    <comment ref="H12" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="O12" authorId="0" shapeId="0">
       <text>
         <t>Random: 2360.0
 Human: 37187.5</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0">
+    <comment ref="L14" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
+    <comment ref="O14" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.1
 Human: 12.1</t>
       </text>
     </comment>
-    <comment ref="G15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
+    <comment ref="L15" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="O16" authorId="0" shapeId="0">
       <text>
         <t>Random: 1.7
 Human: 30.5</t>
@@ -353,7 +356,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0">
+    <comment ref="O18" authorId="0" shapeId="0">
       <text>
         <t>Random: 811.0
 Human: 7387.8</t>
@@ -366,19 +369,19 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0">
+    <comment ref="O20" authorId="0" shapeId="0">
       <text>
         <t>Random: 10780.5
 Human: 35829.4</t>
       </text>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0">
+    <comment ref="O22" authorId="0" shapeId="0">
       <text>
         <t>Random: 152.1
 Human: 1971.0</t>
       </text>
     </comment>
-    <comment ref="N24" authorId="0" shapeId="0">
+    <comment ref="O24" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.0
 Human: 29.6</t>
@@ -391,7 +394,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="O26" authorId="0" shapeId="0">
       <text>
         <t>Random: 65.2
 Human: 4334.7</t>
@@ -411,7 +414,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>Random: 257.6
 Human: 2412.5</t>
@@ -431,7 +434,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="O30" authorId="0" shapeId="0">
       <text>
         <t>Random: 1027.0
 Human: 30826.4</t>
@@ -451,7 +454,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0">
+    <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>Random: 29.0
 Human: 302.8</t>
@@ -464,61 +467,75 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="O34" authorId="0" shapeId="0">
       <text>
         <t>Random: 52.0
 Human: 3035.0</t>
       </text>
     </comment>
-    <comment ref="N36" authorId="0" shapeId="0">
+    <comment ref="C36" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O36" authorId="0" shapeId="0">
       <text>
         <t>Random: 1598.0
 Human: 2665.5</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
+    <comment ref="C37" authorId="0" shapeId="0">
+      <text>
+        <t>EXCLUDED_SEEDS: Krull, seed 710
+Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
+취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
+      </text>
+    </comment>
+    <comment ref="O38" authorId="0" shapeId="0">
       <text>
         <t>Random: 258.5
 Human: 22736.3</t>
       </text>
     </comment>
-    <comment ref="N40" authorId="0" shapeId="0">
+    <comment ref="O40" authorId="0" shapeId="0">
       <text>
         <t>Random: 307.3
 Human: 6951.6</t>
       </text>
     </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
+    <comment ref="O42" authorId="0" shapeId="0">
       <text>
         <t>Random: -20.7
 Human: 14.6</t>
       </text>
     </comment>
-    <comment ref="N44" authorId="0" shapeId="0">
+    <comment ref="O44" authorId="0" shapeId="0">
       <text>
         <t>Random: 24.9
 Human: 69571.3</t>
       </text>
     </comment>
-    <comment ref="N46" authorId="0" shapeId="0">
+    <comment ref="O46" authorId="0" shapeId="0">
       <text>
         <t>Random: 163.9
 Human: 13455.0</t>
       </text>
     </comment>
-    <comment ref="N48" authorId="0" shapeId="0">
+    <comment ref="O48" authorId="0" shapeId="0">
       <text>
         <t>Random: 11.5
 Human: 7845.0</t>
       </text>
     </comment>
-    <comment ref="N50" authorId="0" shapeId="0">
+    <comment ref="O50" authorId="0" shapeId="0">
       <text>
         <t>Random: 68.4
 Human: 42054.7</t>
       </text>
     </comment>
-    <comment ref="N52" authorId="0" shapeId="0">
+    <comment ref="O52" authorId="0" shapeId="0">
       <text>
         <t>Random: 533.4
 Human: 11693.2</t>
@@ -817,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -832,11 +849,12 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,44 +881,47 @@
         <v>2010</v>
       </c>
       <c r="G1" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H1" s="1" t="n">
         <v>2710</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>3290</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>6010</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>6020</v>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>DramaXS (논문 점수)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -926,34 +947,35 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>608.00</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>1376.00</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="3" t="n">
         <v>820</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>1051.5</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>231.5</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="R2" s="6" t="n">
         <v>0.03355121088711431</v>
       </c>
     </row>
@@ -977,32 +999,33 @@
       <c r="E3" s="7" t="inlineStr"/>
       <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>705.00</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>1169.00</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="9" t="n">
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="9" t="n">
         <v>972.25</v>
       </c>
-      <c r="P3" s="9" t="n">
+      <c r="Q3" s="9" t="n">
         <v>79.25</v>
       </c>
-      <c r="Q3" s="10" t="n">
+      <c r="R3" s="10" t="n">
         <v>-0.01148567370541602</v>
       </c>
     </row>
@@ -1026,34 +1049,35 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>92.60</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>140.325</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>9.324999999999989</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>0.005441442492851717</v>
       </c>
     </row>
@@ -1077,32 +1101,33 @@
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>139.80</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="9" t="n">
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="9" t="n">
         <v>130.175</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="Q5" s="9" t="n">
         <v>10.14999999999998</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="R5" s="10" t="n">
         <v>-0.005922856976133498</v>
       </c>
     </row>
@@ -1128,32 +1153,33 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>521.80</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
         <v>539</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>383.5</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="Q6" s="5" t="n">
         <v>-155.5</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>-0.2992686682063125</v>
       </c>
     </row>
@@ -1179,30 +1205,31 @@
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>428.40</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="9" t="n">
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="9" t="n">
         <v>449.925</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="Q7" s="9" t="n">
         <v>66.42499999999995</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="R7" s="10" t="n">
         <v>0.1278387220939183</v>
       </c>
     </row>
@@ -1232,28 +1259,29 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="3" t="n">
         <v>1632</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="Q8" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>0.005787804613362595</v>
       </c>
     </row>
@@ -1283,26 +1311,27 @@
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="9" t="n">
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="9" t="n">
         <v>1397.5</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
         <v>282.5</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="R9" s="10" t="n">
         <v>-0.03406364173489444</v>
       </c>
     </row>
@@ -1327,33 +1356,34 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>870.00</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>281.00</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>464.00</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>458.75</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="Q10" s="5" t="n">
         <v>321.75</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>0.4354445797807552</v>
       </c>
     </row>
@@ -1378,31 +1408,32 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>339.00</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>324.00</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="9" t="n">
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
+      <c r="P11" s="9" t="n">
         <v>278.75</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="Q11" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="R11" s="10" t="n">
         <v>-0.243605359317905</v>
       </c>
     </row>
@@ -1429,35 +1460,36 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>8100.00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4000.00</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="3" t="n">
         <v>10860</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>10775</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>-85</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="R12" s="6" t="n">
         <v>-0.002440600100495298</v>
       </c>
     </row>
@@ -1484,33 +1516,34 @@
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>4300.00</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>4900.00</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="9" t="n">
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr"/>
+      <c r="P13" s="9" t="n">
         <v>8600</v>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="Q13" s="9" t="n">
         <v>2175</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>-0.06245064963032087</v>
       </c>
     </row>
@@ -1537,39 +1570,40 @@
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>25.80</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>32.20</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>63.2</v>
       </c>
-      <c r="P14" s="5" t="n">
+      <c r="Q14" s="5" t="n">
         <v>-14.8</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="R14" s="6" t="n">
         <v>-1.233333333333333</v>
       </c>
     </row>
@@ -1596,37 +1630,38 @@
       </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>36.00</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="9" t="n">
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
+      <c r="P15" s="9" t="n">
         <v>75.34999999999999</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="Q15" s="9" t="n">
         <v>12.14999999999999</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="R15" s="10" t="n">
         <v>1.012499999999999</v>
       </c>
     </row>
@@ -1651,33 +1686,34 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9.70</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>14.725</v>
       </c>
-      <c r="P16" s="5" t="n">
+      <c r="Q16" s="5" t="n">
         <v>7.725</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="R16" s="6" t="n">
         <v>0.2682291666666666</v>
       </c>
     </row>
@@ -1702,31 +1738,32 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>10.60</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>17.20</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="9" t="n">
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="9" t="n">
         <v>16.55</v>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="Q17" s="9" t="n">
         <v>1.825000000000001</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="R17" s="10" t="n">
         <v>0.06336805555555559</v>
       </c>
     </row>
@@ -1757,31 +1794,32 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1450.00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="3" t="n">
         <v>1642</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="P18" s="4" t="n">
         <v>1382.5</v>
       </c>
-      <c r="P18" s="5" t="n">
+      <c r="Q18" s="5" t="n">
         <v>-259.5</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="R18" s="6" t="n">
         <v>-0.03945687872521591</v>
       </c>
     </row>
@@ -1812,29 +1850,30 @@
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>2260.00</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="9" t="n">
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="9" t="n">
         <v>1550</v>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="Q19" s="9" t="n">
         <v>167.5</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="R19" s="10" t="n">
         <v>0.02546831285731663</v>
       </c>
     </row>
@@ -1859,33 +1898,34 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>73510.00</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>66980.00</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>82640.00</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
         <v>83931</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>76802.5</v>
       </c>
-      <c r="P20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>-7128.5</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="R20" s="6" t="n">
         <v>-0.2845833549577027</v>
       </c>
     </row>
@@ -1910,31 +1950,32 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>72700.00</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>77110.00</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>71030.00</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="9" t="n">
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
+      <c r="P21" s="9" t="n">
         <v>74437.5</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="Q21" s="9" t="n">
         <v>2365</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="R21" s="10" t="n">
         <v>-0.09441532362698561</v>
       </c>
     </row>
@@ -1964,28 +2005,29 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>153.50</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>255.00</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="P22" s="4" t="n">
         <v>187.25</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="Q22" s="5" t="n">
         <v>-13.75</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="R22" s="6" t="n">
         <v>-0.007559513991973171</v>
       </c>
     </row>
@@ -2015,26 +2057,27 @@
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>211.50</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>124.50</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="9" t="n">
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="9" t="n">
         <v>151</v>
       </c>
-      <c r="P23" s="9" t="n">
+      <c r="Q23" s="9" t="n">
         <v>36.25</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="R23" s="10" t="n">
         <v>-0.01992962779702018</v>
       </c>
     </row>
@@ -2053,19 +2096,24 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="O24" s="4" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2082,21 +2130,26 @@
       <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="9" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
       <c r="P25" s="9" t="inlineStr"/>
-      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="R25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2122,34 +2175,35 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1952.00</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="n">
         <v>1311.5</v>
       </c>
-      <c r="P26" s="5" t="n">
+      <c r="Q26" s="5" t="n">
         <v>526.5</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="R26" s="6" t="n">
         <v>0.123316547605106</v>
       </c>
     </row>
@@ -2174,35 +2228,40 @@
           <t>2540.00</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>1291.00</t>
+        </is>
+      </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>2224.00</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="9" t="n">
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="9" t="n">
         <v>1319.25</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="Q27" s="9" t="n">
         <v>7.75</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="R27" s="10" t="n">
         <v>0.001815200843190069</v>
       </c>
     </row>
@@ -2229,35 +2288,36 @@
           <t>1016.00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2896.00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2150.00</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>1676.00</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="3" t="n">
         <v>2757</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="P28" s="4" t="n">
         <v>1934.5</v>
       </c>
-      <c r="P28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>-822.5</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="R28" s="6" t="n">
         <v>-0.3816882453942178</v>
       </c>
     </row>
@@ -2284,33 +2344,34 @@
           <t>1082.00</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>2506.00</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>3132.00</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>2030.00</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="9" t="n">
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="9" t="n">
         <v>2187.5</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="Q29" s="9" t="n">
         <v>253</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="R29" s="10" t="n">
         <v>0.1174068402246044</v>
       </c>
     </row>
@@ -2337,35 +2398,36 @@
           <t>7510.00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>3622.50</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>13517.00</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>7107.50</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="3" t="n">
         <v>7946</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="P30" s="4" t="n">
         <v>7949.75</v>
       </c>
-      <c r="P30" s="5" t="n">
+      <c r="Q30" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="R30" s="6" t="n">
         <v>0.0001258414598951657</v>
       </c>
     </row>
@@ -2392,33 +2454,34 @@
           <t>3155.00</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>7488.00</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>13340.00</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>3556.50</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="9" t="n">
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="9" t="n">
         <v>7987.125</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="Q31" s="9" t="n">
         <v>37.375</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="R31" s="10" t="n">
         <v>0.001254219883621818</v>
       </c>
     </row>
@@ -2449,31 +2512,32 @@
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>520.00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="P32" s="4" t="n">
         <v>428.75</v>
       </c>
-      <c r="P32" s="5" t="n">
+      <c r="Q32" s="5" t="n">
         <v>56.75</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="R32" s="6" t="n">
         <v>0.2072680788897005</v>
       </c>
     </row>
@@ -2504,29 +2568,30 @@
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>615.00</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>605.00</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
-      <c r="O33" s="9" t="n">
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="9" t="n">
         <v>535</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="Q33" s="9" t="n">
         <v>106.25</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="R33" s="10" t="n">
         <v>0.3880569758948137</v>
       </c>
     </row>
@@ -2559,25 +2624,26 @@
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>1420.00</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="P34" s="4" t="n">
         <v>1350</v>
       </c>
-      <c r="P34" s="5" t="n">
+      <c r="Q34" s="5" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="R34" s="6" t="n">
         <v>-0.01139792155548106</v>
       </c>
     </row>
@@ -2610,23 +2676,24 @@
       </c>
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>1140.00</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="9" t="n">
+      <c r="N35" s="7" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="9" t="n">
         <v>1335</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="Q35" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="R35" s="10" t="n">
         <v>-0.005028494803888703</v>
       </c>
     </row>
@@ -2641,7 +2708,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>8075.00</t>
         </is>
@@ -2659,30 +2726,31 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>10649.00</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="3" t="n">
         <v>9693</v>
       </c>
-      <c r="O36" s="4" t="n">
-        <v>8875.799999999999</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>-817.2000000000007</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>-0.7655269320843098</v>
+      <c r="P36" s="4" t="n">
+        <v>9076</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>-617</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>-0.5779859484777518</v>
       </c>
     </row>
     <row r="37">
@@ -2696,7 +2764,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>7926.00</t>
         </is>
@@ -2714,28 +2782,29 @@
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>10233.00</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
-      <c r="O37" s="9" t="n">
-        <v>9240.4</v>
-      </c>
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
       <c r="P37" s="9" t="n">
-        <v>364.6000000000004</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>0.3415456674473071</v>
+        <v>9569</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>493</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.4618266978922717</v>
       </c>
     </row>
     <row r="38">
@@ -2767,25 +2836,26 @@
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>19020.00</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="3" t="n">
         <v>23920</v>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="P38" s="4" t="n">
         <v>16480</v>
       </c>
-      <c r="P38" s="5" t="n">
+      <c r="Q38" s="5" t="n">
         <v>-7440</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="R38" s="6" t="n">
         <v>-0.3309932466700478</v>
       </c>
     </row>
@@ -2818,23 +2888,24 @@
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>23080.00</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
-      <c r="O39" s="9" t="n">
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
+      <c r="P39" s="9" t="n">
         <v>16137.5</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="Q39" s="9" t="n">
         <v>342.5</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="R39" s="10" t="n">
         <v>-0.01523725631511981</v>
       </c>
     </row>
@@ -2867,25 +2938,26 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>1548.00</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="3" t="n">
         <v>2270</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="P40" s="4" t="n">
         <v>2460.25</v>
       </c>
-      <c r="P40" s="5" t="n">
+      <c r="Q40" s="5" t="n">
         <v>190.25</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="R40" s="6" t="n">
         <v>0.02863356561263037</v>
       </c>
     </row>
@@ -2918,23 +2990,24 @@
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>1847.00</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
-      <c r="O41" s="9" t="n">
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="8" t="inlineStr"/>
+      <c r="P41" s="9" t="n">
         <v>2525.25</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="Q41" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="R41" s="10" t="n">
         <v>0.009782821365681862</v>
       </c>
     </row>
@@ -2959,33 +3032,34 @@
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>21.00</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>11.80</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>-17.80</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="P42" s="4" t="n">
         <v>8.75</v>
       </c>
-      <c r="P42" s="5" t="n">
+      <c r="Q42" s="5" t="n">
         <v>-6.25</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="R42" s="6" t="n">
         <v>-0.1770538243626062</v>
       </c>
     </row>
@@ -3010,31 +3084,32 @@
       </c>
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>20.80</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>13.90</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
-      <c r="O43" s="9" t="n">
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
+      <c r="P43" s="9" t="n">
         <v>14.75</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="Q43" s="9" t="n">
         <v>5.999999999999998</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="R43" s="10" t="n">
         <v>0.169971671388102</v>
       </c>
     </row>
@@ -3067,25 +3142,26 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="3" t="n">
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="O44" s="4" t="n">
+      <c r="P44" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="P44" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="6" t="n">
         <v>0.0001437888948960694</v>
       </c>
     </row>
@@ -3118,23 +3194,24 @@
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>-219.40</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
-      <c r="O45" s="9" t="n">
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
+      <c r="P45" s="9" t="n">
         <v>-4.850000000000001</v>
       </c>
-      <c r="P45" s="9" t="n">
+      <c r="Q45" s="9" t="n">
         <v>104.85</v>
       </c>
-      <c r="Q45" s="10" t="n">
+      <c r="R45" s="10" t="n">
         <v>-0.001507626562985287</v>
       </c>
     </row>
@@ -3167,25 +3244,26 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="3" t="n">
         <v>796</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="P46" s="4" t="n">
         <v>1446.25</v>
       </c>
-      <c r="P46" s="5" t="n">
+      <c r="Q46" s="5" t="n">
         <v>650.25</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="R46" s="6" t="n">
         <v>0.04892371587001828</v>
       </c>
     </row>
@@ -3218,23 +3296,24 @@
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
-      <c r="O47" s="9" t="n">
+      <c r="N47" s="7" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr"/>
+      <c r="P47" s="9" t="n">
         <v>1496.25</v>
       </c>
-      <c r="P47" s="9" t="n">
+      <c r="Q47" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="R47" s="10" t="n">
         <v>0.003761915868513517</v>
       </c>
     </row>
@@ -3259,33 +3338,34 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>14670.00</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>7030.00</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>7860.00</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="3" t="n">
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="3" t="n">
         <v>14020</v>
       </c>
-      <c r="O48" s="4" t="n">
+      <c r="P48" s="4" t="n">
         <v>11812.5</v>
       </c>
-      <c r="P48" s="5" t="n">
+      <c r="Q48" s="5" t="n">
         <v>-2207.5</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="R48" s="6" t="n">
         <v>-0.2818025148401098</v>
       </c>
     </row>
@@ -3310,31 +3390,32 @@
       <c r="F49" s="7" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>15330.00</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>8520.00</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>8500.00</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
-      <c r="O49" s="9" t="n">
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr"/>
+      <c r="P49" s="9" t="n">
         <v>12537.5</v>
       </c>
-      <c r="P49" s="9" t="n">
+      <c r="Q49" s="9" t="n">
         <v>725</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="R49" s="10" t="n">
         <v>0.09255122231441884</v>
       </c>
     </row>
@@ -3359,33 +3440,34 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>824.00</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>432.00</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>534.00</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="3" t="n">
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="P50" s="4" t="n">
         <v>626</v>
       </c>
-      <c r="P50" s="5" t="n">
+      <c r="Q50" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="R50" s="6" t="n">
         <v>0.003072430769084201</v>
       </c>
     </row>
@@ -3410,31 +3492,32 @@
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>778.00</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>474.00</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>458.00</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
-      <c r="O51" s="9" t="n">
+      <c r="N51" s="7" t="inlineStr"/>
+      <c r="O51" s="8" t="inlineStr"/>
+      <c r="P51" s="9" t="n">
         <v>558</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="Q51" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="R51" s="10" t="n">
         <v>-0.001619575909284695</v>
       </c>
     </row>
@@ -3467,25 +3550,26 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="3" t="n">
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="3" t="n">
         <v>7387</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="P52" s="4" t="n">
         <v>5269.5</v>
       </c>
-      <c r="P52" s="5" t="n">
+      <c r="Q52" s="5" t="n">
         <v>-2117.5</v>
       </c>
-      <c r="Q52" s="6" t="n">
+      <c r="R52" s="6" t="n">
         <v>-0.1897435437911074</v>
       </c>
     </row>
@@ -3518,23 +3602,24 @@
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr"/>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
-      <c r="O53" s="9" t="n">
+      <c r="N53" s="7" t="inlineStr"/>
+      <c r="O53" s="8" t="inlineStr"/>
+      <c r="P53" s="9" t="n">
         <v>6038.75</v>
       </c>
-      <c r="P53" s="9" t="n">
+      <c r="Q53" s="9" t="n">
         <v>769.25</v>
       </c>
-      <c r="Q53" s="10" t="n">
+      <c r="R53" s="10" t="n">
         <v>0.06893044678220039</v>
       </c>
     </row>
@@ -3550,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P220"/>
+  <dimension ref="A1:P223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3715,7 +3800,7 @@
       <c r="O2" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P2" s="14" t="n">
+      <c r="P2" s="15" t="n">
         <v>46277.48542824074</v>
       </c>
     </row>
@@ -3785,7 +3870,7 @@
       <c r="O3" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P3" s="14" t="n">
+      <c r="P3" s="15" t="n">
         <v>46277.51052083333</v>
       </c>
     </row>
@@ -3855,7 +3940,7 @@
       <c r="O4" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P4" s="14" t="n">
+      <c r="P4" s="15" t="n">
         <v>46277.51194444444</v>
       </c>
     </row>
@@ -3925,7 +4010,7 @@
       <c r="O5" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P5" s="14" t="n">
+      <c r="P5" s="15" t="n">
         <v>46277.58818287037</v>
       </c>
     </row>
@@ -3995,7 +4080,7 @@
       <c r="O6" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P6" s="14" t="n">
+      <c r="P6" s="15" t="n">
         <v>46277.5909375</v>
       </c>
     </row>
@@ -4061,7 +4146,7 @@
       <c r="O7" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P7" s="14" t="n">
+      <c r="P7" s="15" t="n">
         <v>46277.63061342593</v>
       </c>
     </row>
@@ -4127,7 +4212,7 @@
       <c r="O8" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="15" t="n">
         <v>46277.66618055556</v>
       </c>
     </row>
@@ -4197,7 +4282,7 @@
       <c r="O9" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P9" s="14" t="n">
+      <c r="P9" s="15" t="n">
         <v>46277.78224537037</v>
       </c>
     </row>
@@ -4267,7 +4352,7 @@
       <c r="O10" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P10" s="14" t="n">
+      <c r="P10" s="15" t="n">
         <v>46277.79376157407</v>
       </c>
     </row>
@@ -4333,7 +4418,7 @@
       <c r="O11" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="15" t="n">
         <v>46277.83049768519</v>
       </c>
     </row>
@@ -4403,7 +4488,7 @@
       <c r="O12" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="15" t="n">
         <v>46277.86043981482</v>
       </c>
     </row>
@@ -4473,7 +4558,7 @@
       <c r="O13" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P13" s="14" t="n">
+      <c r="P13" s="15" t="n">
         <v>46277.87179398148</v>
       </c>
     </row>
@@ -4543,7 +4628,7 @@
       <c r="O14" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P14" s="14" t="n">
+      <c r="P14" s="15" t="n">
         <v>46278.05765046296</v>
       </c>
     </row>
@@ -4613,7 +4698,7 @@
       <c r="O15" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P15" s="14" t="n">
+      <c r="P15" s="15" t="n">
         <v>46278.06443287037</v>
       </c>
     </row>
@@ -4683,7 +4768,7 @@
       <c r="O16" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P16" s="14" t="n">
+      <c r="P16" s="15" t="n">
         <v>46278.08553240741</v>
       </c>
     </row>
@@ -4753,7 +4838,7 @@
       <c r="O17" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P17" s="14" t="n">
+      <c r="P17" s="15" t="n">
         <v>46278.08700231482</v>
       </c>
     </row>
@@ -4823,7 +4908,7 @@
       <c r="O18" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P18" s="14" t="n">
+      <c r="P18" s="15" t="n">
         <v>46278.08775462963</v>
       </c>
     </row>
@@ -4893,7 +4978,7 @@
       <c r="O19" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P19" s="14" t="n">
+      <c r="P19" s="15" t="n">
         <v>46278.21667824074</v>
       </c>
     </row>
@@ -4963,7 +5048,7 @@
       <c r="O20" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P20" s="14" t="n">
+      <c r="P20" s="15" t="n">
         <v>46278.24315972222</v>
       </c>
     </row>
@@ -5033,7 +5118,7 @@
       <c r="O21" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P21" s="14" t="n">
+      <c r="P21" s="15" t="n">
         <v>46278.26704861111</v>
       </c>
     </row>
@@ -5103,7 +5188,7 @@
       <c r="O22" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P22" s="14" t="n">
+      <c r="P22" s="15" t="n">
         <v>46278.26740740741</v>
       </c>
     </row>
@@ -5173,7 +5258,7 @@
       <c r="O23" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P23" s="14" t="n">
+      <c r="P23" s="15" t="n">
         <v>46278.27628472223</v>
       </c>
     </row>
@@ -5243,7 +5328,7 @@
       <c r="O24" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P24" s="14" t="n">
+      <c r="P24" s="15" t="n">
         <v>46278.27751157407</v>
       </c>
     </row>
@@ -5313,7 +5398,7 @@
       <c r="O25" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P25" s="14" t="n">
+      <c r="P25" s="15" t="n">
         <v>46278.29635416667</v>
       </c>
     </row>
@@ -5383,7 +5468,7 @@
       <c r="O26" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P26" s="14" t="n">
+      <c r="P26" s="15" t="n">
         <v>46278.35381944444</v>
       </c>
     </row>
@@ -5453,7 +5538,7 @@
       <c r="O27" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P27" s="14" t="n">
+      <c r="P27" s="15" t="n">
         <v>46278.35512731481</v>
       </c>
     </row>
@@ -5523,7 +5608,7 @@
       <c r="O28" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P28" s="14" t="n">
+      <c r="P28" s="15" t="n">
         <v>46278.4143287037</v>
       </c>
     </row>
@@ -5593,7 +5678,7 @@
       <c r="O29" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P29" s="14" t="n">
+      <c r="P29" s="15" t="n">
         <v>46278.49403935186</v>
       </c>
     </row>
@@ -5663,7 +5748,7 @@
       <c r="O30" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P30" s="14" t="n">
+      <c r="P30" s="15" t="n">
         <v>46278.65908564815</v>
       </c>
     </row>
@@ -5733,7 +5818,7 @@
       <c r="O31" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P31" s="14" t="n">
+      <c r="P31" s="15" t="n">
         <v>46278.67763888889</v>
       </c>
     </row>
@@ -5803,7 +5888,7 @@
       <c r="O32" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P32" s="14" t="n">
+      <c r="P32" s="15" t="n">
         <v>46278.69815972223</v>
       </c>
     </row>
@@ -5873,7 +5958,7 @@
       <c r="O33" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P33" s="14" t="n">
+      <c r="P33" s="15" t="n">
         <v>46278.72652777778</v>
       </c>
     </row>
@@ -5943,7 +6028,7 @@
       <c r="O34" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P34" s="14" t="n">
+      <c r="P34" s="15" t="n">
         <v>46278.84016203704</v>
       </c>
     </row>
@@ -6013,7 +6098,7 @@
       <c r="O35" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P35" s="14" t="n">
+      <c r="P35" s="15" t="n">
         <v>46278.85677083334</v>
       </c>
     </row>
@@ -6083,7 +6168,7 @@
       <c r="O36" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P36" s="14" t="n">
+      <c r="P36" s="15" t="n">
         <v>46278.8781712963</v>
       </c>
     </row>
@@ -6153,7 +6238,7 @@
       <c r="O37" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P37" s="14" t="n">
+      <c r="P37" s="15" t="n">
         <v>46278.90575231481</v>
       </c>
     </row>
@@ -6223,7 +6308,7 @@
       <c r="O38" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P38" s="14" t="n">
+      <c r="P38" s="15" t="n">
         <v>46278.94225694444</v>
       </c>
     </row>
@@ -6293,7 +6378,7 @@
       <c r="O39" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P39" s="14" t="n">
+      <c r="P39" s="15" t="n">
         <v>46279.06255787037</v>
       </c>
     </row>
@@ -6363,7 +6448,7 @@
       <c r="O40" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P40" s="14" t="n">
+      <c r="P40" s="15" t="n">
         <v>46279.09913194444</v>
       </c>
     </row>
@@ -6433,7 +6518,7 @@
       <c r="O41" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P41" s="14" t="n">
+      <c r="P41" s="15" t="n">
         <v>46279.15164351852</v>
       </c>
     </row>
@@ -6503,7 +6588,7 @@
       <c r="O42" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P42" s="14" t="n">
+      <c r="P42" s="15" t="n">
         <v>46279.15413194444</v>
       </c>
     </row>
@@ -6573,7 +6658,7 @@
       <c r="O43" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P43" s="14" t="n">
+      <c r="P43" s="15" t="n">
         <v>46279.17649305556</v>
       </c>
     </row>
@@ -6643,7 +6728,7 @@
       <c r="O44" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P44" s="14" t="n">
+      <c r="P44" s="15" t="n">
         <v>46279.22236111111</v>
       </c>
     </row>
@@ -6713,7 +6798,7 @@
       <c r="O45" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P45" s="14" t="n">
+      <c r="P45" s="15" t="n">
         <v>46279.23153935185</v>
       </c>
     </row>
@@ -6783,7 +6868,7 @@
       <c r="O46" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P46" s="14" t="n">
+      <c r="P46" s="15" t="n">
         <v>46279.2678125</v>
       </c>
     </row>
@@ -6853,7 +6938,7 @@
       <c r="O47" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P47" s="14" t="n">
+      <c r="P47" s="15" t="n">
         <v>46279.291875</v>
       </c>
     </row>
@@ -6923,7 +7008,7 @@
       <c r="O48" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P48" s="14" t="n">
+      <c r="P48" s="15" t="n">
         <v>46279.29552083334</v>
       </c>
     </row>
@@ -6993,7 +7078,7 @@
       <c r="O49" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P49" s="14" t="n">
+      <c r="P49" s="15" t="n">
         <v>46279.32731481481</v>
       </c>
     </row>
@@ -7063,7 +7148,7 @@
       <c r="O50" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P50" s="14" t="n">
+      <c r="P50" s="15" t="n">
         <v>46279.37328703704</v>
       </c>
     </row>
@@ -7133,7 +7218,7 @@
       <c r="O51" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P51" s="14" t="n">
+      <c r="P51" s="15" t="n">
         <v>46279.41740740741</v>
       </c>
     </row>
@@ -7203,7 +7288,7 @@
       <c r="O52" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P52" s="14" t="n">
+      <c r="P52" s="15" t="n">
         <v>46279.45078703704</v>
       </c>
     </row>
@@ -7273,7 +7358,7 @@
       <c r="O53" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P53" s="14" t="n">
+      <c r="P53" s="15" t="n">
         <v>46279.47466435185</v>
       </c>
     </row>
@@ -7343,7 +7428,7 @@
       <c r="O54" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P54" s="14" t="n">
+      <c r="P54" s="15" t="n">
         <v>46279.49469907407</v>
       </c>
     </row>
@@ -7413,7 +7498,7 @@
       <c r="O55" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P55" s="14" t="n">
+      <c r="P55" s="15" t="n">
         <v>46279.50685185185</v>
       </c>
     </row>
@@ -7483,7 +7568,7 @@
       <c r="O56" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P56" s="14" t="n">
+      <c r="P56" s="15" t="n">
         <v>46279.58126157407</v>
       </c>
     </row>
@@ -7553,7 +7638,7 @@
       <c r="O57" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P57" s="14" t="n">
+      <c r="P57" s="15" t="n">
         <v>46279.62493055555</v>
       </c>
     </row>
@@ -7623,7 +7708,7 @@
       <c r="O58" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P58" s="14" t="n">
+      <c r="P58" s="15" t="n">
         <v>46279.64979166666</v>
       </c>
     </row>
@@ -7693,7 +7778,7 @@
       <c r="O59" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P59" s="14" t="n">
+      <c r="P59" s="15" t="n">
         <v>46279.67836805555</v>
       </c>
     </row>
@@ -7763,7 +7848,7 @@
       <c r="O60" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P60" s="14" t="n">
+      <c r="P60" s="15" t="n">
         <v>46279.68984953704</v>
       </c>
     </row>
@@ -7833,7 +7918,7 @@
       <c r="O61" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P61" s="14" t="n">
+      <c r="P61" s="15" t="n">
         <v>46279.75571759259</v>
       </c>
     </row>
@@ -7903,7 +7988,7 @@
       <c r="O62" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P62" s="14" t="n">
+      <c r="P62" s="15" t="n">
         <v>46279.76197916667</v>
       </c>
     </row>
@@ -7973,7 +8058,7 @@
       <c r="O63" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P63" s="14" t="n">
+      <c r="P63" s="15" t="n">
         <v>46279.82975694445</v>
       </c>
     </row>
@@ -8043,7 +8128,7 @@
       <c r="O64" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P64" s="14" t="n">
+      <c r="P64" s="15" t="n">
         <v>46279.83283564815</v>
       </c>
     </row>
@@ -8113,7 +8198,7 @@
       <c r="O65" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P65" s="14" t="n">
+      <c r="P65" s="15" t="n">
         <v>46279.86658564815</v>
       </c>
     </row>
@@ -8183,7 +8268,7 @@
       <c r="O66" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P66" s="14" t="n">
+      <c r="P66" s="15" t="n">
         <v>46279.86854166666</v>
       </c>
     </row>
@@ -8253,7 +8338,7 @@
       <c r="O67" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P67" s="14" t="n">
+      <c r="P67" s="15" t="n">
         <v>46279.88961805555</v>
       </c>
     </row>
@@ -8323,7 +8408,7 @@
       <c r="O68" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P68" s="14" t="n">
+      <c r="P68" s="15" t="n">
         <v>46279.92807870371</v>
       </c>
     </row>
@@ -8393,7 +8478,7 @@
       <c r="O69" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P69" s="14" t="n">
+      <c r="P69" s="15" t="n">
         <v>46279.95943287037</v>
       </c>
     </row>
@@ -8463,7 +8548,7 @@
       <c r="O70" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P70" s="14" t="n">
+      <c r="P70" s="15" t="n">
         <v>46280.03707175926</v>
       </c>
     </row>
@@ -8533,7 +8618,7 @@
       <c r="O71" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P71" s="14" t="n">
+      <c r="P71" s="15" t="n">
         <v>46280.04559027778</v>
       </c>
     </row>
@@ -8603,7 +8688,7 @@
       <c r="O72" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P72" s="14" t="n">
+      <c r="P72" s="15" t="n">
         <v>46280.05359953704</v>
       </c>
     </row>
@@ -8673,7 +8758,7 @@
       <c r="O73" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P73" s="14" t="n">
+      <c r="P73" s="15" t="n">
         <v>46280.10788194444</v>
       </c>
     </row>
@@ -8743,7 +8828,7 @@
       <c r="O74" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P74" s="14" t="n">
+      <c r="P74" s="15" t="n">
         <v>46280.1452199074</v>
       </c>
     </row>
@@ -8813,7 +8898,7 @@
       <c r="O75" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P75" s="14" t="n">
+      <c r="P75" s="15" t="n">
         <v>46280.19780092593</v>
       </c>
     </row>
@@ -8883,7 +8968,7 @@
       <c r="O76" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P76" s="14" t="n">
+      <c r="P76" s="15" t="n">
         <v>46280.24451388889</v>
       </c>
     </row>
@@ -8953,7 +9038,7 @@
       <c r="O77" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P77" s="14" t="n">
+      <c r="P77" s="15" t="n">
         <v>46280.24539351852</v>
       </c>
     </row>
@@ -9023,7 +9108,7 @@
       <c r="O78" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P78" s="14" t="n">
+      <c r="P78" s="15" t="n">
         <v>46280.27893518518</v>
       </c>
     </row>
@@ -9093,7 +9178,7 @@
       <c r="O79" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P79" s="14" t="n">
+      <c r="P79" s="15" t="n">
         <v>46280.31445601852</v>
       </c>
     </row>
@@ -9163,7 +9248,7 @@
       <c r="O80" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P80" s="14" t="n">
+      <c r="P80" s="15" t="n">
         <v>46280.35971064815</v>
       </c>
     </row>
@@ -9233,7 +9318,7 @@
       <c r="O81" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P81" s="14" t="n">
+      <c r="P81" s="15" t="n">
         <v>46280.39851851852</v>
       </c>
     </row>
@@ -9303,7 +9388,7 @@
       <c r="O82" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P82" s="14" t="n">
+      <c r="P82" s="15" t="n">
         <v>46280.41853009259</v>
       </c>
     </row>
@@ -9373,7 +9458,7 @@
       <c r="O83" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P83" s="14" t="n">
+      <c r="P83" s="15" t="n">
         <v>46280.44364583334</v>
       </c>
     </row>
@@ -9443,7 +9528,7 @@
       <c r="O84" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P84" s="14" t="n">
+      <c r="P84" s="15" t="n">
         <v>46280.4897337963</v>
       </c>
     </row>
@@ -9513,7 +9598,7 @@
       <c r="O85" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P85" s="14" t="n">
+      <c r="P85" s="15" t="n">
         <v>46280.50119212963</v>
       </c>
     </row>
@@ -9583,7 +9668,7 @@
       <c r="O86" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P86" s="14" t="n">
+      <c r="P86" s="15" t="n">
         <v>46280.5120949074</v>
       </c>
     </row>
@@ -9653,7 +9738,7 @@
       <c r="O87" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P87" s="14" t="n">
+      <c r="P87" s="15" t="n">
         <v>46280.51324074074</v>
       </c>
     </row>
@@ -9723,7 +9808,7 @@
       <c r="O88" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P88" s="14" t="n">
+      <c r="P88" s="15" t="n">
         <v>46280.52025462963</v>
       </c>
     </row>
@@ -9793,7 +9878,7 @@
       <c r="O89" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P89" s="14" t="n">
+      <c r="P89" s="15" t="n">
         <v>46280.54377314815</v>
       </c>
     </row>
@@ -9863,7 +9948,7 @@
       <c r="O90" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P90" s="14" t="n">
+      <c r="P90" s="15" t="n">
         <v>46280.59976851852</v>
       </c>
     </row>
@@ -9933,7 +10018,7 @@
       <c r="O91" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P91" s="14" t="n">
+      <c r="P91" s="15" t="n">
         <v>46280.61607638889</v>
       </c>
     </row>
@@ -10003,7 +10088,7 @@
       <c r="O92" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P92" s="14" t="n">
+      <c r="P92" s="15" t="n">
         <v>46280.68962962963</v>
       </c>
     </row>
@@ -10073,7 +10158,7 @@
       <c r="O93" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P93" s="14" t="n">
+      <c r="P93" s="15" t="n">
         <v>46280.71888888889</v>
       </c>
     </row>
@@ -10143,7 +10228,7 @@
       <c r="O94" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P94" s="14" t="n">
+      <c r="P94" s="15" t="n">
         <v>46280.74344907407</v>
       </c>
     </row>
@@ -10213,7 +10298,7 @@
       <c r="O95" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P95" s="14" t="n">
+      <c r="P95" s="15" t="n">
         <v>46280.77847222222</v>
       </c>
     </row>
@@ -10283,7 +10368,7 @@
       <c r="O96" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P96" s="14" t="n">
+      <c r="P96" s="15" t="n">
         <v>46280.84616898148</v>
       </c>
     </row>
@@ -10353,7 +10438,7 @@
       <c r="O97" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P97" s="14" t="n">
+      <c r="P97" s="15" t="n">
         <v>46280.86395833334</v>
       </c>
     </row>
@@ -10423,7 +10508,7 @@
       <c r="O98" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P98" s="14" t="n">
+      <c r="P98" s="15" t="n">
         <v>46280.89765046296</v>
       </c>
     </row>
@@ -10493,7 +10578,7 @@
       <c r="O99" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P99" s="14" t="n">
+      <c r="P99" s="15" t="n">
         <v>46280.90140046296</v>
       </c>
     </row>
@@ -10563,7 +10648,7 @@
       <c r="O100" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P100" s="14" t="n">
+      <c r="P100" s="15" t="n">
         <v>46280.92248842592</v>
       </c>
     </row>
@@ -10633,7 +10718,7 @@
       <c r="O101" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P101" s="14" t="n">
+      <c r="P101" s="15" t="n">
         <v>46280.94780092593</v>
       </c>
     </row>
@@ -10703,7 +10788,7 @@
       <c r="O102" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P102" s="14" t="n">
+      <c r="P102" s="15" t="n">
         <v>46281.03773148148</v>
       </c>
     </row>
@@ -10773,7 +10858,7 @@
       <c r="O103" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P103" s="14" t="n">
+      <c r="P103" s="15" t="n">
         <v>46281.05363425926</v>
       </c>
     </row>
@@ -10843,7 +10928,7 @@
       <c r="O104" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P104" s="14" t="n">
+      <c r="P104" s="15" t="n">
         <v>46281.17542824074</v>
       </c>
     </row>
@@ -10913,7 +10998,7 @@
       <c r="O105" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P105" s="14" t="n">
+      <c r="P105" s="15" t="n">
         <v>46281.23145833334</v>
       </c>
     </row>
@@ -10983,7 +11068,7 @@
       <c r="O106" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P106" s="14" t="n">
+      <c r="P106" s="15" t="n">
         <v>46281.26112268519</v>
       </c>
     </row>
@@ -11053,7 +11138,7 @@
       <c r="O107" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P107" s="14" t="n">
+      <c r="P107" s="15" t="n">
         <v>46281.34596064815</v>
       </c>
     </row>
@@ -11123,7 +11208,7 @@
       <c r="O108" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P108" s="14" t="n">
+      <c r="P108" s="15" t="n">
         <v>46281.41318287037</v>
       </c>
     </row>
@@ -11193,7 +11278,7 @@
       <c r="O109" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P109" s="14" t="n">
+      <c r="P109" s="15" t="n">
         <v>46281.47984953703</v>
       </c>
     </row>
@@ -11263,7 +11348,7 @@
       <c r="O110" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P110" s="14" t="n">
+      <c r="P110" s="15" t="n">
         <v>46281.48199074074</v>
       </c>
     </row>
@@ -11333,7 +11418,7 @@
       <c r="O111" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P111" s="14" t="n">
+      <c r="P111" s="15" t="n">
         <v>46281.55998842593</v>
       </c>
     </row>
@@ -11403,7 +11488,7 @@
       <c r="O112" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P112" s="14" t="n">
+      <c r="P112" s="15" t="n">
         <v>46281.56878472222</v>
       </c>
     </row>
@@ -11473,7 +11558,7 @@
       <c r="O113" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P113" s="14" t="n">
+      <c r="P113" s="15" t="n">
         <v>46281.60291666666</v>
       </c>
     </row>
@@ -11543,7 +11628,7 @@
       <c r="O114" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P114" s="14" t="n">
+      <c r="P114" s="15" t="n">
         <v>46281.60375</v>
       </c>
     </row>
@@ -11613,7 +11698,7 @@
       <c r="O115" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P115" s="14" t="n">
+      <c r="P115" s="15" t="n">
         <v>46281.61435185185</v>
       </c>
     </row>
@@ -11683,7 +11768,7 @@
       <c r="O116" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P116" s="14" t="n">
+      <c r="P116" s="15" t="n">
         <v>46281.64665509259</v>
       </c>
     </row>
@@ -11753,7 +11838,7 @@
       <c r="O117" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P117" s="14" t="n">
+      <c r="P117" s="15" t="n">
         <v>46281.67173611111</v>
       </c>
     </row>
@@ -11823,7 +11908,7 @@
       <c r="O118" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P118" s="14" t="n">
+      <c r="P118" s="15" t="n">
         <v>46281.72890046296</v>
       </c>
     </row>
@@ -11893,7 +11978,7 @@
       <c r="O119" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P119" s="14" t="n">
+      <c r="P119" s="15" t="n">
         <v>46281.7578587963</v>
       </c>
     </row>
@@ -11963,7 +12048,7 @@
       <c r="O120" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P120" s="14" t="n">
+      <c r="P120" s="15" t="n">
         <v>46281.80134259259</v>
       </c>
     </row>
@@ -12033,7 +12118,7 @@
       <c r="O121" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P121" s="14" t="n">
+      <c r="P121" s="15" t="n">
         <v>46281.85913194445</v>
       </c>
     </row>
@@ -12103,7 +12188,7 @@
       <c r="O122" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P122" s="14" t="n">
+      <c r="P122" s="15" t="n">
         <v>46281.86515046296</v>
       </c>
     </row>
@@ -12173,7 +12258,7 @@
       <c r="O123" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P123" s="14" t="n">
+      <c r="P123" s="15" t="n">
         <v>46281.93247685185</v>
       </c>
     </row>
@@ -12243,7 +12328,7 @@
       <c r="O124" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P124" s="14" t="n">
+      <c r="P124" s="15" t="n">
         <v>46281.96268518519</v>
       </c>
     </row>
@@ -12313,7 +12398,7 @@
       <c r="O125" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P125" s="14" t="n">
+      <c r="P125" s="15" t="n">
         <v>46281.96670138889</v>
       </c>
     </row>
@@ -12383,7 +12468,7 @@
       <c r="O126" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P126" s="14" t="n">
+      <c r="P126" s="15" t="n">
         <v>46282.01916666667</v>
       </c>
     </row>
@@ -12453,7 +12538,7 @@
       <c r="O127" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P127" s="14" t="n">
+      <c r="P127" s="15" t="n">
         <v>46282.07037037037</v>
       </c>
     </row>
@@ -12523,7 +12608,7 @@
       <c r="O128" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P128" s="14" t="n">
+      <c r="P128" s="15" t="n">
         <v>46282.08375</v>
       </c>
     </row>
@@ -12593,7 +12678,7 @@
       <c r="O129" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P129" s="14" t="n">
+      <c r="P129" s="15" t="n">
         <v>46282.14739583333</v>
       </c>
     </row>
@@ -12663,7 +12748,7 @@
       <c r="O130" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P130" s="14" t="n">
+      <c r="P130" s="15" t="n">
         <v>46282.15549768518</v>
       </c>
     </row>
@@ -12733,7 +12818,7 @@
       <c r="O131" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P131" s="14" t="n">
+      <c r="P131" s="15" t="n">
         <v>46282.16440972222</v>
       </c>
     </row>
@@ -12803,7 +12888,7 @@
       <c r="O132" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P132" s="14" t="n">
+      <c r="P132" s="15" t="n">
         <v>46282.18530092593</v>
       </c>
     </row>
@@ -12873,7 +12958,7 @@
       <c r="O133" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P133" s="14" t="n">
+      <c r="P133" s="15" t="n">
         <v>46282.21564814815</v>
       </c>
     </row>
@@ -12943,7 +13028,7 @@
       <c r="O134" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P134" s="14" t="n">
+      <c r="P134" s="15" t="n">
         <v>46282.2421412037</v>
       </c>
     </row>
@@ -13013,7 +13098,7 @@
       <c r="O135" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P135" s="14" t="n">
+      <c r="P135" s="15" t="n">
         <v>46282.32163194445</v>
       </c>
     </row>
@@ -13083,7 +13168,7 @@
       <c r="O136" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P136" s="14" t="n">
+      <c r="P136" s="15" t="n">
         <v>46282.33078703703</v>
       </c>
     </row>
@@ -13153,7 +13238,7 @@
       <c r="O137" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P137" s="14" t="n">
+      <c r="P137" s="15" t="n">
         <v>46282.36037037037</v>
       </c>
     </row>
@@ -13223,7 +13308,7 @@
       <c r="O138" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P138" s="14" t="n">
+      <c r="P138" s="15" t="n">
         <v>46282.3647337963</v>
       </c>
     </row>
@@ -13293,7 +13378,7 @@
       <c r="O139" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P139" s="14" t="n">
+      <c r="P139" s="15" t="n">
         <v>46282.38931712963</v>
       </c>
     </row>
@@ -13363,7 +13448,7 @@
       <c r="O140" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P140" s="14" t="n">
+      <c r="P140" s="15" t="n">
         <v>46282.3912037037</v>
       </c>
     </row>
@@ -13433,7 +13518,7 @@
       <c r="O141" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P141" s="14" t="n">
+      <c r="P141" s="15" t="n">
         <v>46282.4034375</v>
       </c>
     </row>
@@ -13503,7 +13588,7 @@
       <c r="O142" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P142" s="14" t="n">
+      <c r="P142" s="15" t="n">
         <v>46282.43136574074</v>
       </c>
     </row>
@@ -13573,7 +13658,7 @@
       <c r="O143" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P143" s="14" t="n">
+      <c r="P143" s="15" t="n">
         <v>46282.49684027778</v>
       </c>
     </row>
@@ -13643,7 +13728,7 @@
       <c r="O144" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P144" s="14" t="n">
+      <c r="P144" s="15" t="n">
         <v>46282.51994212963</v>
       </c>
     </row>
@@ -13713,7 +13798,7 @@
       <c r="O145" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P145" s="14" t="n">
+      <c r="P145" s="15" t="n">
         <v>46282.62939814815</v>
       </c>
     </row>
@@ -13783,7 +13868,7 @@
       <c r="O146" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P146" s="14" t="n">
+      <c r="P146" s="15" t="n">
         <v>46282.6515162037</v>
       </c>
     </row>
@@ -13853,7 +13938,7 @@
       <c r="O147" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P147" s="14" t="n">
+      <c r="P147" s="15" t="n">
         <v>46282.78369212963</v>
       </c>
     </row>
@@ -13923,7 +14008,7 @@
       <c r="O148" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P148" s="14" t="n">
+      <c r="P148" s="15" t="n">
         <v>46282.78776620371</v>
       </c>
     </row>
@@ -13993,7 +14078,7 @@
       <c r="O149" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P149" s="14" t="n">
+      <c r="P149" s="15" t="n">
         <v>46282.91478009259</v>
       </c>
     </row>
@@ -14063,7 +14148,7 @@
       <c r="O150" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P150" s="14" t="n">
+      <c r="P150" s="15" t="n">
         <v>46282.94171296297</v>
       </c>
     </row>
@@ -14133,7 +14218,7 @@
       <c r="O151" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P151" s="14" t="n">
+      <c r="P151" s="15" t="n">
         <v>46283.06856481481</v>
       </c>
     </row>
@@ -14203,7 +14288,7 @@
       <c r="O152" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P152" s="14" t="n">
+      <c r="P152" s="15" t="n">
         <v>46283.0745949074</v>
       </c>
     </row>
@@ -14273,7 +14358,7 @@
       <c r="O153" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P153" s="14" t="n">
+      <c r="P153" s="15" t="n">
         <v>46283.19665509259</v>
       </c>
     </row>
@@ -14343,7 +14428,7 @@
       <c r="O154" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P154" s="14" t="n">
+      <c r="P154" s="15" t="n">
         <v>46283.22854166666</v>
       </c>
     </row>
@@ -14413,7 +14498,7 @@
       <c r="O155" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P155" s="14" t="n">
+      <c r="P155" s="15" t="n">
         <v>46283.33405092593</v>
       </c>
     </row>
@@ -14483,7 +14568,7 @@
       <c r="O156" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P156" s="14" t="n">
+      <c r="P156" s="15" t="n">
         <v>46283.35032407408</v>
       </c>
     </row>
@@ -14553,7 +14638,7 @@
       <c r="O157" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P157" s="14" t="n">
+      <c r="P157" s="15" t="n">
         <v>46283.48784722222</v>
       </c>
     </row>
@@ -14623,7 +14708,7 @@
       <c r="O158" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P158" s="14" t="n">
+      <c r="P158" s="15" t="n">
         <v>46283.508125</v>
       </c>
     </row>
@@ -14693,7 +14778,7 @@
       <c r="O159" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P159" s="14" t="n">
+      <c r="P159" s="15" t="n">
         <v>46283.64868055555</v>
       </c>
     </row>
@@ -14763,7 +14848,7 @@
       <c r="O160" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P160" s="14" t="n">
+      <c r="P160" s="15" t="n">
         <v>46283.6619212963</v>
       </c>
     </row>
@@ -14833,7 +14918,7 @@
       <c r="O161" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P161" s="14" t="n">
+      <c r="P161" s="15" t="n">
         <v>46283.76673611111</v>
       </c>
     </row>
@@ -14903,7 +14988,7 @@
       <c r="O162" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P162" s="14" t="n">
+      <c r="P162" s="15" t="n">
         <v>46283.8025</v>
       </c>
     </row>
@@ -14973,7 +15058,7 @@
       <c r="O163" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P163" s="14" t="n">
+      <c r="P163" s="15" t="n">
         <v>46283.92071759259</v>
       </c>
     </row>
@@ -15043,7 +15128,7 @@
       <c r="O164" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P164" s="14" t="n">
+      <c r="P164" s="15" t="n">
         <v>46283.94190972222</v>
       </c>
     </row>
@@ -15113,7 +15198,7 @@
       <c r="O165" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P165" s="14" t="n">
+      <c r="P165" s="15" t="n">
         <v>46284.05696759259</v>
       </c>
     </row>
@@ -15183,7 +15268,7 @@
       <c r="O166" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P166" s="14" t="n">
+      <c r="P166" s="15" t="n">
         <v>46284.09695601852</v>
       </c>
     </row>
@@ -15253,7 +15338,7 @@
       <c r="O167" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P167" s="14" t="n">
+      <c r="P167" s="15" t="n">
         <v>46284.21068287037</v>
       </c>
     </row>
@@ -15323,7 +15408,7 @@
       <c r="O168" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P168" s="14" t="n">
+      <c r="P168" s="15" t="n">
         <v>46284.24060185185</v>
       </c>
     </row>
@@ -15393,7 +15478,7 @@
       <c r="O169" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P169" s="14" t="n">
+      <c r="P169" s="15" t="n">
         <v>46284.33123842593</v>
       </c>
     </row>
@@ -15463,7 +15548,7 @@
       <c r="O170" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P170" s="14" t="n">
+      <c r="P170" s="15" t="n">
         <v>46284.3950462963</v>
       </c>
     </row>
@@ -15533,7 +15618,7 @@
       <c r="O171" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P171" s="14" t="n">
+      <c r="P171" s="15" t="n">
         <v>46284.48659722223</v>
       </c>
     </row>
@@ -15603,7 +15688,7 @@
       <c r="O172" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P172" s="14" t="n">
+      <c r="P172" s="15" t="n">
         <v>46284.51091435185</v>
       </c>
     </row>
@@ -15673,7 +15758,7 @@
       <c r="O173" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P173" s="14" t="n">
+      <c r="P173" s="15" t="n">
         <v>46284.61217592593</v>
       </c>
     </row>
@@ -15743,7 +15828,7 @@
       <c r="O174" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P174" s="14" t="n">
+      <c r="P174" s="15" t="n">
         <v>46284.63247685185</v>
       </c>
     </row>
@@ -15813,7 +15898,7 @@
       <c r="O175" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P175" s="14" t="n">
+      <c r="P175" s="15" t="n">
         <v>46284.66641203704</v>
       </c>
     </row>
@@ -15883,7 +15968,7 @@
       <c r="O176" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P176" s="14" t="n">
+      <c r="P176" s="15" t="n">
         <v>46284.76607638889</v>
       </c>
     </row>
@@ -15953,7 +16038,7 @@
       <c r="O177" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P177" s="14" t="n">
+      <c r="P177" s="15" t="n">
         <v>46284.78469907407</v>
       </c>
     </row>
@@ -16023,7 +16108,7 @@
       <c r="O178" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P178" s="14" t="n">
+      <c r="P178" s="15" t="n">
         <v>46284.895</v>
       </c>
     </row>
@@ -16093,7 +16178,7 @@
       <c r="O179" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P179" s="14" t="n">
+      <c r="P179" s="15" t="n">
         <v>46284.93909722222</v>
       </c>
     </row>
@@ -16163,7 +16248,7 @@
       <c r="O180" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P180" s="14" t="n">
+      <c r="P180" s="15" t="n">
         <v>46284.99038194444</v>
       </c>
     </row>
@@ -16233,7 +16318,7 @@
       <c r="O181" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P181" s="14" t="n">
+      <c r="P181" s="15" t="n">
         <v>46285.02277777778</v>
       </c>
     </row>
@@ -16303,7 +16388,7 @@
       <c r="O182" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P182" s="14" t="n">
+      <c r="P182" s="15" t="n">
         <v>46285.04913194444</v>
       </c>
     </row>
@@ -16373,7 +16458,7 @@
       <c r="O183" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P183" s="14" t="n">
+      <c r="P183" s="15" t="n">
         <v>46285.16568287037</v>
       </c>
     </row>
@@ -16443,7 +16528,7 @@
       <c r="O184" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P184" s="14" t="n">
+      <c r="P184" s="15" t="n">
         <v>46285.31915509259</v>
       </c>
     </row>
@@ -16513,7 +16598,7 @@
       <c r="O185" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P185" s="14" t="n">
+      <c r="P185" s="15" t="n">
         <v>46285.38929398148</v>
       </c>
     </row>
@@ -16583,7 +16668,7 @@
       <c r="O186" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P186" s="14" t="n">
+      <c r="P186" s="15" t="n">
         <v>46285.45016203704</v>
       </c>
     </row>
@@ -16653,7 +16738,7 @@
       <c r="O187" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P187" s="14" t="n">
+      <c r="P187" s="15" t="n">
         <v>46285.60445601852</v>
       </c>
     </row>
@@ -16723,7 +16808,7 @@
       <c r="O188" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P188" s="14" t="n">
+      <c r="P188" s="15" t="n">
         <v>46285.70131944444</v>
       </c>
     </row>
@@ -16793,7 +16878,7 @@
       <c r="O189" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P189" s="14" t="n">
+      <c r="P189" s="15" t="n">
         <v>46285.73811342593</v>
       </c>
     </row>
@@ -16863,7 +16948,7 @@
       <c r="O190" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P190" s="14" t="n">
+      <c r="P190" s="15" t="n">
         <v>46285.89204861111</v>
       </c>
     </row>
@@ -16933,7 +17018,7 @@
       <c r="O191" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P191" s="14" t="n">
+      <c r="P191" s="15" t="n">
         <v>46286.04180555556</v>
       </c>
     </row>
@@ -17003,7 +17088,7 @@
       <c r="O192" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P192" s="14" t="n">
+      <c r="P192" s="15" t="n">
         <v>46286.10230324074</v>
       </c>
     </row>
@@ -17073,7 +17158,7 @@
       <c r="O193" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P193" s="14" t="n">
+      <c r="P193" s="15" t="n">
         <v>46286.19703703704</v>
       </c>
     </row>
@@ -17143,7 +17228,7 @@
       <c r="O194" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P194" s="14" t="n">
+      <c r="P194" s="15" t="n">
         <v>46286.34505787037</v>
       </c>
     </row>
@@ -17213,7 +17298,7 @@
       <c r="O195" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P195" s="14" t="n">
+      <c r="P195" s="15" t="n">
         <v>46286.38792824074</v>
       </c>
     </row>
@@ -17283,7 +17368,7 @@
       <c r="O196" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P196" s="14" t="n">
+      <c r="P196" s="15" t="n">
         <v>46286.49905092592</v>
       </c>
     </row>
@@ -17353,7 +17438,7 @@
       <c r="O197" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P197" s="14" t="n">
+      <c r="P197" s="15" t="n">
         <v>46286.64550925926</v>
       </c>
     </row>
@@ -17423,7 +17508,7 @@
       <c r="O198" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P198" s="14" t="n">
+      <c r="P198" s="15" t="n">
         <v>46286.79150462963</v>
       </c>
     </row>
@@ -17493,7 +17578,7 @@
       <c r="O199" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P199" s="14" t="n">
+      <c r="P199" s="15" t="n">
         <v>46286.79928240741</v>
       </c>
     </row>
@@ -17563,7 +17648,7 @@
       <c r="O200" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P200" s="14" t="n">
+      <c r="P200" s="15" t="n">
         <v>46286.94260416667</v>
       </c>
     </row>
@@ -17633,7 +17718,7 @@
       <c r="O201" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P201" s="14" t="n">
+      <c r="P201" s="15" t="n">
         <v>46286.99332175926</v>
       </c>
     </row>
@@ -17703,7 +17788,7 @@
       <c r="O202" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P202" s="14" t="n">
+      <c r="P202" s="15" t="n">
         <v>46287.09914351852</v>
       </c>
     </row>
@@ -17773,7 +17858,7 @@
       <c r="O203" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P203" s="14" t="n">
+      <c r="P203" s="15" t="n">
         <v>46287.22350694444</v>
       </c>
     </row>
@@ -17843,7 +17928,7 @@
       <c r="O204" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P204" s="14" t="n">
+      <c r="P204" s="15" t="n">
         <v>46287.37719907407</v>
       </c>
     </row>
@@ -17913,7 +17998,7 @@
       <c r="O205" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P205" s="14" t="n">
+      <c r="P205" s="15" t="n">
         <v>46287.39092592592</v>
       </c>
     </row>
@@ -17983,7 +18068,7 @@
       <c r="O206" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P206" s="14" t="n">
+      <c r="P206" s="15" t="n">
         <v>46287.51923611111</v>
       </c>
     </row>
@@ -18053,7 +18138,7 @@
       <c r="O207" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P207" s="14" t="n">
+      <c r="P207" s="15" t="n">
         <v>46287.62731481482</v>
       </c>
     </row>
@@ -18123,7 +18208,7 @@
       <c r="O208" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P208" s="14" t="n">
+      <c r="P208" s="15" t="n">
         <v>46287.67415509259</v>
       </c>
     </row>
@@ -18193,7 +18278,7 @@
       <c r="O209" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P209" s="14" t="n">
+      <c r="P209" s="15" t="n">
         <v>46287.793125</v>
       </c>
     </row>
@@ -18263,7 +18348,7 @@
       <c r="O210" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P210" s="14" t="n">
+      <c r="P210" s="15" t="n">
         <v>46287.94795138889</v>
       </c>
     </row>
@@ -18333,7 +18418,7 @@
       <c r="O211" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P211" s="14" t="n">
+      <c r="P211" s="15" t="n">
         <v>46288.02731481481</v>
       </c>
     </row>
@@ -18403,7 +18488,7 @@
       <c r="O212" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P212" s="14" t="n">
+      <c r="P212" s="15" t="n">
         <v>46288.04887731482</v>
       </c>
     </row>
@@ -18473,7 +18558,7 @@
       <c r="O213" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P213" s="14" t="n">
+      <c r="P213" s="15" t="n">
         <v>46288.21672453704</v>
       </c>
     </row>
@@ -18543,7 +18628,7 @@
       <c r="O214" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P214" s="14" t="n">
+      <c r="P214" s="15" t="n">
         <v>46288.343125</v>
       </c>
     </row>
@@ -18613,7 +18698,7 @@
       <c r="O215" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P215" s="14" t="n">
+      <c r="P215" s="15" t="n">
         <v>46288.49837962963</v>
       </c>
     </row>
@@ -18683,7 +18768,7 @@
       <c r="O216" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P216" s="14" t="n">
+      <c r="P216" s="15" t="n">
         <v>46288.50125</v>
       </c>
     </row>
@@ -18753,7 +18838,7 @@
       <c r="O217" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P217" s="14" t="n">
+      <c r="P217" s="15" t="n">
         <v>46288.64248842592</v>
       </c>
     </row>
@@ -18823,7 +18908,7 @@
       <c r="O218" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P218" s="14" t="n">
+      <c r="P218" s="15" t="n">
         <v>46288.91950231481</v>
       </c>
     </row>
@@ -18893,70 +18978,272 @@
       <c r="O219" s="7" t="n">
         <v>0.0625</v>
       </c>
-      <c r="P219" s="14" t="n">
+      <c r="P219" s="15" t="n">
         <v>46289.20876157407</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="7" t="inlineStr">
         <is>
           <t>Mamba2_AC_Freeway_seed2710_O</t>
         </is>
       </c>
-      <c r="B220" s="15" t="inlineStr">
+      <c r="B220" s="7" t="inlineStr">
         <is>
           <t>m3lhpghb</t>
         </is>
       </c>
-      <c r="C220" s="15" t="inlineStr">
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I220" s="7" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="K220" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L220" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M220" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N220" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O220" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P220" s="15" t="n">
+        <v>46289.43347222222</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Frostbite_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>9t3x82mf</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>Frostbite</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I221" s="7" t="inlineStr">
+        <is>
+          <t>1291.00</t>
+        </is>
+      </c>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="K221" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L221" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M221" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N221" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O221" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P221" s="15" t="n">
+        <v>46289.71842592592</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2030_Both</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="inlineStr">
+        <is>
+          <t>khvdesdy</t>
+        </is>
+      </c>
+      <c r="C222" s="16" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E220" s="15" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F220" s="15" t="inlineStr">
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E222" s="16" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
         <is>
           <t>Freeway</t>
         </is>
       </c>
-      <c r="G220" s="15" t="n">
-        <v>2710</v>
-      </c>
-      <c r="H220" s="15" t="inlineStr">
+      <c r="G222" s="16" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H222" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I222" s="16" t="inlineStr"/>
+      <c r="J222" s="16" t="inlineStr"/>
+      <c r="K222" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L222" s="16" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M222" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N222" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="O222" s="16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P222" s="17" t="n">
+        <v>46290.07979166666</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2030_Both</t>
+        </is>
+      </c>
+      <c r="B223" s="16" t="inlineStr">
+        <is>
+          <t>khvdesdy</t>
+        </is>
+      </c>
+      <c r="C223" s="16" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D223" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E223" s="16" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G223" s="16" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H223" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I220" s="15" t="inlineStr"/>
-      <c r="J220" s="15" t="inlineStr"/>
-      <c r="K220" s="15" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L220" s="15" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M220" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="N220" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O220" s="15" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P220" s="16" t="n">
-        <v>46289.43347222222</v>
+      <c r="I223" s="16" t="inlineStr"/>
+      <c r="J223" s="16" t="inlineStr"/>
+      <c r="K223" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L223" s="16" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M223" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N223" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="O223" s="16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P223" s="17" t="n">
+        <v>46290.07979166666</v>
       </c>
     </row>
   </sheetData>

--- a/results/drama_results.xlsx
+++ b/results/drama_results.xlsx
@@ -132,6 +132,9 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -139,9 +142,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,115 +235,115 @@
     <author>Drama</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>첨부된 논문 표의 DramaXS 게임별 점수입니다. X행에 표시합니다.</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>X: Retrieval 미사용, O: Retrieval 적용 (target: 16).
 양쪽에 유효한 점수가 있는 공통 시드만 사용하며 RUNNING/누락 점수는 제외합니다. update_tex.py의 EXCLUDED_SEEDS에 지정된 시드도 제외합니다. Drama/results/update_tex.py와 동일하게 표시된 시드 점수를 집계합니다.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>X행: Retrieval 미사용의 공통 시드 평균 − DramaXS 논문 점수.
 O행: |target: 16의 공통 시드 평균 − Retrieval 미사용의 공통 시드 평균|.</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>X행: (Retrieval 미사용 평균 − DramaXS 논문 점수) / (Human − Random).
 O행: (target: 16 평균 − Retrieval 미사용 평균) / (Human − Random).
 모든 평균은 EXCLUDED_SEEDS를 제외한 공통 시드 기준입니다. HNS는 Random=0, Human=1 기준이며 차이의 부호를 유지합니다. 백분율이 아닙니다. Random/Human은 STORM 엑셀과 동일한 기준값을 사용합니다.</t>
       </text>
     </comment>
-    <comment ref="O2" authorId="0" shapeId="0">
+    <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>Random: 227.8
 Human: 7127.7</t>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <t>Random: 5.8
 Human: 1719.5</t>
       </text>
     </comment>
-    <comment ref="O6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <t>Random: 222.4
 Human: 742.0</t>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0">
+    <comment ref="P8" authorId="0" shapeId="0">
       <text>
         <t>Random: 210.0
 Human: 8503.3</t>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0">
+    <comment ref="P10" authorId="0" shapeId="0">
       <text>
         <t>Random: 14.2
 Human: 753.1</t>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0">
+    <comment ref="I12" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
+    <comment ref="P12" authorId="0" shapeId="0">
       <text>
         <t>Random: 2360.0
 Human: 37187.5</t>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: BattleZone, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="I14" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0">
+    <comment ref="M14" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O14" authorId="0" shapeId="0">
+    <comment ref="P14" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.1
 Human: 12.1</t>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 2710
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0">
+    <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>EXCLUDED_SEEDS: Boxing, seed 6010
 Drama/results/update_tex.py의 EXCLUDED_SEEDS에 지정되어 공통 시드 평균, Δ Score, Δ HNS 및 LaTeX 결과 집계에서 제외되는 시드입니다.
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O16" authorId="0" shapeId="0">
+    <comment ref="P16" authorId="0" shapeId="0">
       <text>
         <t>Random: 1.7
 Human: 30.5</t>
@@ -356,7 +356,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O18" authorId="0" shapeId="0">
+    <comment ref="P18" authorId="0" shapeId="0">
       <text>
         <t>Random: 811.0
 Human: 7387.8</t>
@@ -369,19 +369,19 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <t>Random: 10780.5
 Human: 35829.4</t>
       </text>
     </comment>
-    <comment ref="O22" authorId="0" shapeId="0">
+    <comment ref="P22" authorId="0" shapeId="0">
       <text>
         <t>Random: 152.1
 Human: 1971.0</t>
       </text>
     </comment>
-    <comment ref="O24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <t>Random: 0.0
 Human: 29.6</t>
@@ -394,7 +394,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <t>Random: 65.2
 Human: 4334.7</t>
@@ -414,7 +414,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>Random: 257.6
 Human: 2412.5</t>
@@ -434,7 +434,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O30" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
       <text>
         <t>Random: 1027.0
 Human: 30826.4</t>
@@ -454,7 +454,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0">
+    <comment ref="P32" authorId="0" shapeId="0">
       <text>
         <t>Random: 29.0
 Human: 302.8</t>
@@ -467,7 +467,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
+    <comment ref="P34" authorId="0" shapeId="0">
       <text>
         <t>Random: 52.0
 Human: 3035.0</t>
@@ -480,7 +480,7 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O36" authorId="0" shapeId="0">
+    <comment ref="P36" authorId="0" shapeId="0">
       <text>
         <t>Random: 1598.0
 Human: 2665.5</t>
@@ -493,49 +493,49 @@
 취소선은 제외된 시드, 노란색 배경은 실행 중인 run을 뜻합니다.</t>
       </text>
     </comment>
-    <comment ref="O38" authorId="0" shapeId="0">
+    <comment ref="P38" authorId="0" shapeId="0">
       <text>
         <t>Random: 258.5
 Human: 22736.3</t>
       </text>
     </comment>
-    <comment ref="O40" authorId="0" shapeId="0">
+    <comment ref="P40" authorId="0" shapeId="0">
       <text>
         <t>Random: 307.3
 Human: 6951.6</t>
       </text>
     </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
+    <comment ref="P42" authorId="0" shapeId="0">
       <text>
         <t>Random: -20.7
 Human: 14.6</t>
       </text>
     </comment>
-    <comment ref="O44" authorId="0" shapeId="0">
+    <comment ref="P44" authorId="0" shapeId="0">
       <text>
         <t>Random: 24.9
 Human: 69571.3</t>
       </text>
     </comment>
-    <comment ref="O46" authorId="0" shapeId="0">
+    <comment ref="P46" authorId="0" shapeId="0">
       <text>
         <t>Random: 163.9
 Human: 13455.0</t>
       </text>
     </comment>
-    <comment ref="O48" authorId="0" shapeId="0">
+    <comment ref="P48" authorId="0" shapeId="0">
       <text>
         <t>Random: 11.5
 Human: 7845.0</t>
       </text>
     </comment>
-    <comment ref="O50" authorId="0" shapeId="0">
+    <comment ref="P50" authorId="0" shapeId="0">
       <text>
         <t>Random: 68.4
 Human: 42054.7</t>
       </text>
     </comment>
-    <comment ref="O52" authorId="0" shapeId="0">
+    <comment ref="P52" authorId="0" shapeId="0">
       <text>
         <t>Random: 533.4
 Human: 11693.2</t>
@@ -834,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -850,11 +850,12 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="46" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -884,44 +885,47 @@
         <v>2030</v>
       </c>
       <c r="H1" s="1" t="n">
+        <v>2040</v>
+      </c>
+      <c r="I1" s="1" t="n">
         <v>2710</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>3290</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>3710</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>6010</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>6020</v>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>DramaXS (논문 점수)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Mean (공통 시드)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Δ Score (행별 비교)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Δ HNS (행별 비교)</t>
         </is>
@@ -948,34 +952,35 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>608.00</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>1376.00</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>1316.00</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3" t="n">
         <v>820</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>1051.5</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="R2" s="5" t="n">
         <v>231.5</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="6" t="n">
         <v>0.03355121088711431</v>
       </c>
     </row>
@@ -1000,32 +1005,33 @@
       <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr"/>
       <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>705.00</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>1169.00</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>732.00</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="9" t="n">
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="9" t="n">
         <v>972.25</v>
       </c>
-      <c r="Q3" s="9" t="n">
+      <c r="R3" s="9" t="n">
         <v>79.25</v>
       </c>
-      <c r="R3" s="10" t="n">
+      <c r="S3" s="10" t="n">
         <v>-0.01148567370541602</v>
       </c>
     </row>
@@ -1050,34 +1056,35 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>92.60</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>96.70</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>141.70</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>140.325</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4" s="5" t="n">
         <v>9.324999999999989</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>0.005441442492851717</v>
       </c>
     </row>
@@ -1102,32 +1109,33 @@
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>139.80</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="9" t="n">
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="9" t="n">
         <v>130.175</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="R5" s="9" t="n">
         <v>10.14999999999998</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="S5" s="10" t="n">
         <v>-0.005922856976133498</v>
       </c>
     </row>
@@ -1154,32 +1162,33 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>323.40</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>336.00</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>521.80</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
         <v>539</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>383.5</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="R6" s="5" t="n">
         <v>-155.5</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="6" t="n">
         <v>-0.2992686682063125</v>
       </c>
     </row>
@@ -1206,30 +1215,31 @@
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>310.80</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>630.00</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>428.40</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="9" t="n">
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="9" t="n">
         <v>449.925</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="R7" s="9" t="n">
         <v>66.42499999999995</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="S7" s="10" t="n">
         <v>0.1278387220939183</v>
       </c>
     </row>
@@ -1260,28 +1270,29 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2420.00</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1220.00</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="3" t="n">
         <v>1632</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="R8" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="6" t="n">
         <v>0.005787804613362595</v>
       </c>
     </row>
@@ -1312,26 +1323,27 @@
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>1215.00</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="9" t="n">
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="9" t="n">
         <v>1397.5</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="R9" s="9" t="n">
         <v>282.5</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="S9" s="10" t="n">
         <v>-0.03406364173489444</v>
       </c>
     </row>
@@ -1357,33 +1369,34 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>870.00</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>281.00</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>464.00</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>458.75</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="R10" s="5" t="n">
         <v>321.75</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>0.4354445797807552</v>
       </c>
     </row>
@@ -1404,36 +1417,41 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>339.00</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>324.00</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="9" t="n">
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="8" t="inlineStr"/>
+      <c r="Q11" s="9" t="n">
         <v>278.75</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="R11" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="S11" s="10" t="n">
         <v>-0.243605359317905</v>
       </c>
     </row>
@@ -1461,35 +1479,36 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>8100.00</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13500.00</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4000.00</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
         <v>10860</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>10775</v>
       </c>
-      <c r="Q12" s="5" t="n">
+      <c r="R12" s="5" t="n">
         <v>-85</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="6" t="n">
         <v>-0.002440600100495298</v>
       </c>
     </row>
@@ -1517,33 +1536,34 @@
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>4300.00</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>6200.00</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>4900.00</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="9" t="n">
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="8" t="inlineStr"/>
+      <c r="Q13" s="9" t="n">
         <v>8600</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="R13" s="9" t="n">
         <v>2175</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="S13" s="10" t="n">
         <v>-0.06245064963032087</v>
       </c>
     </row>
@@ -1571,39 +1591,40 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>25.80</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32.20</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>93.30</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>74.00</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>63.2</v>
       </c>
-      <c r="Q14" s="5" t="n">
+      <c r="R14" s="5" t="n">
         <v>-14.8</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="6" t="n">
         <v>-1.233333333333333</v>
       </c>
     </row>
@@ -1631,37 +1652,38 @@
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>36.00</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>98.60</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="8" t="inlineStr"/>
-      <c r="P15" s="9" t="n">
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="8" t="inlineStr"/>
+      <c r="Q15" s="9" t="n">
         <v>75.34999999999999</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="R15" s="9" t="n">
         <v>12.14999999999999</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="S15" s="10" t="n">
         <v>1.012499999999999</v>
       </c>
     </row>
@@ -1687,33 +1709,34 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9.70</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="3" t="n">
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>14.725</v>
       </c>
-      <c r="Q16" s="5" t="n">
+      <c r="R16" s="5" t="n">
         <v>7.725</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="6" t="n">
         <v>0.2682291666666666</v>
       </c>
     </row>
@@ -1739,31 +1762,32 @@
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>10.60</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>20.70</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>17.20</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr"/>
-      <c r="P17" s="9" t="n">
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="8" t="inlineStr"/>
+      <c r="Q17" s="9" t="n">
         <v>16.55</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="R17" s="9" t="n">
         <v>1.825000000000001</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="S17" s="10" t="n">
         <v>0.06336805555555559</v>
       </c>
     </row>
@@ -1783,7 +1807,7 @@
           <t>1450.00</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>2020.00</t>
         </is>
@@ -1795,31 +1819,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1450.00</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1250.00</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="3" t="n">
         <v>1642</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>1382.5</v>
       </c>
-      <c r="Q18" s="5" t="n">
+      <c r="R18" s="5" t="n">
         <v>-259.5</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="6" t="n">
         <v>-0.03945687872521591</v>
       </c>
     </row>
@@ -1839,7 +1864,7 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>750.00</t>
         </is>
@@ -1851,29 +1876,30 @@
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>2260.00</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>1430.00</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="9" t="n">
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="9" t="n">
         <v>1550</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="R19" s="9" t="n">
         <v>167.5</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="S19" s="10" t="n">
         <v>0.02546831285731663</v>
       </c>
     </row>
@@ -1899,33 +1925,34 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>73510.00</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>66980.00</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>82640.00</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
         <v>83931</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>76802.5</v>
       </c>
-      <c r="Q20" s="5" t="n">
+      <c r="R20" s="5" t="n">
         <v>-7128.5</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>-0.2845833549577027</v>
       </c>
     </row>
@@ -1951,31 +1978,32 @@
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>72700.00</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>77110.00</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>71030.00</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="9" t="n">
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr"/>
+      <c r="Q21" s="9" t="n">
         <v>74437.5</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="R21" s="9" t="n">
         <v>2365</v>
       </c>
-      <c r="R21" s="10" t="n">
+      <c r="S21" s="10" t="n">
         <v>-0.09441532362698561</v>
       </c>
     </row>
@@ -2006,28 +2034,29 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>153.50</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>255.00</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
         <v>187.25</v>
       </c>
-      <c r="Q22" s="5" t="n">
+      <c r="R22" s="5" t="n">
         <v>-13.75</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="6" t="n">
         <v>-0.007559513991973171</v>
       </c>
     </row>
@@ -2058,26 +2087,27 @@
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>211.50</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>124.50</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="8" t="inlineStr"/>
-      <c r="P23" s="9" t="n">
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="8" t="inlineStr"/>
+      <c r="Q23" s="9" t="n">
         <v>151</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="R23" s="9" t="n">
         <v>36.25</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="S23" s="10" t="n">
         <v>-0.01992962779702018</v>
       </c>
     </row>
@@ -2096,24 +2126,39 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>RUNNING</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>31.30</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
+      <c r="Q24" s="4" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0.6500000000000004</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0.02195945945945947</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2130,26 +2175,37 @@
       <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>RUNNING</t>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
           <t>32.20</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
-      <c r="P25" s="9" t="inlineStr"/>
-      <c r="Q25" s="9" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>0.4500000000000011</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>0.01520270270270274</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2162,7 +2218,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>260.00</t>
         </is>
@@ -2176,34 +2232,35 @@
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>1952.00</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>268.00</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>244.00</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>1311.5</v>
       </c>
-      <c r="Q26" s="5" t="n">
+      <c r="R26" s="5" t="n">
         <v>526.5</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="6" t="n">
         <v>0.123316547605106</v>
       </c>
     </row>
@@ -2218,7 +2275,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
@@ -2236,32 +2293,33 @@
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>2224.00</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>267.00</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>246.00</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="8" t="inlineStr"/>
-      <c r="P27" s="9" t="n">
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="9" t="n">
         <v>1319.25</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="R27" s="9" t="n">
         <v>7.75</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="S27" s="10" t="n">
         <v>0.001815200843190069</v>
       </c>
     </row>
@@ -2278,7 +2336,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>2198.00</t>
         </is>
@@ -2289,35 +2347,36 @@
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>2896.00</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>2150.00</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>1676.00</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="3" t="n">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="3" t="n">
         <v>2757</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>1934.5</v>
       </c>
-      <c r="Q28" s="5" t="n">
+      <c r="R28" s="5" t="n">
         <v>-822.5</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="6" t="n">
         <v>-0.3816882453942178</v>
       </c>
     </row>
@@ -2334,7 +2393,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>1160.00</t>
         </is>
@@ -2345,33 +2404,34 @@
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>2506.00</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>3132.00</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>2030.00</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr"/>
-      <c r="O29" s="8" t="inlineStr"/>
-      <c r="P29" s="9" t="n">
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr"/>
+      <c r="Q29" s="9" t="n">
         <v>2187.5</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="R29" s="9" t="n">
         <v>253</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="S29" s="10" t="n">
         <v>0.1174068402246044</v>
       </c>
     </row>
@@ -2393,41 +2453,42 @@
           <t>7552.00</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>7510.00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>3622.50</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>13517.00</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>7107.50</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="3" t="n">
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="3" t="n">
         <v>7946</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>7949.75</v>
       </c>
-      <c r="Q30" s="5" t="n">
+      <c r="R30" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="6" t="n">
         <v>0.0001258414598951657</v>
       </c>
     </row>
@@ -2449,39 +2510,40 @@
           <t>7564.00</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>3155.00</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>7488.00</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>13340.00</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>3556.50</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="8" t="inlineStr"/>
-      <c r="P31" s="9" t="n">
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="9" t="n">
         <v>7987.125</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="R31" s="9" t="n">
         <v>37.375</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="S31" s="10" t="n">
         <v>0.001254219883621818</v>
       </c>
     </row>
@@ -2506,38 +2568,39 @@
           <t>355.00</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>1325.00</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>520.00</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>355.00</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>428.75</v>
       </c>
-      <c r="Q32" s="5" t="n">
+      <c r="R32" s="5" t="n">
         <v>56.75</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="6" t="n">
         <v>0.2072680788897005</v>
       </c>
     </row>
@@ -2562,36 +2625,37 @@
           <t>475.00</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>600.00</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>615.00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>605.00</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" s="8" t="inlineStr"/>
-      <c r="P33" s="9" t="n">
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="9" t="n">
         <v>535</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="R33" s="9" t="n">
         <v>106.25</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="S33" s="10" t="n">
         <v>0.3880569758948137</v>
       </c>
     </row>
@@ -2625,25 +2689,26 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>1420.00</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>1350</v>
       </c>
-      <c r="Q34" s="5" t="n">
+      <c r="R34" s="5" t="n">
         <v>-34</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="6" t="n">
         <v>-0.01139792155548106</v>
       </c>
     </row>
@@ -2677,23 +2742,24 @@
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>1140.00</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
-      <c r="P35" s="9" t="n">
+      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="9" t="n">
         <v>1335</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="R35" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="S35" s="10" t="n">
         <v>-0.005028494803888703</v>
       </c>
     </row>
@@ -2708,7 +2774,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>8075.00</t>
         </is>
@@ -2727,29 +2793,30 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>10649.00</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>9836.00</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="3" t="n">
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="3" t="n">
         <v>9693</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>9076</v>
       </c>
-      <c r="Q36" s="5" t="n">
+      <c r="R36" s="5" t="n">
         <v>-617</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="6" t="n">
         <v>-0.5779859484777518</v>
       </c>
     </row>
@@ -2764,7 +2831,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>7926.00</t>
         </is>
@@ -2783,27 +2850,28 @@
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>10233.00</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>8737.00</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" s="8" t="inlineStr"/>
-      <c r="P37" s="9" t="n">
+      <c r="O37" s="7" t="inlineStr"/>
+      <c r="P37" s="8" t="inlineStr"/>
+      <c r="Q37" s="9" t="n">
         <v>9569</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="R37" s="9" t="n">
         <v>493</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="S37" s="10" t="n">
         <v>0.4618266978922717</v>
       </c>
     </row>
@@ -2837,25 +2905,26 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>19020.00</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="3" t="n">
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="3" t="n">
         <v>23920</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>16480</v>
       </c>
-      <c r="Q38" s="5" t="n">
+      <c r="R38" s="5" t="n">
         <v>-7440</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="6" t="n">
         <v>-0.3309932466700478</v>
       </c>
     </row>
@@ -2889,23 +2958,24 @@
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>23080.00</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" s="8" t="inlineStr"/>
-      <c r="P39" s="9" t="n">
+      <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="9" t="n">
         <v>16137.5</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="R39" s="9" t="n">
         <v>342.5</v>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="S39" s="10" t="n">
         <v>-0.01523725631511981</v>
       </c>
     </row>
@@ -2939,25 +3009,26 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>1548.00</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="3" t="n">
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="3" t="n">
         <v>2270</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>2460.25</v>
       </c>
-      <c r="Q40" s="5" t="n">
+      <c r="R40" s="5" t="n">
         <v>190.25</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="6" t="n">
         <v>0.02863356561263037</v>
       </c>
     </row>
@@ -2991,23 +3062,24 @@
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>1847.00</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" s="8" t="inlineStr"/>
-      <c r="P41" s="9" t="n">
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="8" t="inlineStr"/>
+      <c r="Q41" s="9" t="n">
         <v>2525.25</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="R41" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="S41" s="10" t="n">
         <v>0.009782821365681862</v>
       </c>
     </row>
@@ -3033,33 +3105,34 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>21.00</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>11.80</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>-17.80</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="3" t="n">
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>8.75</v>
       </c>
-      <c r="Q42" s="5" t="n">
+      <c r="R42" s="5" t="n">
         <v>-6.25</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="6" t="n">
         <v>-0.1770538243626062</v>
       </c>
     </row>
@@ -3085,31 +3158,32 @@
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>20.80</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>13.90</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" s="8" t="inlineStr"/>
-      <c r="P43" s="9" t="n">
+      <c r="O43" s="7" t="inlineStr"/>
+      <c r="P43" s="8" t="inlineStr"/>
+      <c r="Q43" s="9" t="n">
         <v>14.75</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="R43" s="9" t="n">
         <v>5.999999999999998</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="S43" s="10" t="n">
         <v>0.169971671388102</v>
       </c>
     </row>
@@ -3143,25 +3217,26 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="3" t="n">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="Q44" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S44" s="6" t="n">
         <v>0.0001437888948960694</v>
       </c>
     </row>
@@ -3195,23 +3270,24 @@
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>-219.40</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" s="8" t="inlineStr"/>
-      <c r="P45" s="9" t="n">
+      <c r="O45" s="7" t="inlineStr"/>
+      <c r="P45" s="8" t="inlineStr"/>
+      <c r="Q45" s="9" t="n">
         <v>-4.850000000000001</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="R45" s="9" t="n">
         <v>104.85</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="S45" s="10" t="n">
         <v>-0.001507626562985287</v>
       </c>
     </row>
@@ -3245,25 +3321,26 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>787.50</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="3" t="n">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="3" t="n">
         <v>796</v>
       </c>
-      <c r="P46" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>1446.25</v>
       </c>
-      <c r="Q46" s="5" t="n">
+      <c r="R46" s="5" t="n">
         <v>650.25</v>
       </c>
-      <c r="R46" s="6" t="n">
+      <c r="S46" s="6" t="n">
         <v>0.04892371587001828</v>
       </c>
     </row>
@@ -3297,23 +3374,24 @@
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>792.50</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
-      <c r="O47" s="8" t="inlineStr"/>
-      <c r="P47" s="9" t="n">
+      <c r="O47" s="7" t="inlineStr"/>
+      <c r="P47" s="8" t="inlineStr"/>
+      <c r="Q47" s="9" t="n">
         <v>1496.25</v>
       </c>
-      <c r="Q47" s="9" t="n">
+      <c r="R47" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="S47" s="10" t="n">
         <v>0.003761915868513517</v>
       </c>
     </row>
@@ -3339,33 +3417,34 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>14670.00</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>7030.00</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>7860.00</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="3" t="n">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="3" t="n">
         <v>14020</v>
       </c>
-      <c r="P48" s="4" t="n">
+      <c r="Q48" s="4" t="n">
         <v>11812.5</v>
       </c>
-      <c r="Q48" s="5" t="n">
+      <c r="R48" s="5" t="n">
         <v>-2207.5</v>
       </c>
-      <c r="R48" s="6" t="n">
+      <c r="S48" s="6" t="n">
         <v>-0.2818025148401098</v>
       </c>
     </row>
@@ -3391,31 +3470,32 @@
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>15330.00</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>8520.00</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>8500.00</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
-      <c r="O49" s="8" t="inlineStr"/>
-      <c r="P49" s="9" t="n">
+      <c r="O49" s="7" t="inlineStr"/>
+      <c r="P49" s="8" t="inlineStr"/>
+      <c r="Q49" s="9" t="n">
         <v>12537.5</v>
       </c>
-      <c r="Q49" s="9" t="n">
+      <c r="R49" s="9" t="n">
         <v>725</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="S49" s="10" t="n">
         <v>0.09255122231441884</v>
       </c>
     </row>
@@ -3441,33 +3521,34 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>824.00</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>432.00</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>534.00</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="3" t="n">
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="P50" s="4" t="n">
+      <c r="Q50" s="4" t="n">
         <v>626</v>
       </c>
-      <c r="Q50" s="5" t="n">
+      <c r="R50" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="R50" s="6" t="n">
+      <c r="S50" s="6" t="n">
         <v>0.003072430769084201</v>
       </c>
     </row>
@@ -3493,31 +3574,32 @@
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>778.00</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>474.00</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>458.00</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
-      <c r="O51" s="8" t="inlineStr"/>
-      <c r="P51" s="9" t="n">
+      <c r="O51" s="7" t="inlineStr"/>
+      <c r="P51" s="8" t="inlineStr"/>
+      <c r="Q51" s="9" t="n">
         <v>558</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="R51" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="R51" s="10" t="n">
+      <c r="S51" s="10" t="n">
         <v>-0.001619575909284695</v>
       </c>
     </row>
@@ -3551,25 +3633,26 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>2654.00</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="3" t="n">
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="3" t="n">
         <v>7387</v>
       </c>
-      <c r="P52" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>5269.5</v>
       </c>
-      <c r="Q52" s="5" t="n">
+      <c r="R52" s="5" t="n">
         <v>-2117.5</v>
       </c>
-      <c r="R52" s="6" t="n">
+      <c r="S52" s="6" t="n">
         <v>-0.1897435437911074</v>
       </c>
     </row>
@@ -3603,23 +3686,24 @@
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>5486.00</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
-      <c r="O53" s="8" t="inlineStr"/>
-      <c r="P53" s="9" t="n">
+      <c r="O53" s="7" t="inlineStr"/>
+      <c r="P53" s="8" t="inlineStr"/>
+      <c r="Q53" s="9" t="n">
         <v>6038.75</v>
       </c>
-      <c r="Q53" s="9" t="n">
+      <c r="R53" s="9" t="n">
         <v>769.25</v>
       </c>
-      <c r="R53" s="10" t="n">
+      <c r="S53" s="10" t="n">
         <v>0.06893044678220039</v>
       </c>
     </row>
@@ -3635,7 +3719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P223"/>
+  <dimension ref="A1:P227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -19123,127 +19207,407 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="16" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Freeway_seed2030_Both</t>
-        </is>
-      </c>
-      <c r="B222" s="16" t="inlineStr">
-        <is>
-          <t>khvdesdy</t>
-        </is>
-      </c>
-      <c r="C222" s="16" t="inlineStr">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2710_X</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>vpxa1ak7</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n">
+        <v>2710</v>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I222" s="7" t="inlineStr">
+        <is>
+          <t>31.30</t>
+        </is>
+      </c>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="K222" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L222" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M222" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N222" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O222" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P222" s="15" t="n">
+        <v>46290.22195601852</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2030_O</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>l96lmgvj</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H223" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I223" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K223" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L223" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M223" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N223" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O223" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P223" s="15" t="n">
+        <v>46290.28285879629</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2030_X</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>1fcphg7b</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I224" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K224" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L224" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M224" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N224" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O224" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P224" s="15" t="n">
+        <v>46290.55267361111</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2040_O</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>4ukadgjv</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>2040</v>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I225" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K225" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L225" s="7" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M225" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N225" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O225" s="7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P225" s="15" t="n">
+        <v>46290.71641203704</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_BankHeist_seed2000_O</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>ld1pwoi6</t>
+        </is>
+      </c>
+      <c r="C226" s="16" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="D222" s="16" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E222" s="16" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F222" s="16" t="inlineStr">
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E226" s="16" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F226" s="16" t="inlineStr">
+        <is>
+          <t>BankHeist</t>
+        </is>
+      </c>
+      <c r="G226" s="16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H226" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I226" s="16" t="inlineStr"/>
+      <c r="J226" s="16" t="inlineStr"/>
+      <c r="K226" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L226" s="16" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M226" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N226" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="O226" s="16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P226" s="17" t="n">
+        <v>46290.94701388889</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2_AC_Freeway_seed2040_X</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>pguxxdyy</t>
+        </is>
+      </c>
+      <c r="C227" s="16" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="inlineStr">
+        <is>
+          <t>Mamba2</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F227" s="16" t="inlineStr">
         <is>
           <t>Freeway</t>
         </is>
       </c>
-      <c r="G222" s="16" t="n">
-        <v>2030</v>
-      </c>
-      <c r="H222" s="16" t="inlineStr">
+      <c r="G227" s="16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="H227" s="16" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I222" s="16" t="inlineStr"/>
-      <c r="J222" s="16" t="inlineStr"/>
-      <c r="K222" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L222" s="16" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M222" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="N222" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="O222" s="16" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P222" s="17" t="n">
-        <v>46290.07979166666</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="16" t="inlineStr">
-        <is>
-          <t>Mamba2_AC_Freeway_seed2030_Both</t>
-        </is>
-      </c>
-      <c r="B223" s="16" t="inlineStr">
-        <is>
-          <t>khvdesdy</t>
-        </is>
-      </c>
-      <c r="C223" s="16" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="D223" s="16" t="inlineStr">
-        <is>
-          <t>Mamba2</t>
-        </is>
-      </c>
-      <c r="E223" s="16" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="F223" s="16" t="inlineStr">
-        <is>
-          <t>Freeway</t>
-        </is>
-      </c>
-      <c r="G223" s="16" t="n">
-        <v>2030</v>
-      </c>
-      <c r="H223" s="16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I223" s="16" t="inlineStr"/>
-      <c r="J223" s="16" t="inlineStr"/>
-      <c r="K223" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L223" s="16" t="inlineStr">
-        <is>
-          <t>retrieved</t>
-        </is>
-      </c>
-      <c r="M223" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="N223" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="O223" s="16" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P223" s="17" t="n">
-        <v>46290.07979166666</v>
+      <c r="I227" s="16" t="inlineStr"/>
+      <c r="J227" s="16" t="inlineStr"/>
+      <c r="K227" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L227" s="16" t="inlineStr">
+        <is>
+          <t>retrieved</t>
+        </is>
+      </c>
+      <c r="M227" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N227" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="O227" s="16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P227" s="17" t="n">
+        <v>46290.97782407407</v>
       </c>
     </row>
   </sheetData>
